--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F391"/>
+  <dimension ref="A1:F419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3361,7 +3361,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>pre_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
@@ -3389,7 +3389,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3417,7 +3417,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3501,7 +3501,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3529,7 +3529,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3585,7 +3585,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3641,7 +3641,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3753,7 +3753,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>pre_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -3809,17 +3809,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>צמח</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3837,7 +3837,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3865,17 +3865,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>צמח</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3893,7 +3893,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3941,17 +3941,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3979,7 +3977,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>נתיב השיירה</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3999,15 +3997,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4027,17 +4027,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>נתיב השיירה</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4057,17 +4055,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4087,15 +4083,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4115,15 +4113,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4151,7 +4151,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4179,7 +4179,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4235,7 +4235,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4263,7 +4263,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4291,7 +4291,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4319,7 +4319,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4375,7 +4375,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4459,7 +4459,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4487,7 +4487,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4515,7 +4515,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4543,7 +4543,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4571,7 +4571,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4599,7 +4599,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4627,7 +4627,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4655,7 +4655,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4683,12 +4683,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>אזור תעשייה אלון התבור</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4711,12 +4711,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>אחוזת ברק</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4739,7 +4739,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>דברת</t>
+          <t>אזור תעשייה אלון התבור</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4767,7 +4767,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>דחי</t>
+          <t>אחוזת ברק</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>טמרה בגלבוע</t>
+          <t>דברת</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4823,7 +4823,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>מרחביה מושב</t>
+          <t>דחי</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4851,7 +4851,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>מרחביה קיבוץ</t>
+          <t>טמרה בגלבוע</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4879,7 +4879,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>נאעורה</t>
+          <t>מרחביה מושב</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4907,7 +4907,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>נין</t>
+          <t>מרחביה קיבוץ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4935,7 +4935,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>סולם</t>
+          <t>נאעורה</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4963,7 +4963,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>עפולה</t>
+          <t>נין</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4991,7 +4991,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>רמת צבי</t>
+          <t>סולם</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>עפולה</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5047,7 +5047,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>רמת צבי</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5075,7 +5075,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>גדעונה</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>גזית</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>גן נר</t>
+          <t>גדעונה</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>גזית</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5187,7 +5187,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>היוגב</t>
+          <t>גן נר</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5215,12 +5215,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>יזרעאל</t>
+          <t>היוגב</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5271,12 +5271,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ישובי אומן</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5299,7 +5299,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ישובי יעל</t>
+          <t>יזרעאל</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5327,7 +5327,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>ישובי אומן</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5355,7 +5355,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>כפר ברוך</t>
+          <t>ישובי יעל</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5375,17 +5375,15 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>כפר יחזקאל</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5413,7 +5411,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>כפר מצר</t>
+          <t>כפר ברוך</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5433,15 +5431,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>כפר קיש</t>
+          <t>כפר יחזקאל</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5469,7 +5469,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>כפר מצר</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5497,7 +5497,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>מגן שאול</t>
+          <t>כפר קיש</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>מוקיבלה</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5553,7 +5553,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>מרכז חבר</t>
+          <t>מגן שאול</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>מתחם סקי גלבוע</t>
+          <t>מוקיבלה</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5609,7 +5609,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>נורית</t>
+          <t>מרכז חבר</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5637,7 +5637,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>סנדלה</t>
+          <t>מתחם סקי גלבוע</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5665,7 +5665,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>עין דור</t>
+          <t>נורית</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5693,7 +5693,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>קבוצת גבע</t>
+          <t>סנדלה</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>רם און</t>
+          <t>עין דור</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5749,7 +5749,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>קבוצת גבע</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5777,7 +5777,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>רם און</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר ברוך</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5825,17 +5825,15 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבואות הגלבוע</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5863,12 +5861,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>תחנת רכבת כפר ברוך</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5883,20 +5881,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>אזור תעשייה מבואות הגלבוע</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5919,7 +5919,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5947,7 +5947,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5975,7 +5975,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6003,7 +6003,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6087,12 +6087,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6143,12 +6143,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>בית ירח</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6171,12 +6171,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6199,7 +6199,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>גבעת אבני</t>
+          <t>בית ירח</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6227,12 +6227,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>גבעת אבני</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6283,7 +6283,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6311,7 +6311,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6339,7 +6339,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6367,7 +6367,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6395,7 +6395,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6423,12 +6423,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6479,12 +6479,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6563,12 +6563,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6591,7 +6591,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6619,12 +6619,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6647,12 +6647,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6675,7 +6675,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6703,12 +6703,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6731,7 +6731,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6759,7 +6759,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6787,12 +6787,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6815,12 +6815,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6843,7 +6843,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6871,12 +6871,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>עילבון</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6927,7 +6927,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6955,12 +6955,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>עילבון</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6983,7 +6983,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7011,12 +7011,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7039,7 +7039,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7067,12 +7067,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -7095,7 +7095,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>שרונה</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7123,7 +7123,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7151,12 +7151,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>שרונה</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -7179,12 +7179,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7207,12 +7207,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7227,17 +7227,15 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F239" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7257,22 +7255,20 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F240" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -7297,12 +7293,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -7327,12 +7323,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7357,12 +7353,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7387,7 +7383,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7407,15 +7403,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7445,7 +7443,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7465,17 +7463,15 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F247" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7495,20 +7491,22 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7533,7 +7531,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7553,22 +7551,20 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F250" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -7593,7 +7589,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7623,7 +7619,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7653,7 +7649,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7683,12 +7679,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7713,12 +7709,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7743,7 +7739,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7763,15 +7759,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7791,20 +7789,22 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7855,12 +7855,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7883,12 +7883,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7903,22 +7903,20 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F262" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7933,22 +7931,20 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F263" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7973,12 +7969,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7997,18 +7993,18 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -8023,15 +8019,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8061,7 +8059,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8081,17 +8079,15 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F268" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8111,20 +8107,22 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -8149,7 +8147,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>מגדל העמק</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8169,17 +8167,15 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F271" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8209,7 +8205,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>מגדל העמק</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8229,15 +8225,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8267,7 +8265,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8287,17 +8285,15 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F275" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8317,15 +8313,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F276" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>משהד</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8349,18 +8347,18 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>420</v>
+        <v>360</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -8375,17 +8373,15 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F278" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>משהד</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8405,15 +8401,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F279" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8433,15 +8431,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8461,17 +8461,15 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8491,17 +8489,15 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F282" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8521,20 +8517,22 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F283" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -8549,20 +8547,22 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8585,12 +8585,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8605,17 +8605,15 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F286" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8635,17 +8633,15 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F287" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8669,18 +8665,18 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>420</v>
+        <v>360</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8705,7 +8701,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8729,18 +8725,18 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8755,15 +8751,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F291" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8793,7 +8791,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8821,12 +8819,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8845,18 +8843,18 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>420</v>
+        <v>360</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8871,17 +8869,15 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F295" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8901,20 +8897,22 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8939,12 +8937,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8959,22 +8957,20 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8989,15 +8985,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9027,12 +9025,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9055,12 +9053,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -9075,15 +9073,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9111,12 +9111,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -9139,7 +9139,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9167,7 +9167,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9195,7 +9195,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9223,7 +9223,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>חוסנייה</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9251,7 +9251,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9279,12 +9279,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>חוסנייה</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9307,7 +9307,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9335,12 +9335,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9363,17 +9363,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>מכמנים - כמאנה מערבית</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -9391,7 +9391,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9419,17 +9419,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>מכמנים - כמאנה מערבית</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -9447,7 +9447,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9503,7 +9503,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9531,7 +9531,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9551,22 +9551,20 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F319" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9581,22 +9579,20 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F320" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>סואעד חמירה</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9615,23 +9611,23 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9645,23 +9641,23 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>סואעד חמירה</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9681,12 +9677,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9711,12 +9707,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9731,15 +9727,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9759,15 +9757,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>גלעד</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9787,17 +9787,15 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F327" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9817,17 +9815,15 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F328" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9847,15 +9843,17 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9875,15 +9873,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>מדרך עוז</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9903,17 +9903,15 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F331" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9941,7 +9939,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>עין העמק</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9961,15 +9959,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>עין השופט</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9997,7 +9997,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10017,22 +10017,20 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F335" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10055,12 +10053,12 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -10075,15 +10073,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10111,7 +10111,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>חדרה - נווה חיים</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10167,7 +10167,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>חדרה - נווה חיים</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10195,7 +10195,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10251,12 +10251,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>באקה אל גרבייה</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10307,12 +10307,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>באקה אל גרבייה</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -10335,7 +10335,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10363,12 +10363,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10419,12 +10419,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>גן השומרון</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10447,7 +10447,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10475,7 +10475,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>גן השומרון</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -10503,7 +10503,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10587,12 +10587,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -10615,12 +10615,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -10643,12 +10643,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10671,12 +10671,12 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -10699,12 +10699,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10727,7 +10727,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10755,12 +10755,12 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>עין עירון</t>
+          <t>מצר</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -10783,7 +10783,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10811,7 +10811,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>עין עירון</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10839,7 +10839,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10867,7 +10867,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10895,12 +10895,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10923,7 +10923,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10951,7 +10951,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>רגבים</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10979,12 +10979,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -11007,7 +11007,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>אום אל פחם</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11063,12 +11063,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11091,7 +11091,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>ברטעה</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11119,12 +11119,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11175,12 +11175,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -11203,7 +11203,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11231,12 +11231,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>מעלה עירון</t>
+          <t>מועאוויה</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11287,7 +11287,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11315,12 +11315,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>מעלה עירון</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -11343,7 +11343,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>מצפה אילן</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11371,12 +11371,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -11399,12 +11399,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>עין אל סהלה</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -11427,12 +11427,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11455,7 +11455,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -11511,7 +11511,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>נמל קיסריה</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11539,12 +11539,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>קציר</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11567,30 +11567,814 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
+          <t>נמל קיסריה</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Menashe</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>קציר</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
           <t>מטולה</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>Confrontation Line</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="C393" t="inlineStr">
         <is>
           <t>Golan</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
         <is>
           <t>missile_only</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>מטולה</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>הגושרים</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>הגושרים</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>עמיר</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>שדה נחמיה</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>כפר בלום</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>נאות מרדכי</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ע'ג'ר</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>בית הלל</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>בית הלל</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>מעיין ברוך</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>כפר יובל</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>מרגליות</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>קיבוץ דן</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>שניר</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>הגושרים</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>הגושרים</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>עמיר</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>שדה נחמיה</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>עמיר</t>
+          <t>כפר בלום</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>שדה נחמיה</t>
+          <t>נאות מרדכי</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>כפר בלום</t>
+          <t>ע'ג'ר</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>נאות מרדכי</t>
+          <t>בית הלל</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ע'ג'ר</t>
+          <t>בית הלל</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>בית הלל</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>בית הלל</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>מרגליות</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>קיבוץ דן</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>מרגליות</t>
+          <t>שניר</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1179,17 +1179,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>קיבוץ דן</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1207,17 +1207,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>שניר</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1235,17 +1235,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1263,17 +1263,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,514 +779,10 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>עמיר</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>שדה נחמיה</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>כפר בלום</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>נאות מרדכי</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ע'ג'ר</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>בית הלל</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>בית הלל</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>מעיין ברוך</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>כפר יובל</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>תל חי</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>תל חי</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>מרגליות</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>קיבוץ דן</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>שניר</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>עמוקה</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Upper Galilee</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Galilee</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>חצור הגלילית</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Upper Galilee</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Galilee</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>מטולה</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>מטולה</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>מלכיה</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -527,7 +527,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>מלכיה</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -759,30 +759,450 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>מלכיה</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>יראון</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ראש הנקרה</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>שלומי</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>חוף בצת</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>בצת</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>אזור תעשייה קריית ביאליק</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HaMifratz (The Bay)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>כפר מסריק</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>אזור תעשייה שער נעמן</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>עכו - אזור תעשייה</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>קריית ביאליק</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HaMifratz (The Bay)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ג'דידה מכר</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>עין המפרץ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>עכו - רמות ים</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>עכו</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>בית העלמין החדש עכו</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>מלכיה</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -787,7 +787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>שלומי</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -927,17 +927,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -955,17 +955,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -983,17 +983,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1011,17 +1011,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1039,17 +1039,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1067,17 +1067,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1095,17 +1095,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -1123,17 +1123,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1151,17 +1151,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1179,30 +1179,1122 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>מלכיה</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>יראון</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ראש הנקרה</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ראש הנקרה</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ראש הנקרה</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>שלומי</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>שלומי</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>שלומי</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>שלומי</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>חוף בצת</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>חוף בצת</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>בצת</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>בצת</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>בצת</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>בצת</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>אזור תעשייה קריית ביאליק</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HaMifratz (The Bay)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>כפר מסריק</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>אזור תעשייה שער נעמן</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>עכו - אזור תעשייה</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>קריית ביאליק</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HaMifratz (The Bay)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ג'דידה מכר</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>עין המפרץ</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>עכו - רמות ים</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>עכו</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>בית העלמין החדש עכו</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Upper Galilee</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Galilee</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>מרגליות</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>drone_only</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>חניתה</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>מצובה</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>גשר הזיו</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>לימן</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>לימן</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>סער</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>בן עמי</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>נהריה</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>כברי</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>חוף אכזיב</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>חוף אכזיב</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>עברון</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>מזרעה</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Upper Galilee</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Galilee</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>איזור תעשייה מילואות צפון</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>אבירים</t>
+          <t>מעיליא</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>זרעית</t>
+          <t>אבירים</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>שומרה</t>
+          <t>אבירים</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>שתולה</t>
+          <t>זרעית</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>נטועה</t>
+          <t>זרעית</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>פסוטה</t>
+          <t>שומרה</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -787,7 +787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>מלכיה</t>
+          <t>שומרה</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>שתולה</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>נטועה</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -871,7 +871,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>פסוטה</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -899,30 +899,1122 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>מלכיה</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>קריית שמונה</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>תל חי</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>מטולה</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Confrontation Line</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Golan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>מטולה</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>מטולה</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>מטולה</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>מטולה</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>כפר גלעדי</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>כפר יובל</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>כפר יובל</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>כפר יובל</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>כפר יובל</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>משגב עם</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>גונן</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>מרגליות</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>מרגליות</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>בית הלל</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>בית הלל</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>מעיין ברוך</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>מעיין ברוך</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>הגושרים</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>הגושרים</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ע'ג'ר</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ע'ג'ר</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>מעונה</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>מעלות תרשיחא</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ערב אל עראמשה</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>דפנה</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Confrontation Line</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Golan</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1011,7 +1011,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1123,7 +1123,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מרגליות</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>גונן</t>
+          <t>מרגליות</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>מרגליות</t>
+          <t>בית הלל</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>בית הלל</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>הגושרים</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1375,7 +1375,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>ע'ג'ר</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ע'ג'ר</t>
+          <t>אבירים</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1459,7 +1459,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>אבירים</t>
+          <t>מעונה</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>מעונה</t>
+          <t>מעיליא</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>מעיליא</t>
+          <t>מעלות תרשיחא</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>מעלות תרשיחא</t>
+          <t>זרעית</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>זרעית</t>
+          <t>ערב אל עראמשה</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ערב אל עראמשה</t>
+          <t>שומרה</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1627,7 +1627,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>שומרה</t>
+          <t>דפנה</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1655,17 +1655,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>דפנה</t>
+          <t>צפת - נוף כנרת</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>pre_only</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>צפת - נוף כנרת</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>אזור תעשייה כרמיאל</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>אזור תעשייה כרמיאל</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1767,7 +1767,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ביריה</t>
+          <t>בית ג'אן</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>בית ג'אן</t>
+          <t>בענה</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>בענה</t>
+          <t>דיר אל-אסד</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>דיר אל-אסד</t>
+          <t>הר חלוץ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>הר חלוץ</t>
+          <t>חרשים</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>חרשים</t>
+          <t>כרמיאל</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1935,7 +1935,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>כרמיאל</t>
+          <t>לבון</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1963,7 +1963,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>לבון</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>נחף</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>נחף</t>
+          <t>סאג'ור</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>סאג'ור</t>
+          <t>עין אל אסד</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>עין אל אסד</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2095,15 +2095,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2123,17 +2125,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>ראמה</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ראמה</t>
+          <t>שזור</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2189,7 +2189,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>שזור</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>אמירים</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2245,7 +2245,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>אמירים</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2273,7 +2273,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>כסרא סמיע</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2329,7 +2329,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>כסרא סמיע</t>
+          <t>כפר שמאי</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>כפר שמאי</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2413,7 +2413,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2441,7 +2441,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2469,7 +2469,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>פרוד</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>פרוד</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2525,7 +2525,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>שפר</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>שפר</t>
+          <t>חמדת ימים</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2581,17 +2581,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>חמדת ימים</t>
+          <t>אושה</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2601,15 +2601,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>אושה</t>
+          <t>חיפה - בת גלים ק.אליעזר</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2639,7 +2641,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>חיפה - בת גלים ק.אליעזר</t>
+          <t>חיפה - מערב</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2669,7 +2671,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>חיפה - מערב</t>
+          <t>חיפה - מפרץ</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2699,7 +2701,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>חיפה - מפרץ</t>
+          <t>חיפה - נווה שאנן ורמות כרמל</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2729,7 +2731,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>חיפה - נווה שאנן ורמות כרמל</t>
+          <t>חיפה - קריית חיים ושמואל</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2759,7 +2761,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>חיפה - קריית חיים ושמואל</t>
+          <t>כפר ביאליק</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2789,7 +2791,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>כפר ביאליק</t>
+          <t>כפר המכבי</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2819,7 +2821,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>כפר המכבי</t>
+          <t>קריית אתא</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2849,7 +2851,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>קריית אתא</t>
+          <t>קריית ביאליק</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2879,7 +2881,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>קריית ים</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2909,7 +2911,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>קריית ים</t>
+          <t>קריית מוצקין</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2939,7 +2941,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>קריית מוצקין</t>
+          <t>רמת יוחנן</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2969,17 +2971,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>רמת יוחנן</t>
+          <t>אזור תעשייה שער נעמן</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2999,7 +3001,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>אפק</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3029,17 +3031,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>אפק</t>
+          <t>אזור תעשייה קריית ביאליק</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3059,7 +3061,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3089,7 +3091,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>איבטין</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3119,12 +3121,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>איבטין</t>
+          <t>בית אורן</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3149,7 +3151,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>בית אורן</t>
+          <t>גבעת וולפסון</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3179,7 +3181,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>גבעת וולפסון</t>
+          <t>דלית אל כרמל</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3209,12 +3211,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>דלית אל כרמל</t>
+          <t>החותרים</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3239,7 +3241,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>החותרים</t>
+          <t>טירת כרמל</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3269,7 +3271,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>טירת כרמל</t>
+          <t>יגור</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3299,7 +3301,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>יגור</t>
+          <t>כפר גלים</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3329,7 +3331,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>כפר גלים</t>
+          <t>כפר חסידים</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3359,12 +3361,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>כפר חסידים</t>
+          <t>עספיא</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3389,12 +3391,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>עספיא</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3419,17 +3421,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>אורנים</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3449,7 +3451,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>אורנים</t>
+          <t>אלונים</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3479,7 +3481,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>אלונים</t>
+          <t>בסמת טבעון</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3509,7 +3511,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>בסמת טבעון</t>
+          <t>כפר תקווה</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3539,7 +3541,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>כפר תקווה</t>
+          <t>נופית</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3569,7 +3571,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>נופית</t>
+          <t>קריית טבעון - בית זייד</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3599,7 +3601,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>קריית טבעון - בית זייד</t>
+          <t>ראס עלי</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3629,7 +3631,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ראס עלי</t>
+          <t>שער העמקים</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3659,17 +3661,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>שער העמקים</t>
+          <t>אזור תעשייה ניר עציון</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3689,12 +3691,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>אזור תעשייה ניר עציון</t>
+          <t>בית סוהר קישון</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3719,7 +3721,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>בית סוהר קישון</t>
+          <t>בית צבי</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3749,7 +3751,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>בית צבי</t>
+          <t>בת שלמה</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3769,17 +3771,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>בת שלמה</t>
+          <t>גבע כרמל</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3799,15 +3799,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>גבע כרמל</t>
+          <t>הבונים</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3837,7 +3839,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>הבונים</t>
+          <t>מאיר שפיה</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3857,17 +3859,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>מאיר שפיה</t>
+          <t>מגדים</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3887,15 +3887,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>מגדים</t>
+          <t>נווה ים</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3925,7 +3927,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>נווה ים</t>
+          <t>עופר</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3945,17 +3947,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>עופר</t>
+          <t>עין איילה</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>עין איילה</t>
+          <t>עין הוד</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4003,15 +4003,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>עין הוד</t>
+          <t>עין חוד</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4041,7 +4043,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>עין חוד</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4071,7 +4073,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>עתלית</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4101,7 +4103,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>עתלית</t>
+          <t>פוריידיס</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4121,17 +4123,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>פוריידיס</t>
+          <t>צרופה</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4151,20 +4151,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>צרופה</t>
+          <t>בית עלמין תל רגב</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4189,17 +4191,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>בית עלמין תל רגב</t>
+          <t>כפר ח'וואלד</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4219,17 +4221,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>כפר ח'וואלד</t>
+          <t>תחנת רכבת כפר יהושוע</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4249,17 +4251,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר יהושוע</t>
+          <t>אזור תעשייה צ.ח.ר</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4269,17 +4271,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>אזור תעשייה צ.ח.ר</t>
+          <t>אליפלט</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>אליפלט</t>
+          <t>אמנון</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>אמנון</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4363,7 +4363,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4391,7 +4391,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4419,7 +4419,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4447,7 +4447,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4475,7 +4475,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4503,7 +4503,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4531,7 +4531,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4559,7 +4559,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4643,7 +4643,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4699,7 +4699,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4727,7 +4727,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4783,7 +4783,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4811,17 +4811,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>צמח</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4839,17 +4839,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>צמח</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4859,15 +4859,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4887,17 +4889,15 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4917,15 +4917,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4955,7 +4957,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4975,17 +4977,15 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>נתיב השיירה</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5013,7 +5013,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>נתיב השיירה</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5033,15 +5033,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5071,7 +5073,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5101,7 +5103,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5131,7 +5133,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5151,17 +5153,15 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5189,7 +5189,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5209,15 +5209,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5237,17 +5239,15 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5295,15 +5295,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5333,7 +5335,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5353,17 +5355,15 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5383,15 +5383,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5411,17 +5413,15 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5449,7 +5449,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5477,7 +5477,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5505,7 +5505,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5533,7 +5533,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5561,7 +5561,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5645,7 +5645,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5673,7 +5673,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5701,12 +5701,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>אזור תעשייה אלון התבור</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>אזור תעשייה אלון התבור</t>
+          <t>אחוזת ברק</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5757,7 +5757,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>אחוזת ברק</t>
+          <t>דברת</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>דברת</t>
+          <t>דחי</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>דחי</t>
+          <t>טמרה בגלבוע</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5841,7 +5841,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>טמרה בגלבוע</t>
+          <t>מרחביה מושב</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5869,7 +5869,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>מרחביה מושב</t>
+          <t>מרחביה קיבוץ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>מרחביה קיבוץ</t>
+          <t>נאעורה</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5925,7 +5925,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>נאעורה</t>
+          <t>נין</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5953,7 +5953,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>נין</t>
+          <t>סולם</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>סולם</t>
+          <t>עפולה</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6009,7 +6009,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>עפולה</t>
+          <t>רמת צבי</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>רמת צבי</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>גדעונה</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>גדעונה</t>
+          <t>גזית</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>גזית</t>
+          <t>גן נר</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6177,7 +6177,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>גן נר</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6205,7 +6205,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>היוגב</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6233,12 +6233,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>היוגב</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6261,12 +6261,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>יזרעאל</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6289,7 +6289,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>יזרעאל</t>
+          <t>ישובי אומן</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6317,7 +6317,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ישובי אומן</t>
+          <t>ישובי יעל</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ישובי יעל</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6373,7 +6373,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>כפר ברוך</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6401,7 +6401,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>כפר ברוך</t>
+          <t>כפר יחזקאל</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6429,7 +6429,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>כפר יחזקאל</t>
+          <t>כפר מצר</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6457,7 +6457,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>כפר מצר</t>
+          <t>כפר קיש</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6485,7 +6485,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>כפר קיש</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>מגן שאול</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6541,7 +6541,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>מגן שאול</t>
+          <t>מוקיבלה</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>מוקיבלה</t>
+          <t>מרכז חבר</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>מרכז חבר</t>
+          <t>מתחם סקי גלבוע</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6625,7 +6625,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>מתחם סקי גלבוע</t>
+          <t>נורית</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>נורית</t>
+          <t>סנדלה</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6681,7 +6681,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>סנדלה</t>
+          <t>עין דור</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>עין דור</t>
+          <t>קבוצת גבע</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>קבוצת גבע</t>
+          <t>רם און</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6765,7 +6765,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>רם און</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6793,7 +6793,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>תחנת רכבת כפר ברוך</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6849,7 +6849,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר ברוך</t>
+          <t>אזור תעשייה מבואות הגלבוע</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6877,12 +6877,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבואות הגלבוע</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6933,7 +6933,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6961,7 +6961,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6989,7 +6989,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7017,7 +7017,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7045,7 +7045,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7073,7 +7073,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7101,12 +7101,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -7157,7 +7157,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>בית ירח</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7185,12 +7185,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>בית ירח</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -7213,12 +7213,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>גבעת אבני</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -7241,7 +7241,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>גבעת אבני</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7297,7 +7297,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7325,7 +7325,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7353,7 +7353,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7381,7 +7381,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7437,12 +7437,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7465,12 +7465,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7493,12 +7493,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7521,12 +7521,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7549,7 +7549,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7577,12 +7577,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7605,12 +7605,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -7633,7 +7633,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7661,12 +7661,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -7689,12 +7689,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7717,7 +7717,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7773,7 +7773,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7801,12 +7801,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -7829,7 +7829,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7857,7 +7857,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7885,12 +7885,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7913,12 +7913,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>עילבון</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -7941,12 +7941,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>עילבון</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -7969,7 +7969,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8025,12 +8025,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -8053,12 +8053,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -8081,7 +8081,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>שרונה</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8137,17 +8137,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>שרונה</t>
+          <t>אשדות יעקב</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -8165,7 +8165,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>אשדות יעקב</t>
+          <t>אלמגור</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>אלמגור</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -8213,20 +8213,22 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8251,12 +8253,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8271,17 +8273,15 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F276" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8301,15 +8301,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F277" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8339,12 +8341,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8369,7 +8371,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8399,12 +8401,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -8429,7 +8431,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8459,7 +8461,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8479,17 +8481,15 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F283" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8509,15 +8509,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8537,17 +8539,15 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F285" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8575,12 +8575,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8595,20 +8595,22 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8633,7 +8635,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8663,7 +8665,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8693,7 +8695,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8723,7 +8725,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8753,12 +8755,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8783,7 +8785,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8813,7 +8815,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8843,7 +8845,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8873,12 +8875,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8903,12 +8905,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8933,12 +8935,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8953,17 +8955,15 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8991,12 +8991,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -9011,15 +9011,17 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9049,12 +9051,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -9079,7 +9081,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9099,17 +9101,15 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F304" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9157,15 +9157,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9185,22 +9187,20 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F307" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9215,20 +9215,22 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>מגדל העמק</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9243,22 +9245,20 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F309" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>מגדל העמק</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -9273,20 +9273,22 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -9301,22 +9303,20 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F311" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -9331,20 +9331,22 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -9369,12 +9371,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -9399,12 +9401,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>משהד</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -9419,17 +9421,15 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F315" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>משהד</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9449,15 +9449,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9477,17 +9479,15 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F317" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9515,7 +9515,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9535,15 +9535,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9573,7 +9575,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9593,22 +9595,20 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F321" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9623,15 +9623,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9661,12 +9663,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9691,12 +9693,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9721,12 +9723,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9741,17 +9743,15 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F326" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9771,15 +9771,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9809,12 +9811,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -9839,12 +9841,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -9869,12 +9871,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -9899,7 +9901,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9929,12 +9931,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -9959,12 +9961,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -9989,7 +9991,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10019,12 +10021,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -10039,17 +10041,15 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F336" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10077,7 +10077,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10097,20 +10097,22 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -10125,22 +10127,20 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10155,20 +10155,22 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -10193,7 +10195,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10213,17 +10215,15 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F342" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10243,15 +10243,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10271,17 +10273,15 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F344" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10309,7 +10309,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>חוסנייה</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10337,7 +10337,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>חוסנייה</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10365,12 +10365,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10393,12 +10393,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10449,17 +10449,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>מכמנים - כמאנה מערבית</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -10477,17 +10477,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>מכמנים - כמאנה מערבית</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -10505,7 +10505,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10525,15 +10525,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10553,17 +10555,15 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F354" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10591,7 +10591,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10639,20 +10639,22 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -10677,7 +10679,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>סואעד חמירה</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -10707,17 +10709,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>סואעד חמירה</t>
+          <t>חמת גדר</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10727,17 +10729,15 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F360" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>חמת גדר</t>
+          <t>אבני איתן</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -10765,7 +10765,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>אבני איתן</t>
+          <t>אלי עד</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10793,7 +10793,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>אלי עד</t>
+          <t>אפיק</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10821,7 +10821,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>אפיק</t>
+          <t>בני יהודה וגבעת יואב</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10849,7 +10849,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>בני יהודה וגבעת יואב</t>
+          <t>גשור</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>גשור</t>
+          <t>האון</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10905,7 +10905,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>האון</t>
+          <t>חספין</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10933,7 +10933,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>חספין</t>
+          <t>כפר חרוב</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10961,7 +10961,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>כפר חרוב</t>
+          <t>מבוא חמה</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10989,7 +10989,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>מבוא חמה</t>
+          <t>מיצר</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>מיצר</t>
+          <t>מסדה</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11045,7 +11045,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>מסדה</t>
+          <t>מעגן</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11073,7 +11073,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>מעגן</t>
+          <t>נאות גולן</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11101,7 +11101,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>נאות גולן</t>
+          <t>נוב</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11129,7 +11129,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>נוב</t>
+          <t>נטור</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11157,7 +11157,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>נטור</t>
+          <t>עין גב</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11185,7 +11185,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>עין גב</t>
+          <t>רמת מגשימים</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11213,7 +11213,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>רמת מגשימים</t>
+          <t>שער הגולן</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11241,7 +11241,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>שער הגולן</t>
+          <t>תל קציר</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11269,7 +11269,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>תל קציר</t>
+          <t>אזור תעשייה בני יהודה</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11297,7 +11297,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>אזור תעשייה בני יהודה</t>
+          <t>אניעם</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11325,7 +11325,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>אניעם</t>
+          <t>חד נס</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11353,7 +11353,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>חד נס</t>
+          <t>יונתן</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11381,7 +11381,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>יונתן</t>
+          <t>כנף</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11409,7 +11409,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>כנף</t>
+          <t>מעלה גמלא</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11437,7 +11437,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>מעלה גמלא</t>
+          <t>קדמת צבי</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11465,7 +11465,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>קדמת צבי</t>
+          <t>קצרין - אזור תעשייה</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11493,7 +11493,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>קצרין - אזור תעשייה</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -11521,7 +11521,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>קשת</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11549,7 +11549,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>קשת</t>
+          <t>רמות</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -11577,12 +11577,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>רמות</t>
+          <t>אודם</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11605,7 +11605,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>אודם</t>
+          <t>אל רום</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11633,7 +11633,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>אל רום</t>
+          <t>בוקעתא</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11661,7 +11661,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>בוקעתא</t>
+          <t>מג'דל שמס</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11689,7 +11689,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>מג'דל שמס</t>
+          <t>מסעדה</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11717,7 +11717,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>מסעדה</t>
+          <t>נמרוד</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11745,7 +11745,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>נמרוד</t>
+          <t>עין קנייא</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11773,7 +11773,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>עין קנייא</t>
+          <t>קלע אלון</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11801,7 +11801,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>קלע אלון</t>
+          <t>רמת טראמפ</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -11829,7 +11829,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>רמת טראמפ</t>
+          <t>אורטל</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -11857,12 +11857,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>אורטל</t>
+          <t>אלוני הבשן</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -11885,12 +11885,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>אלוני הבשן</t>
+          <t>מרום גולן</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -11913,7 +11913,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>מרום גולן</t>
+          <t>עין זיוון</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11941,7 +11941,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>עין זיוון</t>
+          <t>שעל</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11969,17 +11969,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>שעל</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -11989,15 +11989,17 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12017,22 +12019,20 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F406" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -12055,7 +12055,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>גלעד</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12083,7 +12083,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12111,7 +12111,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12139,7 +12139,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12167,7 +12167,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>מדרך עוז</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -12195,7 +12195,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -12223,7 +12223,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>עין העמק</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -12251,7 +12251,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>עין השופט</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -12279,7 +12279,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12307,7 +12307,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12363,12 +12363,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -12391,7 +12391,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -12419,7 +12419,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>חדרה - נווה חיים</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -12475,7 +12475,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>חדרה - נווה חיים</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -12503,7 +12503,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -12531,7 +12531,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -12559,7 +12559,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -12587,12 +12587,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>באקה אל גרבייה</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -12615,12 +12615,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>באקה אל גרבייה</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -12643,7 +12643,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12671,7 +12671,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -12699,12 +12699,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -12727,12 +12727,12 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>גן השומרון</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12783,7 +12783,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>גן השומרון</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -12811,7 +12811,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12839,7 +12839,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12867,7 +12867,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12895,7 +12895,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12923,12 +12923,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -12951,7 +12951,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12979,12 +12979,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -13007,7 +13007,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13035,12 +13035,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>מצר</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -13063,12 +13063,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -13091,7 +13091,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>עין עירון</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -13119,7 +13119,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>עין עירון</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -13147,7 +13147,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -13175,7 +13175,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -13203,7 +13203,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -13231,12 +13231,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>רגבים</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -13259,12 +13259,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -13287,12 +13287,12 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>אום אל פחם</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -13315,7 +13315,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -13343,7 +13343,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>ברטעה</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -13399,12 +13399,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -13427,12 +13427,12 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -13455,7 +13455,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -13483,7 +13483,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -13511,12 +13511,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -13539,12 +13539,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>מועאוויה</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -13567,7 +13567,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -13595,7 +13595,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>מעלה עירון</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -13623,7 +13623,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>מעלה עירון</t>
+          <t>מצפה אילן</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -13651,12 +13651,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -13679,12 +13679,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>עין אל סהלה</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -13735,12 +13735,12 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -13763,7 +13763,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -13791,7 +13791,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -13819,7 +13819,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -13847,7 +13847,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>נמל קיסריה</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -13875,12 +13875,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>נמל קיסריה</t>
+          <t>קציר</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>Wadi Ara</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -13899,34 +13899,6 @@
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>קציר</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>Wadi Ara</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>Haifa Area</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="E474" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F474" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F677"/>
+  <dimension ref="A1:F665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>חוף אכזיב</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>לימן</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>חוף אכזיב</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>שלומי</t>
+          <t>לימן</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>missile_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>גשר הזיו</t>
+          <t>צבעון</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>סער</t>
+          <t>סאסא</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>נהריה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>מצובה</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>אביבים</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>drone_only</t>
+          <t>missile_only</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -843,17 +843,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>לימן</t>
+          <t>באר שבע - צפון</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -863,25 +863,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>חוף אכזיב</t>
+          <t>בית קמה</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -891,25 +893,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>כרמים</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -919,25 +923,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>מיתר</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -947,25 +953,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>לקיה</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -975,25 +983,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>צבעון</t>
+          <t>באר שבע - מזרח</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1003,25 +1013,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>סאסא</t>
+          <t>להב</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1031,25 +1043,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>תל שבע</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1059,25 +1073,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>אשכולות</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1087,25 +1103,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>באר שבע - מערב</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1115,25 +1133,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>תארבין</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1143,25 +1163,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>סנסנה</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1171,15 +1193,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>כרמית</t>
+          <t>רהט</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1209,7 +1233,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>להב</t>
+          <t>כרמית</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1239,7 +1263,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>שגב שלום</t>
+          <t>אום בטין</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1269,7 +1293,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>באר שבע - מערב</t>
+          <t>חצרים</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1299,7 +1323,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>חורה</t>
+          <t>עומר</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1329,7 +1353,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>חצרים</t>
+          <t>באר שבע - דרום</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1359,7 +1383,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>עומר</t>
+          <t>שובל</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1389,7 +1413,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>אל סייד</t>
+          <t>להבים</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1419,7 +1443,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>סנסנה</t>
+          <t>משמר הנגב</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1449,7 +1473,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>אתר דודאים</t>
+          <t>אל סייד</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1479,7 +1503,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>גבעות בר</t>
+          <t>שגב שלום</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1539,7 +1563,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>רהט</t>
+          <t>אזור תעשייה עידן הנגב</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1569,7 +1593,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>באר שבע - צפון</t>
+          <t>אתר דודאים</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1599,7 +1623,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>באר שבע - מזרח</t>
+          <t>גבעות בר</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1629,7 +1653,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>אזור תעשייה עידן הנגב</t>
+          <t>חורה</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1659,7 +1683,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>בית קמה</t>
+          <t>דביר</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1689,17 +1713,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>אום בטין</t>
+          <t>אזור תעשייה נ.ע.מ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1719,17 +1743,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>תארבין</t>
+          <t>בטחה</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1749,17 +1773,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>תל שבע</t>
+          <t>שרשרת</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1779,17 +1803,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>להבים</t>
+          <t>שיבולים</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1809,17 +1833,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>שובל</t>
+          <t>שבי דרום</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1839,17 +1863,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>לקיה</t>
+          <t>יושיביה</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1869,17 +1893,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>מיתר</t>
+          <t>מבועים</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1899,17 +1923,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>אשכולות</t>
+          <t>פדויים</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1929,17 +1953,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>באר שבע - דרום</t>
+          <t>זרועה</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1959,17 +1983,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>כרמים</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1989,17 +2013,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>דביר</t>
+          <t>תפרח</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2019,17 +2043,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>משמר הנגב</t>
+          <t>גבולות</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2049,7 +2073,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>דורות</t>
+          <t>ניר עקיבא</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2079,7 +2103,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>תאשור</t>
+          <t>מסלול</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2109,7 +2133,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ברור חיל</t>
+          <t>פטיש</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2139,7 +2163,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>גבולות</t>
+          <t>קלחים</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2169,7 +2193,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>אשל הנשיא</t>
+          <t>דורות</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2199,7 +2223,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>שרשרת</t>
+          <t>שדה צבי</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2229,7 +2253,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>אזור תעשייה נ.ע.מ</t>
+          <t>ברור חיל</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2259,7 +2283,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>רנן</t>
+          <t>תאשור</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2289,7 +2313,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>שבי דרום</t>
+          <t>גילת</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2349,7 +2373,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>תדהר</t>
+          <t>אורים</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2409,7 +2433,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>בטחה</t>
+          <t>ניר משה</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2439,7 +2463,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>יושיביה</t>
+          <t>אשל הנשיא</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2469,7 +2493,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>בית הגדי</t>
+          <t>רנן</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2499,7 +2523,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ניר עקיבא</t>
+          <t>בית הגדי</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2529,7 +2553,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>תפרח</t>
+          <t>תדהר</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2559,7 +2583,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>אופקים</t>
+          <t>אשבול</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2619,7 +2643,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>אורים</t>
+          <t>רוחמה</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2649,7 +2673,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>שדה צבי</t>
+          <t>ברוש</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2679,17 +2703,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>גילת</t>
+          <t>כמהין</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2709,17 +2733,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ברוש</t>
+          <t>דימונה</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2739,17 +2763,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>קלחים</t>
+          <t>קדש ברנע</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2769,17 +2793,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ניר משה</t>
+          <t>שדה בוקר</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2799,17 +2823,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>זרועה</t>
+          <t>קסר א-סר</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2829,17 +2853,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>שיבולים</t>
+          <t>מרחב עם</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2859,17 +2883,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>פדויים</t>
+          <t>תל ערד</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2889,17 +2913,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>מבועים</t>
+          <t>סעווה</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2919,17 +2943,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>מסלול</t>
+          <t>ניצנה</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2949,17 +2973,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>רוחמה</t>
+          <t>עזוז</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2979,17 +3003,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>אשבול</t>
+          <t>כפר הנוקדים</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3009,17 +3033,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>פטיש</t>
+          <t>ואדי אל נעם דרום</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3039,7 +3063,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>מרעית</t>
+          <t>אל פורעה</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3069,7 +3093,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>אבו קרינאת</t>
+          <t>מרעית</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3099,7 +3123,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>אשלים</t>
+          <t>באר מילכה</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3129,7 +3153,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ערד</t>
+          <t>כסייפה</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3159,7 +3183,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>כסייפה</t>
+          <t>אשלים</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3189,7 +3213,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>שאנטי במדבר</t>
+          <t>ביר הדאג'</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3249,7 +3273,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>אל פורעה</t>
+          <t>אזור תעשייה רותם</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3279,7 +3303,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ניצנה</t>
+          <t>ערערה בנגב</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3309,7 +3333,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ואדי אל נעם דרום</t>
+          <t>ערד</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3339,7 +3363,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>באר מילכה</t>
+          <t>מדרשת בן גוריון</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3369,7 +3393,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ביר הדאג'</t>
+          <t>טללים</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3399,7 +3423,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ערערה בנגב</t>
+          <t>אבו תלול</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3429,7 +3453,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>כפר הנוקדים</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3459,7 +3483,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>עזוז</t>
+          <t>רביבים</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3489,7 +3513,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>טללים</t>
+          <t>שאנטי במדבר</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3519,7 +3543,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>מרחב עם</t>
+          <t>ירוחם</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3549,7 +3573,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>חירן</t>
+          <t>אבו קרינאת</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3579,7 +3603,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>מדרשת בן גוריון</t>
+          <t>רתמים</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3609,7 +3633,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>קדש ברנע</t>
+          <t>חירן</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3639,12 +3663,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>אבו תלול</t>
+          <t>אזור תעשייה דימונה</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>South Negev</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3669,17 +3693,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>שדה בוקר</t>
+          <t>חוות מנחם</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3693,23 +3717,23 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>אזור תעשייה רותם</t>
+          <t>מרחצאות עין גדי</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3723,23 +3747,23 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>דימונה</t>
+          <t>מלונות ים המלח מרכז</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3753,23 +3777,23 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ירוחם</t>
+          <t>עין בוקק</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3783,23 +3807,23 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>סעווה</t>
+          <t>עין תמר</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3813,23 +3837,23 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>כמהין</t>
+          <t>נווה זוהר</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3843,23 +3867,23 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>רביבים</t>
+          <t>בתי מלון ים המלח</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3873,23 +3897,23 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>תל ערד</t>
+          <t>עין גדי</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3903,23 +3927,23 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>קסר א-סר</t>
+          <t>מצפה מדרג</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3933,23 +3957,23 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>נאות הכיכר</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3963,23 +3987,23 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>רתמים</t>
+          <t>מצדה</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3993,23 +4017,23 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>300</v>
+        <v>420</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>אזור תעשייה דימונה</t>
+          <t>עידן</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>South Negev</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4019,22 +4043,20 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>מרחצאות עין גדי</t>
+          <t>עין חצבה</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4049,22 +4071,20 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>מצפה מדרג</t>
+          <t>חצבה</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4079,27 +4099,25 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>בתי מלון ים המלח</t>
+          <t>חוות דרומא</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4109,27 +4127,25 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>חוות מנחם</t>
+          <t>אשתמוע</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4139,27 +4155,25 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>עין גדי</t>
+          <t>מצפה יאיר</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4169,27 +4183,25 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>נווה זוהר</t>
+          <t>חוות מור ואברהם</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4199,27 +4211,25 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>מצדה</t>
+          <t>סוסיא הקדומה</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4229,27 +4239,25 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>נאות הכיכר</t>
+          <t>אביגיל</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4259,27 +4267,25 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>עין בוקק</t>
+          <t>חוות יויו</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4289,27 +4295,25 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F131" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>עין תמר</t>
+          <t>חוות טואמין</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4319,27 +4323,25 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F132" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>מלונות ים המלח מרכז</t>
+          <t>חוות טליה</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4349,27 +4351,25 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>420</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>עין חצבה</t>
+          <t>חוות מקנה יהודה</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4387,17 +4387,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>חצבה</t>
+          <t>אזור תעשייה מיתרים</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4415,17 +4415,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>עידן</t>
+          <t>בני אדם</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4443,12 +4443,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>חוות יויו</t>
+          <t>כרמל</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4471,12 +4471,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>חוות מור ואברהם</t>
+          <t>טנא עומרים</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>חוות טואמין</t>
+          <t>שני ליבנה</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4527,12 +4527,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>מצפה יאיר</t>
+          <t>הר עמשא</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4555,12 +4555,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>אביגיל</t>
+          <t>מעון</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4583,12 +4583,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>חוות דרומא</t>
+          <t>בית יתיר</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4611,12 +4611,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>חוות מקנה יהודה</t>
+          <t>סוסיא</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>אזור תעשייה מיתרים</t>
+          <t>שמעה</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4667,12 +4667,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>סוסיא הקדומה</t>
+          <t>עשהאל</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4695,17 +4695,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>אשתמוע</t>
+          <t>מתחם פי גלילות</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4715,25 +4715,27 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>חוות טליה</t>
+          <t>בת ים</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4743,25 +4745,27 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>בני אדם</t>
+          <t>קריית אונו</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4771,25 +4775,27 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>מעון</t>
+          <t>אור יהודה</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4799,25 +4805,27 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>בית יתיר</t>
+          <t>תל אביב - דרום העיר ויפו</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4827,25 +4835,27 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>שמעה</t>
+          <t>פתח תקווה</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4855,25 +4865,27 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>שני ליבנה</t>
+          <t>יהוד מונוסון</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4883,25 +4895,27 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>טנא עומרים</t>
+          <t>רמת השרון</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4911,25 +4925,27 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>כרמל</t>
+          <t>גבעת השלושה</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4939,25 +4955,27 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>סוסיא</t>
+          <t>הרצליה - מערב</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4967,25 +4985,27 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>עשהאל</t>
+          <t>תל אביב - מרכז העיר</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4995,25 +5015,27 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>הר עמשא</t>
+          <t>סביון</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Tel Aviv / Gush Dan</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5023,15 +5045,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>פתח תקווה</t>
+          <t>גני תקווה</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5061,7 +5085,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>בני ברק</t>
+          <t>מעש</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5091,7 +5115,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>מגשימים</t>
+          <t>מקווה ישראל</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5121,7 +5145,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>תל אביב - דרום העיר ויפו</t>
+          <t>גת רימון</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5151,7 +5175,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>בת ים</t>
+          <t>תל אביב - מזרח</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5181,7 +5205,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>הרצליה - מערב</t>
+          <t>בני ברק</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5211,7 +5235,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>מקווה ישראל</t>
+          <t>תל אביב - עבר הירקון</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5241,7 +5265,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>אזור</t>
+          <t>רמת גן - מערב</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5271,7 +5295,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>תל אביב - עבר הירקון</t>
+          <t>אזור</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5301,7 +5325,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>גני תקווה</t>
+          <t>כפר סירקין</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5331,7 +5355,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>גבעתיים</t>
+          <t>מתחם גלילות</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5361,7 +5385,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>כפר שמריהו</t>
+          <t>מגשימים</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5391,7 +5415,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>רמת גן - מערב</t>
+          <t>חולון</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5421,7 +5445,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>מעש</t>
+          <t>הרצליה - מרכז וגליל ים</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5451,7 +5475,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>מתחם גלילות</t>
+          <t>כפר שמריהו</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5481,7 +5505,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>כפר סירקין</t>
+          <t>גבעתיים</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5541,7 +5565,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>גבעת שמואל</t>
+          <t>רמת גן - מזרח</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5571,7 +5595,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>רמת גן - מזרח</t>
+          <t>גבעת שמואל</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5601,12 +5625,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>מתחם פי גלילות</t>
+          <t>מזור</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5631,12 +5655,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>אור יהודה</t>
+          <t>מודיעין מכבים רעות</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5661,12 +5685,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>סביון</t>
+          <t>חדיד</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5691,12 +5715,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>הרצליה - מרכז וגליל ים</t>
+          <t>נחלים</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5721,12 +5745,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>יהוד מונוסון</t>
+          <t>אלעד</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5751,12 +5775,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>תל אביב - מרכז העיר</t>
+          <t>כפר דניאל</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5781,12 +5805,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>חולון</t>
+          <t>גמזו</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5811,12 +5835,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>רמת השרון</t>
+          <t>מודיעין - ישפרו סנטר</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5841,12 +5865,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>גת רימון</t>
+          <t>מודיעין - ליגד סנטר</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5871,12 +5895,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>גבעת השלושה</t>
+          <t>מתתיהו</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5901,12 +5925,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>תל אביב - מזרח</t>
+          <t>שוהם</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5931,12 +5955,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>קריית אונו</t>
+          <t>כפר טרומן</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Yarkon</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5961,7 +5985,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>חדיד</t>
+          <t>טירת יהודה</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5991,7 +6015,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>אלעד</t>
+          <t>נחשונים</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6021,7 +6045,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>נחלים</t>
+          <t>חשמונאים</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6051,7 +6075,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>בני עטרות</t>
+          <t>בארות יצחק</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6081,7 +6105,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>עינת</t>
+          <t>מבוא חורון</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6111,7 +6135,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>מתתיהו</t>
+          <t>כפר האורנים</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6141,7 +6165,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>שוהם</t>
+          <t>מבוא מודיעים</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6171,7 +6195,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>מבוא מודיעים</t>
+          <t>ברקת</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6201,7 +6225,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>בארות יצחק</t>
+          <t>מודיעין עילית</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6231,7 +6255,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>מודיעין עילית</t>
+          <t>נופך</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6291,7 +6315,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>מודיעין - ליגד סנטר</t>
+          <t>כפר רות</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6321,7 +6345,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>מודיעין - ישפרו סנטר</t>
+          <t>שילת</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6381,7 +6405,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>גמזו</t>
+          <t>בני עטרות</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6411,7 +6435,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>נופך</t>
+          <t>בית נחמיה</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6441,7 +6465,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ברקת</t>
+          <t>ראש העין</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6471,7 +6495,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>נחשונים</t>
+          <t>איירפורט סיטי</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6501,7 +6525,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>מזור</t>
+          <t>בית עריף</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6531,7 +6555,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>בית עריף</t>
+          <t>רינתיה</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6561,7 +6585,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>טירת יהודה</t>
+          <t>אזור תעשייה אפק ולב הארץ</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6591,7 +6615,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>אזור תעשייה אפק ולב הארץ</t>
+          <t>עינת</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6621,7 +6645,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>בית נחמיה</t>
+          <t>נאות קדומים</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6651,17 +6675,17 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>שילת</t>
+          <t>כפר הס</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6681,17 +6705,17 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>איירפורט סיטי</t>
+          <t>עין החורש</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6711,17 +6735,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>כפר דניאל</t>
+          <t>חיבת ציון</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6741,17 +6765,17 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>חשמונאים</t>
+          <t>כפר ויתקין</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6771,17 +6795,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ראש העין</t>
+          <t>אבן יהודה</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6801,17 +6825,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>כפר רות</t>
+          <t>העוגן</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6831,17 +6855,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>מודיעין מכבים רעות</t>
+          <t>חרות</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6861,17 +6885,17 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>כפר טרומן</t>
+          <t>זמר</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6891,17 +6915,17 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>מבוא חורון</t>
+          <t>בצרה</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6921,17 +6945,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>נאות קדומים</t>
+          <t>כפר קאסם</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6951,17 +6975,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>כפר האורנים</t>
+          <t>אזור תעשייה כפר יונה</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6981,17 +7005,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>רינתיה</t>
+          <t>בני דרור</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Yarkon</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tel Aviv / Gush Dan</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -7011,7 +7035,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>בית יצחק - שער חפר</t>
+          <t>נווה ימין</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7041,7 +7065,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>כפר ברא</t>
+          <t>בת חפר</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7071,7 +7095,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>תחנת רכבת ראש העין</t>
+          <t>גן חיים</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7101,7 +7125,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>אזור תעשייה עמק חפר</t>
+          <t>ניר אליהו</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7131,7 +7155,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>צור משה</t>
+          <t>הדר עם</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7161,7 +7185,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>אמץ</t>
+          <t>בורגתה</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7191,7 +7215,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>בת חן</t>
+          <t>בית חרות</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7221,7 +7245,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>חופית</t>
+          <t>ביתן אהרן</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7251,7 +7275,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>אלקנה</t>
+          <t>רעננה</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7281,7 +7305,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>אחיטוב</t>
+          <t>עולש</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7311,7 +7335,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>רמות השבים</t>
+          <t>כפר ברא</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7341,7 +7365,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>חיבת ציון</t>
+          <t>צור משה</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7371,7 +7395,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>כוכב יאיר - צור יגאל</t>
+          <t>מרכז אזורי דרום השרון</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7401,7 +7425,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>מסוף אורנית</t>
+          <t>נווה ירק</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7431,7 +7455,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>רשפון</t>
+          <t>עדנים</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7461,7 +7485,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>בארותיים</t>
+          <t>רשפון</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7491,7 +7515,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>אלפי מנשה</t>
+          <t>אזור תעשייה עמק חפר</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7521,7 +7545,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>שדה ורבורג</t>
+          <t>סלעית</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7551,7 +7575,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ארסוף</t>
+          <t>עזריאל</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7581,7 +7605,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>תל יצחק</t>
+          <t>נתניה - מזרח</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7611,7 +7635,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>נעורים</t>
+          <t>תחנת רכבת ראש העין</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7641,7 +7665,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>עץ אפרים</t>
+          <t>אמץ</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7671,7 +7695,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ניצני עוז</t>
+          <t>חבצלת השרון וצוקי ים</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7701,7 +7725,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>שדי חמד</t>
+          <t>משמר השרון</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7731,7 +7755,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>גאולים</t>
+          <t>ינוב</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7761,7 +7785,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>מכמורת</t>
+          <t>קלנסווה</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7791,7 +7815,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>כפר מונש</t>
+          <t>אלקנה</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7821,7 +7845,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>רמת הכובש</t>
+          <t>מסוף אורנית</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7851,7 +7875,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>בית הלוי</t>
+          <t>כפר ידידיה</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7881,7 +7905,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>נתניה - מזרח</t>
+          <t>געש</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7911,7 +7935,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>גני עם</t>
+          <t>אורנית</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7941,7 +7965,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>צופים</t>
+          <t>חרב לאת</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7971,7 +7995,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>בחן</t>
+          <t>עץ אפרים</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8001,7 +8025,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>אורנית</t>
+          <t>שדי חמד</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8031,7 +8055,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>יד חנה</t>
+          <t>טייבה</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8061,7 +8085,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>אלישיב</t>
+          <t>גנות הדר</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8091,7 +8115,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>מתן</t>
+          <t>כפר חיים</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8121,7 +8145,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>כפר ויתקין</t>
+          <t>כפר יונה</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8151,7 +8175,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>שער אפרים</t>
+          <t>אחיטוב</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8181,7 +8205,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>פורת</t>
+          <t>נירית</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8211,7 +8235,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>אלישמע</t>
+          <t>כפר נטר</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8241,7 +8265,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>חבצלת השרון וצוקי ים</t>
+          <t>בני ציון</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8271,7 +8295,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>טייבה</t>
+          <t>גבעת שפירא</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8301,7 +8325,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>עזריאל</t>
+          <t>חניאל</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8331,7 +8355,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>בת חפר</t>
+          <t>פורת</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8361,7 +8385,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>נתניה - מערב</t>
+          <t>ירחיב</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8391,7 +8415,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>אבן יהודה</t>
+          <t>גן יאשיה</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8421,7 +8445,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>חורשים</t>
+          <t>הוד השרון</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8451,7 +8475,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>עין ורד</t>
+          <t>בחן</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8481,7 +8505,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>גבעת חיים מאוחד</t>
+          <t>אודים</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8511,7 +8535,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>בית ינאי</t>
+          <t>חגור</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8541,7 +8565,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>גאולי תימן</t>
+          <t>מתן</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8571,7 +8595,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>עין שריד</t>
+          <t>משמרת</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8601,7 +8625,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>בני ציון</t>
+          <t>אלישיב</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8631,7 +8655,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>גן יאשיה</t>
+          <t>עין ורד</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8661,7 +8685,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>העוגן</t>
+          <t>המרכז האקדמי רופין</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8691,7 +8715,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>כפר נטר</t>
+          <t>חגלה</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8721,7 +8745,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>כפר יונה</t>
+          <t>שושנת העמקים</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8751,7 +8775,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>גנות הדר</t>
+          <t>חורשים</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8781,7 +8805,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>הוד השרון</t>
+          <t>שערי תקווה</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8811,7 +8835,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>הדר עם</t>
+          <t>יד חנה</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8841,7 +8865,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>בית ברל</t>
+          <t>עין שריד</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8871,7 +8895,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>כפר עבודה</t>
+          <t>אלישמע</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8901,7 +8925,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>צור יצחק</t>
+          <t>גאולי תימן</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8931,7 +8955,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>חרב לאת</t>
+          <t>גני עם</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8961,7 +8985,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>גבעת שפירא</t>
+          <t>ג'לג'וליה</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8991,7 +9015,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>כפר סבא</t>
+          <t>גבעת חיים איחוד</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9021,7 +9045,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>המרכז האקדמי רופין</t>
+          <t>צופים</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9051,7 +9075,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>בית עלמין מורשה</t>
+          <t>צור יצחק</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9081,7 +9105,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>נווה ימין</t>
+          <t>אייל</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9111,7 +9135,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>פרדסיה</t>
+          <t>צופית</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9141,7 +9165,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>כפר ידידיה</t>
+          <t>חרוצים</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9171,7 +9195,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>זמר</t>
+          <t>תל יצחק</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9201,7 +9225,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ינוב</t>
+          <t>בית עלמין מורשה</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9231,7 +9255,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>תל מונד</t>
+          <t>טירה</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9291,7 +9315,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>אזור תעשייה כפר יונה</t>
+          <t>אלפי מנשה</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9321,7 +9345,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>נווה ירק</t>
+          <t>נתניה - מערב</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9351,7 +9375,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ירחיב</t>
+          <t>כפר סבא</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9381,7 +9405,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>בית חרות</t>
+          <t>בית ינאי</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9411,7 +9435,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>סלעית</t>
+          <t>שפיים</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9441,7 +9465,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>אייל</t>
+          <t>ירקונה</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9471,7 +9495,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>משמר השרון</t>
+          <t>בית הלוי</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9501,7 +9525,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>חרוצים</t>
+          <t>פרדסיה</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9531,7 +9555,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>צור נתן</t>
+          <t>מעברות</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9561,7 +9585,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>אודים</t>
+          <t>כוכב יאיר - צור יגאל</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9591,7 +9615,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ירקונה</t>
+          <t>אביחיל</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9651,7 +9675,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>עולש</t>
+          <t>מכון וינגייט</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9681,7 +9705,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>חגור</t>
+          <t>בית ברל</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9711,7 +9735,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>משמרת</t>
+          <t>תל מונד</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9741,7 +9765,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>המעפיל</t>
+          <t>ניצני עוז</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9771,7 +9795,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>בית יהושע</t>
+          <t>המעפיל</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9801,7 +9825,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>בורגתה</t>
+          <t>בית יצחק - שער חפר</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9831,7 +9855,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>גבעת חיים איחוד</t>
+          <t>גבעת חיים מאוחד</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9861,7 +9885,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>שושנת העמקים</t>
+          <t>קדימה צורן</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9891,7 +9915,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>נירית</t>
+          <t>ארסוף</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9921,7 +9945,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>עין החורש</t>
+          <t>בת חן</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9951,7 +9975,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>טירה</t>
+          <t>כפר מונש</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9981,7 +10005,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>קדימה צורן</t>
+          <t>כפר עבודה</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10011,7 +10035,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>יקום</t>
+          <t>תנובות</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10041,7 +10065,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>שערי תקווה</t>
+          <t>חופית</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10071,7 +10095,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ג'לג'וליה</t>
+          <t>גאולים</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10101,7 +10125,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>חניאל</t>
+          <t>בארותיים</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10131,7 +10155,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>צופית</t>
+          <t>בית יהושע</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10161,7 +10185,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>אביחיל</t>
+          <t>נורדיה</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10191,7 +10215,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>רעננה</t>
+          <t>שדה ורבורג</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10221,7 +10245,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>חגלה</t>
+          <t>צור נתן</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10251,7 +10275,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>נורדיה</t>
+          <t>רמת הכובש</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10281,7 +10305,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>בני דרור</t>
+          <t>מכמורת</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10311,7 +10335,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>כפר הס</t>
+          <t>יקום</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10341,7 +10365,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>תנובות</t>
+          <t>נעורים</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10371,7 +10395,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>מכון וינגייט</t>
+          <t>רמות השבים</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10401,7 +10425,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>כפר חיים</t>
+          <t>שער אפרים</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10431,17 +10455,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ניר אליהו</t>
+          <t>ענב</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -10461,17 +10485,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>עדנים</t>
+          <t>בית אריה</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -10491,17 +10515,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>חרות</t>
+          <t>חרמש דרום</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -10521,17 +10545,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ביתן אהרן</t>
+          <t>חוות מלכיאל</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -10551,17 +10575,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>געש</t>
+          <t>חוות נחל שילה</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -10581,17 +10605,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>בצרה</t>
+          <t>פדואל</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -10611,17 +10635,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>גן חיים</t>
+          <t>חוות אביה</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -10641,17 +10665,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>כפר קאסם</t>
+          <t>קידה</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -10671,17 +10695,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>קלנסווה</t>
+          <t>עופרים</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -10701,17 +10725,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>מרכז אזורי דרום השרון</t>
+          <t>חוות חנינא</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -10731,17 +10755,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>שפיים</t>
+          <t>נווה ארז</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -10761,17 +10785,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>מעברות</t>
+          <t>שדה אפרים</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Shomron</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -10791,7 +10815,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>מעלה לבונה</t>
+          <t>חוות עולם חסד</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10821,7 +10845,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>חוות חנינא</t>
+          <t>חוות אביחי</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10851,7 +10875,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>רחלים</t>
+          <t>עטרת</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -10881,7 +10905,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>חרשה</t>
+          <t>מעלה מכמש</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10911,7 +10935,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>נילי</t>
+          <t>כפר תפוח</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10941,7 +10965,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ברוכין</t>
+          <t>חרמש</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10971,7 +10995,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>שבי שומרון</t>
+          <t>החווה של זוהר</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11001,7 +11025,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>אזור תעשייה בראון</t>
+          <t>עמנואל</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11031,7 +11055,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>נווה צוף</t>
+          <t>תל ציון</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11061,7 +11085,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>עופרים</t>
+          <t>כוכב השחר</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -11091,7 +11115,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>אבני חפץ</t>
+          <t>עדי עד</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11121,7 +11145,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>חוות אל נווה</t>
+          <t>נופים</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11151,7 +11175,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>רימונים</t>
+          <t>חוות נחלת צבי</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11181,7 +11205,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ברקן</t>
+          <t>ברוכין</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -11211,7 +11235,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>נריה</t>
+          <t>קרני שומרון</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11241,7 +11265,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>מצפה דני</t>
+          <t>אזור תעשייה ברקן</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11271,7 +11295,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>יבוא דודי</t>
+          <t>חוות שחרית</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11301,7 +11325,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>יצהר</t>
+          <t>גופנה</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11331,7 +11355,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>גבע בנימין</t>
+          <t>עפרה</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -11361,7 +11385,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>עפרה</t>
+          <t>איתמר</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -11391,7 +11415,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>פדואל</t>
+          <t>גבעת פורת יוסף</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11421,7 +11445,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>עלי</t>
+          <t>חוות אלחי</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11451,7 +11475,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>שדה אפרים</t>
+          <t>עמיחי</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11481,7 +11505,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>גבעת אסף</t>
+          <t>מעלה לבונה</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11511,7 +11535,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>חוות גלעד</t>
+          <t>גבעת הראל</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11541,7 +11565,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>חוות שדה</t>
+          <t>אביתר</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11571,7 +11595,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>עטרת</t>
+          <t>אזור תעשייה אריאל</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11601,7 +11625,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>חוות נחל שילה</t>
+          <t>קדומים</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11631,7 +11655,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>חוות מלכיאל</t>
+          <t>ריחן</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11661,7 +11685,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>חומש</t>
+          <t>רמת מגרון</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11691,7 +11715,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>חוות נווה צוף</t>
+          <t>עלי</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11721,7 +11745,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>חיננית</t>
+          <t>חוות מגנזי</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11751,7 +11775,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>גבעת הרואה</t>
+          <t>רימונים</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11781,7 +11805,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>נווה ארז</t>
+          <t>חוות בניהו</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11811,7 +11835,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>תל ציון</t>
+          <t>פסגות</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11841,7 +11865,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>חוות בניהו</t>
+          <t>רחלים</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11871,7 +11895,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>גבעת פורת יוסף</t>
+          <t>טל מנשה</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11901,7 +11925,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>דולב</t>
+          <t>שילה</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11931,7 +11955,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>אזור תעשייה ברקן</t>
+          <t>חוות נוף אב"י</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -11961,7 +11985,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>טלמון</t>
+          <t>חוות צרידה</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11991,7 +12015,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>יקיר</t>
+          <t>חוות שדה</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12021,7 +12045,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>אחיה</t>
+          <t>שקד</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12051,7 +12075,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>חוות שוביאל</t>
+          <t>נופי נחמיה</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12081,7 +12105,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>חוות אביחי</t>
+          <t>גבעת אסף</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12111,7 +12135,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>חוות מרום שמואל</t>
+          <t>אזור תעשייה שער בנימין</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -12141,7 +12165,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>מבוא דותן</t>
+          <t>קריית נטפים</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -12171,7 +12195,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>חוות מגדלים</t>
+          <t>מצפה דני</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -12201,7 +12225,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>חוות צרידה</t>
+          <t>חוות נווה צוף</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -12231,7 +12255,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>גבעת הראל</t>
+          <t>שבות רחל</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12261,7 +12285,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>עלי זהב - לשם</t>
+          <t>חוות מעלה אהוביה</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12291,7 +12315,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>אעירה השחר</t>
+          <t>חוות שוביאל</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12321,7 +12345,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ריחן</t>
+          <t>ברקן</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -12351,7 +12375,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>רבבה</t>
+          <t>חומש</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -12381,7 +12405,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>חוות עולם חסד</t>
+          <t>טלמון</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12411,7 +12435,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>קידה</t>
+          <t>יצהר</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -12441,7 +12465,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>נופים</t>
+          <t>מבוא דותן</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -12471,7 +12495,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>כוכב יעקב</t>
+          <t>עלי זהב - לשם</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12501,7 +12525,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>עמנואל</t>
+          <t>חוות ינון</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12531,7 +12555,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>בית אל</t>
+          <t>כרם רעים</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12561,7 +12585,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>אזור תעשייה שחק</t>
+          <t>נווה צוף</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12591,7 +12615,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>נחליאל</t>
+          <t>גבע בנימין</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12621,7 +12645,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>חרמש דרום</t>
+          <t>בית אל</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12651,7 +12675,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>קדומים</t>
+          <t>דולב</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -12681,7 +12705,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>החווה של זוהר</t>
+          <t>חרשה</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -12711,7 +12735,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>מגדלים</t>
+          <t>הר ברכה</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -12741,7 +12765,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ענב</t>
+          <t>חוות מגדלים</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -12771,7 +12795,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>מגרון</t>
+          <t>אזור תעשייה שחק</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12801,7 +12825,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>מעלה מכמש</t>
+          <t>שבי שומרון</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12831,7 +12855,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>עמיחי</t>
+          <t>בית חורון</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12861,7 +12885,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>נעלה</t>
+          <t>חוות מרום שמואל</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -12891,7 +12915,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>מכינת אלישע</t>
+          <t>נריה</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -12921,7 +12945,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>רמת מגרון</t>
+          <t>נעלה</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -12951,7 +12975,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>חוות מגנזי</t>
+          <t>חיננית</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -12981,7 +13005,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>שבות רחל</t>
+          <t>רבבה</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -13011,7 +13035,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>חוות אלחי</t>
+          <t>אריאל</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13041,7 +13065,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>עדי עד</t>
+          <t>יקיר</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13071,7 +13095,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>שילה</t>
+          <t>אזור תעשייה בראון</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13101,7 +13125,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>חוות מעלה אהוביה</t>
+          <t>חוות גלעד</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13131,7 +13155,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>נופי נחמיה</t>
+          <t>אחיה</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -13161,7 +13185,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>כפר תפוח</t>
+          <t>מגדלים</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -13191,7 +13215,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>גופנה</t>
+          <t>אבני חפץ</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13221,7 +13245,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>קרני שומרון</t>
+          <t>חוות אל נווה</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13251,7 +13275,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>חרמש</t>
+          <t>יבוא דודי</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -13281,7 +13305,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>כוכב השחר</t>
+          <t>מגרון</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13311,7 +13335,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>חוות נחלת צבי</t>
+          <t>חוות יאיר</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -13341,7 +13365,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>חוות אביה</t>
+          <t>גבעת הרואה</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -13371,7 +13395,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>כרם רעים</t>
+          <t>דורות עילית</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -13401,7 +13425,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>אריאל</t>
+          <t>נחליאל</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -13431,7 +13455,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>חוות שחרית</t>
+          <t>נילי</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13461,7 +13485,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>אביתר</t>
+          <t>אעירה השחר</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -13491,7 +13515,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>טל מנשה</t>
+          <t>כוכב יעקב</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -13521,7 +13545,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>בית חורון</t>
+          <t>מכינת אלישע</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -13551,7 +13575,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>איתמר</t>
+          <t>אלון מורה</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13581,17 +13605,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>חוות ינון</t>
+          <t>אש קודש</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>Bika'a</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -13601,27 +13625,25 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F443" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>שקד</t>
+          <t>ניר צבי</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -13641,17 +13663,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>פסגות</t>
+          <t>בית דגן</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -13671,17 +13693,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>דורות עילית</t>
+          <t>אזור תעשייה גדרה</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -13701,17 +13723,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>הר ברכה</t>
+          <t>משמר איילון</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -13731,17 +13753,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>קריית נטפים</t>
+          <t>גני יוחנן</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -13761,17 +13783,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>חוות נוף אב"י</t>
+          <t>תעשיון צריפין</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -13791,17 +13813,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>בית אריה</t>
+          <t>יגל</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -13821,17 +13843,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>חוות יאיר</t>
+          <t>גזר</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -13851,17 +13873,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>אלון מורה</t>
+          <t>אחיסמך</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -13881,17 +13903,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער בנימין</t>
+          <t>גנות</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -13911,17 +13933,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>אזור תעשייה אריאל</t>
+          <t>בית חשמונאי</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Shomron</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -13941,17 +13963,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>אש קודש</t>
+          <t>גן שלמה</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Bika'a</t>
+          <t>HaShfela</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Sharon / Shephelah</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -13961,15 +13983,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>גינתון</t>
+          <t>נצר חזני</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -13999,7 +14023,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>אחיעזר</t>
+          <t>גינתון</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -14029,7 +14053,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>בית חשמונאי</t>
+          <t>בית חנן</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -14059,7 +14083,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ראשון לציון - מערב</t>
+          <t>בן שמן</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14089,7 +14113,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>גנות</t>
+          <t>כפר נוער בן שמן</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -14119,7 +14143,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ראשון לציון - מזרח</t>
+          <t>רמות מאיר</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -14149,7 +14173,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>בית חנן</t>
+          <t>פתחיה</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -14179,7 +14203,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>לוד</t>
+          <t>כרמי יוסף</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -14209,7 +14233,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>יסודות</t>
+          <t>אזור תעשייה נשר - רמלה</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -14239,7 +14263,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>מזכרת בתיה</t>
+          <t>פארק תעשיות פלמחים</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -14269,7 +14293,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>פדיה</t>
+          <t>אירוס</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -14299,7 +14323,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>סתריה</t>
+          <t>יציץ</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -14329,7 +14353,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>גן שורק</t>
+          <t>חולדה</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -14359,7 +14383,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>משמר השבעה</t>
+          <t>לוד</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -14389,7 +14413,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ניר צבי</t>
+          <t>סתריה</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -14419,7 +14443,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>ישרש</t>
+          <t>קריית עקרון</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -14449,7 +14473,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>חולדה</t>
+          <t>נטעים</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14479,7 +14503,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>מצליח</t>
+          <t>עזריה</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -14509,7 +14533,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>אזור תעשייה גדרה</t>
+          <t>משמר דוד</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -14539,7 +14563,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>צפריה</t>
+          <t>פדיה</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -14569,7 +14593,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>רמות מאיר</t>
+          <t>גיבתון</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14599,7 +14623,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>גיבתון</t>
+          <t>עיינות</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -14629,7 +14653,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>משמר איילון</t>
+          <t>ראשון לציון - מזרח</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -14659,7 +14683,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>נצר חזני</t>
+          <t>רחובות</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -14689,7 +14713,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>אזור תעשייה נשר - רמלה</t>
+          <t>נס ציונה</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -14719,7 +14743,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>קריית עקרון</t>
+          <t>בית עוזיאל</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -14749,7 +14773,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>תעשיון צריפין</t>
+          <t>חמד</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -14779,7 +14803,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>כפר נוער בן שמן</t>
+          <t>באר יעקב</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -14809,7 +14833,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>בית דגן</t>
+          <t>ישרש</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -14839,7 +14863,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>רמלה</t>
+          <t>כפר שמואל</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -14869,7 +14893,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>גני הדר</t>
+          <t>מזכרת בתיה</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -14899,7 +14923,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>פתחיה</t>
+          <t>גן שורק</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -14929,7 +14953,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>גאליה</t>
+          <t>רמלה</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -14959,7 +14983,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>בית עובד</t>
+          <t>גני הדר</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -14989,7 +15013,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>בן שמן</t>
+          <t>אחיעזר</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -15019,7 +15043,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>נס ציונה</t>
+          <t>יסודות</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -15049,7 +15073,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>רחובות</t>
+          <t>צפריה</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -15079,7 +15103,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>כפר בן נון</t>
+          <t>ראשון לציון - מערב</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -15109,7 +15133,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>זיתן</t>
+          <t>גאליה</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15139,7 +15163,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>באר יעקב</t>
+          <t>משמר השבעה</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -15169,7 +15193,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>אחיסמך</t>
+          <t>זיתן</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -15199,7 +15223,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>נען</t>
+          <t>כפר בן נון</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -15229,7 +15253,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>גני יוחנן</t>
+          <t>בית עובד</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -15259,7 +15283,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>עזריה</t>
+          <t>נען</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -15289,7 +15313,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>גזר</t>
+          <t>מצליח</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -15349,12 +15373,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>יציץ</t>
+          <t>רבדים</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -15373,18 +15397,18 @@
         </is>
       </c>
       <c r="F502" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>יגל</t>
+          <t>סגולה</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -15403,18 +15427,18 @@
         </is>
       </c>
       <c r="F503" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>כפר שמואל</t>
+          <t>נווה מבטח</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -15433,18 +15457,18 @@
         </is>
       </c>
       <c r="F504" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>חמד</t>
+          <t>גדרה</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -15463,18 +15487,18 @@
         </is>
       </c>
       <c r="F505" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>אירוס</t>
+          <t>פלמחים</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -15493,18 +15517,18 @@
         </is>
       </c>
       <c r="F506" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>נטעים</t>
+          <t>איתן</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -15523,18 +15547,18 @@
         </is>
       </c>
       <c r="F507" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>כרמי יוסף</t>
+          <t>גבעת וושינגטון</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -15553,18 +15577,18 @@
         </is>
       </c>
       <c r="F508" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>פארק תעשיות פלמחים</t>
+          <t>קבוצת יבנה</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -15583,18 +15607,18 @@
         </is>
       </c>
       <c r="F509" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>עיינות</t>
+          <t>קריית מלאכי</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -15613,18 +15637,18 @@
         </is>
       </c>
       <c r="F510" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>משמר דוד</t>
+          <t>בית עזרא</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -15643,18 +15667,18 @@
         </is>
       </c>
       <c r="F511" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>גן שלמה</t>
+          <t>ביצרון</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -15673,18 +15697,18 @@
         </is>
       </c>
       <c r="F512" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>בית עוזיאל</t>
+          <t>ורדון</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>HaShfela</t>
+          <t>Lachish</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -15703,13 +15727,13 @@
         </is>
       </c>
       <c r="F513" t="n">
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>יד בנימין</t>
+          <t>ניר בנים</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -15739,7 +15763,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>בניה</t>
+          <t>אשדוד - איזור תעשייה צפוני</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -15769,7 +15793,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>מרכז שפירא</t>
+          <t>יבנה</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -15799,7 +15823,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>לכיש</t>
+          <t>שדה משה</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -15829,7 +15853,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>סגולה</t>
+          <t>גן הדרום</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -15859,7 +15883,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>נגבה</t>
+          <t>זוהר</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -15889,7 +15913,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>שדמה</t>
+          <t>כרם ביבנה</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -15919,7 +15943,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>נוגה</t>
+          <t>אבן שמואל</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -15949,7 +15973,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>רווחה</t>
+          <t>אביגדור</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -15979,7 +16003,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>ינון</t>
+          <t>גבעת ברנר</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -16009,7 +16033,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>נחלה</t>
+          <t>רווחה</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -16039,7 +16063,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>קוממיות</t>
+          <t>זבדיאל</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -16069,7 +16093,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>חפץ חיים</t>
+          <t>מרכז שפירא</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -16099,7 +16123,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>אזור תעשייה באר טוביה</t>
+          <t>תחנת רכבת קריית מלאכי - יואב</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -16129,7 +16153,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>זרחיה</t>
+          <t>אזור תעשייה עד הלום</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -16159,7 +16183,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>קדרון</t>
+          <t>אחווה</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -16189,7 +16213,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>יבנה</t>
+          <t>נהורה</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -16219,7 +16243,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>שדה יואב</t>
+          <t>יד בנימין</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -16249,7 +16273,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>שדה עוזיהו</t>
+          <t>כפר הנגיד</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -16279,7 +16303,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>ביצרון</t>
+          <t>כנות</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -16309,7 +16333,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>גבעת וושינגטון</t>
+          <t>אמונים</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -16339,7 +16363,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>חצב</t>
+          <t>אזור תעשייה רבדים</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -16369,7 +16393,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>מנוחה</t>
+          <t>נועם</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -16399,7 +16423,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>אזור תעשייה תימורים</t>
+          <t>חפץ חיים</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -16429,7 +16453,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>שלווה</t>
+          <t>גן יבנה</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -16459,7 +16483,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>בן זכאי</t>
+          <t>אזור תעשייה תימורים</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -16489,7 +16513,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>משגב דב</t>
+          <t>בני דרום</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -16519,7 +16543,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>תימורים</t>
+          <t>אזור תעשייה קריית גת</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -16549,7 +16573,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>בית גמליאל</t>
+          <t>נגבה</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -16579,7 +16603,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>בני דרום</t>
+          <t>לכיש</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -16609,7 +16633,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>משואות יצחק</t>
+          <t>בית גמליאל</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -16639,7 +16663,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>כרם ביבנה</t>
+          <t>שפיר</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -16669,7 +16693,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>כפר ורבורג</t>
+          <t>ערוגות</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -16699,7 +16723,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>כפר מרדכי</t>
+          <t>עוזה</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -16729,7 +16753,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>גן הדרום</t>
+          <t>אל עזי</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -16759,7 +16783,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>בית חלקיה</t>
+          <t>משגב דב</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -16789,7 +16813,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>אביגדור</t>
+          <t>גת</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -16819,7 +16843,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>בית עזרא</t>
+          <t>שדה יואב</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -16849,7 +16873,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>שפיר</t>
+          <t>תלמי יחיאל</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -16879,7 +16903,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>אזור תעשייה עד הלום</t>
+          <t>נוגה</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -16909,7 +16933,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>אורות</t>
+          <t>עזריקם</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -16939,7 +16963,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>עוזה</t>
+          <t>אורות</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -16969,7 +16993,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>מישר</t>
+          <t>אזור תעשייה באר טוביה</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -16999,7 +17023,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>ורדון</t>
+          <t>שדמה</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -17029,7 +17053,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>אחווה</t>
+          <t>שחר</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -17059,7 +17083,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>נווה מבטח</t>
+          <t>מישר</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -17089,7 +17113,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>עזריקם</t>
+          <t>בניה</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -17119,7 +17143,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>כפר אחים</t>
+          <t>שתולים</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -17149,7 +17173,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>גבעת ברנר</t>
+          <t>פארק תעשייה ראם</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -17179,7 +17203,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>עזר</t>
+          <t>תלמים</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -17209,7 +17233,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>גבעתי</t>
+          <t>אלומה</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -17239,7 +17263,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>שדה משה</t>
+          <t>שלווה</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -17269,7 +17293,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>קריית מלאכי</t>
+          <t>קדמה</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -17299,7 +17323,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>קבוצת יבנה</t>
+          <t>עזר</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -17329,7 +17353,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>שתולים</t>
+          <t>חצב</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17359,7 +17383,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>תלמים</t>
+          <t>מתחם בני דרום</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -17389,7 +17413,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>אלומה</t>
+          <t>כפר ורבורג</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17419,7 +17443,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית גת</t>
+          <t>תימורים</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -17449,7 +17473,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>אחוזם</t>
+          <t>עוצם</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -17479,7 +17503,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>עשרת</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -17509,7 +17533,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>תחנת רכבת קריית מלאכי - יואב</t>
+          <t>בית אלעזרי</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -17539,7 +17563,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>זוהר</t>
+          <t>בן זכאי</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -17569,7 +17593,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>איתן</t>
+          <t>באר טוביה</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -17599,7 +17623,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>כפר הנגיד</t>
+          <t>שדה דוד</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -17629,7 +17653,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>גן יבנה</t>
+          <t>אחוזם</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -17659,7 +17683,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>עוצם</t>
+          <t>גבעתי</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -17689,7 +17713,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>נהורה</t>
+          <t>מנוחה</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -17719,7 +17743,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>כנות</t>
+          <t>משואות יצחק</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -17749,7 +17773,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>אזור תעשייה כנות</t>
+          <t>בני ראם</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -17779,7 +17803,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>יד נתן</t>
+          <t>קוממיות</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -17809,7 +17833,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>גדרה</t>
+          <t>נחלה</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -17839,7 +17863,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>פלמחים</t>
+          <t>ינון</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -17869,7 +17893,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>נועם</t>
+          <t>חצור</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -17899,7 +17923,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>עין צורים</t>
+          <t>יד נתן</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -17929,7 +17953,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ניר גלים</t>
+          <t>קדרון</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -17959,7 +17983,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>שדה דוד</t>
+          <t>זרחיה</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -17989,7 +18013,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>אשדוד - איזור תעשייה צפוני</t>
+          <t>ניר גלים</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18019,7 +18043,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>רבדים</t>
+          <t>כפר אחים</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18049,7 +18073,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>זבדיאל</t>
+          <t>כפר מרדכי</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18079,7 +18103,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>חצור</t>
+          <t>עין צורים</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18109,7 +18133,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>אמונים</t>
+          <t>בית חלקיה</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18139,7 +18163,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>כפר אביב</t>
+          <t>מעון צופיה</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18169,7 +18193,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>פארק תעשייה ראם</t>
+          <t>גני טל</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18199,7 +18223,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>מעון צופיה</t>
+          <t>כפר אביב</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18229,7 +18253,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>אל עזי</t>
+          <t>אזור תעשייה כנות</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18259,7 +18283,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>ערוגות</t>
+          <t>שדה עוזיהו</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18289,17 +18313,17 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>קדמה</t>
+          <t>גבעת ישעיהו</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -18309,27 +18333,25 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F600" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>באר טוביה</t>
+          <t>נווה שלום</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -18339,27 +18361,25 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F601" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>אזור תעשייה רבדים</t>
+          <t>זנוח</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -18369,27 +18389,25 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F602" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>בית אלעזרי</t>
+          <t>שורש</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -18399,27 +18417,25 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F603" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>תלמי יחיאל</t>
+          <t>כפר זוהרים</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -18429,27 +18445,25 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F604" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>אבן שמואל</t>
+          <t>גפן</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -18459,27 +18473,25 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F605" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>גת</t>
+          <t>בית נקופה</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -18489,27 +18501,25 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F606" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>גני טל</t>
+          <t>גבעות עדן</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -18519,27 +18529,25 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F607" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>בני ראם</t>
+          <t>מבוא ביתר</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -18549,27 +18557,25 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F608" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>ניר בנים</t>
+          <t>צפרירים</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -18579,27 +18585,25 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F609" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>מתחם בני דרום</t>
+          <t>הראל</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -18609,27 +18613,25 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F610" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>עשרת</t>
+          <t>טל שחר</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Lachish</t>
+          <t>Judea Foothills</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Sharon / Shephelah</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -18639,17 +18641,15 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F611" t="n">
-        <v>180</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>עגור</t>
+          <t>צובה</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -18677,7 +18677,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>בית מאיר</t>
+          <t>גלאון</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -18705,7 +18705,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>רמת רזיאל</t>
+          <t>עגור</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -18733,7 +18733,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>בית ניר</t>
+          <t>ישעי</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -18761,7 +18761,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>אזור תעשייה ברוש</t>
+          <t>נחם</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -18789,7 +18789,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>הר אדר</t>
+          <t>אביעזר</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -18817,7 +18817,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>אביעזר</t>
+          <t>מטע</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -18845,7 +18845,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>כסלון</t>
+          <t>כפר מנחם</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -18873,7 +18873,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>גלאון</t>
+          <t>נחושה</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -18901,7 +18901,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>זכריה</t>
+          <t>יד השמונה</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -18929,7 +18929,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>נווה שלום</t>
+          <t>שריגים - לי-און</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -18957,7 +18957,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>בית נקופה</t>
+          <t>תעוז</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -18985,7 +18985,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>נחשון</t>
+          <t>רטורנו - גבעת שמש</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19013,7 +19013,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>גבעת יערים</t>
+          <t>תרום</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19041,7 +19041,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>צור הדסה</t>
+          <t>צרעה</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19069,7 +19069,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>שריגים - לי-און</t>
+          <t>גבעת יערים</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19097,7 +19097,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>צלפון</t>
+          <t>תירוש</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19125,7 +19125,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>נחושה</t>
+          <t>מחסיה</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19153,7 +19153,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>תעוז</t>
+          <t>בית מאיר</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19181,7 +19181,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>מסילת ציון</t>
+          <t>הר אדר</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -19209,7 +19209,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>תרום</t>
+          <t>בית שמש</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19237,7 +19237,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>יד השמונה</t>
+          <t>אדרת</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19265,7 +19265,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>קריית ענבים</t>
+          <t>נטף</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -19293,7 +19293,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>בר גיורא</t>
+          <t>זכריה</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19321,7 +19321,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>נטף</t>
+          <t>בקוע</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19349,7 +19349,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>בקוע</t>
+          <t>כפר הנוער קריית יערים</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19377,7 +19377,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>נווה מיכאל - רוגלית</t>
+          <t>צלפון</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -19405,7 +19405,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>תירוש</t>
+          <t>עין נקובא</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19433,7 +19433,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>כפר זוהרים</t>
+          <t>בית גוברין</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19461,7 +19461,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>זנוח</t>
+          <t>קריית יערים</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19489,7 +19489,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>מטע</t>
+          <t>כפר אוריה</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -19517,7 +19517,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>צרעה</t>
+          <t>כסלון</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -19545,7 +19545,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>בית גוברין</t>
+          <t>עין ראפה</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19573,7 +19573,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>עין נקובא</t>
+          <t>צור הדסה</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19601,7 +19601,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>אבו גוש</t>
+          <t>שואבה</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19629,7 +19629,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>בית שמש</t>
+          <t>אזור תעשייה ברוש</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -19657,7 +19657,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>מעלה החמישה</t>
+          <t>אשתאול</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19685,7 +19685,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>נחם</t>
+          <t>בית ניר</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19713,7 +19713,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>כפר מנחם</t>
+          <t>נחשון</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19741,7 +19741,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>מבוא ביתר</t>
+          <t>אבו גוש</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19769,7 +19769,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>לוזית</t>
+          <t>מסילת ציון</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -19797,7 +19797,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>אשתאול</t>
+          <t>לטרון</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -19825,7 +19825,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>אדרת</t>
+          <t>נס הרים</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -19853,7 +19853,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>גיזו</t>
+          <t>בר גיורא</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -19881,7 +19881,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>גבעת ישעיהו</t>
+          <t>רמת רזיאל</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -19909,7 +19909,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>אזור תעשייה הר טוב - צרעה</t>
+          <t>שדות מיכה</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -19937,7 +19937,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>עין ראפה</t>
+          <t>אזור תעשייה הר טוב - צרעה</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -19965,7 +19965,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>גפן</t>
+          <t>גיזו</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -19993,7 +19993,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>נווה אילן</t>
+          <t>נווה מיכאל - רוגלית</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -20021,7 +20021,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>קריית יערים</t>
+          <t>קריית ענבים</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -20049,7 +20049,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>צובה</t>
+          <t>לוזית</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -20077,7 +20077,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>מיני ישראל - נחשון</t>
+          <t>נווה אילן</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -20105,7 +20105,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>לטרון</t>
+          <t>מיני ישראל - נחשון</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -20133,7 +20133,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>שדות מיכה</t>
+          <t>מעלה החמישה</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -20157,342 +20157,6 @@
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
-        <is>
-          <t>נס הרים</t>
-        </is>
-      </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D666" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E666" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F666" t="inlineStr"/>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
-        <is>
-          <t>צפרירים</t>
-        </is>
-      </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E667" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F667" t="inlineStr"/>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
-        <is>
-          <t>רטורנו - גבעת שמש</t>
-        </is>
-      </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E668" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F668" t="inlineStr"/>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
-        <is>
-          <t>מחסיה</t>
-        </is>
-      </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D669" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E669" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F669" t="inlineStr"/>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>גבעות עדן</t>
-        </is>
-      </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D670" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F670" t="inlineStr"/>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>טל שחר</t>
-        </is>
-      </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F671" t="inlineStr"/>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>כפר הנוער קריית יערים</t>
-        </is>
-      </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F672" t="inlineStr"/>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>הראל</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D673" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E673" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F673" t="inlineStr"/>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>שואבה</t>
-        </is>
-      </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D674" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F674" t="inlineStr"/>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>ישעי</t>
-        </is>
-      </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F675" t="inlineStr"/>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>שורש</t>
-        </is>
-      </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F676" t="inlineStr"/>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>כפר אוריה</t>
-        </is>
-      </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>Judea Foothills</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
-        <is>
-          <t>West Bank</t>
-        </is>
-      </c>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F677" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F664"/>
+  <dimension ref="A1:F668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,27 +451,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>חוות מור ואברהם</t>
+          <t>ערב אל עראמשה</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pre_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -479,27 +479,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>חוות מקנה יהודה</t>
+          <t>חניתה</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>pre_only</t>
+          <t>drone_only</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -507,17 +507,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>אזור תעשייה מיתרים</t>
+          <t>מרגליות</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -527,25 +527,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>חוות טליה</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -555,25 +557,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>חוות טואמין</t>
+          <t>אביבים</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -583,25 +587,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>חוות יויו</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -611,25 +617,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>מצפה יאיר</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -639,25 +647,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>סוסיא הקדומה</t>
+          <t>להבות הבשן</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -667,25 +677,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>אביגיל</t>
+          <t>חניתה</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -695,25 +707,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>חוות דרומא</t>
+          <t>חוף אכזיב</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -723,25 +737,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>אשתמוע</t>
+          <t>חורפיש</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yehuda</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>West Bank</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -751,15 +767,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ערב אל עראמשה</t>
+          <t>סאסא</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -774,20 +792,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>חניתה</t>
+          <t>בית העלמין החדש נהריה</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -802,20 +822,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>דישון</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -845,7 +867,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>יפתח</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -875,7 +897,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>שתולה</t>
+          <t>רמות נפתלי</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -905,7 +927,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ג'ש - גוש חלב</t>
+          <t>אבן מנחם</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -935,7 +957,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>עבדון</t>
+          <t>אלקוש</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -965,7 +987,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>חוף אכזיב</t>
+          <t>פקיעין</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -995,7 +1017,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>בית העלמין החדש נהריה</t>
+          <t>עבדון</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1025,7 +1047,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>בן עמי</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1055,7 +1077,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>גורנות הגליל</t>
+          <t>נאות מרדכי</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1085,7 +1107,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>שומרה</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1115,7 +1137,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>אדמית</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1145,7 +1167,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>שלומי</t>
+          <t>ריחאנייה</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1175,7 +1197,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>שאר ישוב</t>
+          <t>ע'ג'ר</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1205,7 +1227,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>גשר הזיו</t>
+          <t>קיבוץ דן</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1235,7 +1257,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>כפר סאלד</t>
+          <t>יחיעם</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1265,7 +1287,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>אזור תעשייה רמת דלתון</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1295,7 +1317,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>מעונה</t>
+          <t>עברון</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1325,7 +1347,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>פסוטה</t>
+          <t>הגושרים</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1355,7 +1377,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>נהריה</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1385,7 +1407,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>אלקוש</t>
+          <t>נטועה</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1415,7 +1437,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>מלכיה</t>
+          <t>עלמה</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1445,7 +1467,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ברעם</t>
+          <t>כפר בלום</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1475,7 +1497,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>חורפיש</t>
+          <t>מעלות תרשיחא</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1505,7 +1527,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>קיבוץ דן</t>
+          <t>שדה נחמיה</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1535,7 +1557,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>מתת</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1565,7 +1587,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>מנות</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1595,7 +1617,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>כרם בן זמרה</t>
+          <t>שמיר</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1625,7 +1647,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>נווה זיו</t>
+          <t>מנרה</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1655,7 +1677,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>אילון</t>
+          <t>דישון</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1685,7 +1707,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>הילה</t>
+          <t>דלתון</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1715,7 +1737,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>עמיר</t>
+          <t>כרם בן זמרה</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1745,7 +1767,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>פקיעין החדשה</t>
+          <t>מכמנים - כמאנה מערבית</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1775,7 +1797,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>אדמית</t>
+          <t>פקיעין החדשה</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1805,7 +1827,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>זרעית</t>
+          <t>הילה</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1835,7 +1857,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>דפנה</t>
+          <t>כפר ורדים</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1865,7 +1887,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>להבות הבשן</t>
+          <t>לב החולה</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1895,7 +1917,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>אבירים</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1925,7 +1947,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>מעלות תרשיחא</t>
+          <t>מצובה</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1955,7 +1977,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>דלתון</t>
+          <t>שלומי</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1985,7 +2007,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2015,7 +2037,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>סער</t>
+          <t>שאר ישוב</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2045,7 +2067,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>עין יעקב</t>
+          <t>עמיר</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2075,7 +2097,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2105,7 +2127,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>גונן</t>
+          <t>צוריאל</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2135,7 +2157,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>שומרה</t>
+          <t>גשר הזיו</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2165,7 +2187,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>כברי</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2195,7 +2217,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>שמיר</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2225,7 +2247,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>בן עמי</t>
+          <t>אילון</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2255,7 +2277,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>מנרה</t>
+          <t>עין יעקב</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2285,7 +2307,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>אבירים</t>
+          <t>געתון</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2315,7 +2337,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ע'ג'ר</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2345,7 +2367,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>עברון</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2375,7 +2397,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>אביבים</t>
+          <t>גורן</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2405,7 +2427,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>יחיעם</t>
+          <t>מעיליא</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2435,7 +2457,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>נווה זיו</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2465,7 +2487,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>נטועה</t>
+          <t>כברי</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2495,7 +2517,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>כפר בלום</t>
+          <t>שתולה</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2525,7 +2547,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>חניתה</t>
+          <t>צבעון</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2555,7 +2577,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>רמות נפתלי</t>
+          <t>זרעית</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2585,7 +2607,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>מכמנים - כמאנה מערבית</t>
+          <t>בית הלל</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2615,7 +2637,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>נהריה</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2645,7 +2667,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>שניר</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2675,7 +2697,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>יערה</t>
+          <t>ברעם</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2705,7 +2727,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>בצת</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2735,7 +2757,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>אבן מנחם</t>
+          <t>שניר</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2765,7 +2787,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>געתון</t>
+          <t>לימן</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2795,7 +2817,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>עלמה</t>
+          <t>כפר סאלד</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2825,7 +2847,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>חוסן</t>
+          <t>בית ספר שדה מירון</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2855,7 +2877,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>צבעון</t>
+          <t>מנות</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2885,7 +2907,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>גורן</t>
+          <t>ערב אל עראמשה</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2915,7 +2937,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>כפר ורדים</t>
+          <t>פסוטה</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2945,7 +2967,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>סאסא</t>
+          <t>חוסן</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2975,7 +2997,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>צוריאל</t>
+          <t>מלכיה</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3005,7 +3027,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>מעיליא</t>
+          <t>מרכז אזורי מבואות חרמון</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3035,7 +3057,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>לב החולה</t>
+          <t>מעונה</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3065,7 +3087,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>שדה נחמיה</t>
+          <t>גורנות הגליל</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3095,7 +3117,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>נאות מרדכי</t>
+          <t>סער</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3125,7 +3147,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ערב אל עראמשה</t>
+          <t>דפנה</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3155,7 +3177,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>מרכז אזורי מבואות חרמון</t>
+          <t>ג'ש - גוש חלב</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3185,7 +3207,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>לימן</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3205,17 +3227,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>יפתח</t>
+          <t>להבות הבשן</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3235,17 +3255,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>פקיעין</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3265,17 +3283,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>מרגליות</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3295,17 +3311,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3325,17 +3339,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>מצובה</t>
+          <t>בצת</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3355,17 +3367,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>בית הלל</t>
+          <t>כפר סאלד</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3385,27 +3395,25 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ריחאנייה</t>
+          <t>דימונה</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3419,23 +3427,23 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>אזור תעשייה רמת דלתון</t>
+          <t>טללים</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3449,23 +3457,23 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>בית ספר שדה מירון</t>
+          <t>עזוז</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3479,23 +3487,23 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>מתת</t>
+          <t>ניצנה</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3509,23 +3517,23 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>מדרשת בן גוריון</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3535,25 +3543,27 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>שאנטי במדבר</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3563,25 +3573,27 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>קסר א-סר</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3591,25 +3603,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>רביבים</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Confrontation Line</t>
+          <t>Southern Negev</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3619,15 +3633,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>drone_only</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>שאנטי במדבר</t>
+          <t>אבו תלול</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3657,7 +3673,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>רביבים</t>
+          <t>רתמים</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3687,7 +3703,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>אשלים</t>
+          <t>מרחב עם</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3717,7 +3733,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>קדש ברנע</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3747,7 +3763,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>תל ערד</t>
+          <t>מרעית</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3777,7 +3793,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>עזוז</t>
+          <t>אבו קרינאת</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3807,7 +3823,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ביר הדאג'</t>
+          <t>שדה בוקר</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3837,7 +3853,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ניצנה</t>
+          <t>ערערה בנגב</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3867,7 +3883,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>טללים</t>
+          <t>כמהין</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3897,7 +3913,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>מדרשת בן גוריון</t>
+          <t>מצפה רמון</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3927,7 +3943,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>באר מילכה</t>
+          <t>אשלים</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3957,7 +3973,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>דימונה</t>
+          <t>ערד</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3987,7 +4003,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>מרחב עם</t>
+          <t>כפר הנוקדים</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4017,7 +4033,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>אל פורעה</t>
+          <t>אזור תעשייה רותם</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4047,7 +4063,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>כפר הנוקדים</t>
+          <t>אל פורעה</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4077,7 +4093,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>אבו קרינאת</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4107,7 +4123,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>שדה בוקר</t>
+          <t>חירן</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4137,7 +4153,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ירוחם</t>
+          <t>ביר הדאג'</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4167,7 +4183,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>כסייפה</t>
+          <t>ירוחם</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4197,7 +4213,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>סעווה</t>
+          <t>תל ערד</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4227,7 +4243,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>קסר א-סר</t>
+          <t>סעווה</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4257,7 +4273,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ערערה בנגב</t>
+          <t>כסייפה</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4287,7 +4303,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ערד</t>
+          <t>באר מילכה</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4347,12 +4363,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>קדש ברנע</t>
+          <t>אזור תעשייה דימונה</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>South Negev</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4377,17 +4393,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>כמהין</t>
+          <t>עין בוקק</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4407,17 +4423,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>רתמים</t>
+          <t>עין גדי</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4437,17 +4453,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>מרעית</t>
+          <t>חוות מנחם</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4467,17 +4483,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>חירן</t>
+          <t>מצפה מדרג</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4497,17 +4513,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>אזור תעשייה רותם</t>
+          <t>עין תמר</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4527,17 +4543,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>אבו תלול</t>
+          <t>מלונות ים המלח מרכז</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4557,17 +4573,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>מצפה רמון</t>
+          <t>נאות הכיכר</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Southern Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4587,17 +4603,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>אזור תעשייה דימונה</t>
+          <t>מרחצאות עין גדי</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>South Negev</t>
+          <t>Dead Sea</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>Arava</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4617,7 +4633,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>מצדה</t>
+          <t>בתי מלון ים המלח</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4647,7 +4663,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>עין תמר</t>
+          <t>נווה זוהר</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4677,7 +4693,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>עין בוקק</t>
+          <t>מצדה</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4707,12 +4723,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>נווה זוהר</t>
+          <t>חצבה</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4727,22 +4743,20 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F145" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>בתי מלון ים המלח</t>
+          <t>עין חצבה</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4757,22 +4771,20 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>מרחצאות עין גדי</t>
+          <t>עידן</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Aravah</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4787,27 +4799,25 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>מלונות ים המלח מרכז</t>
+          <t>חוות טליה</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4817,27 +4827,25 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>נאות הכיכר</t>
+          <t>חוות טואמין</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4847,27 +4855,25 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>מצפה מדרג</t>
+          <t>מצפה יאיר</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4877,27 +4883,25 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>חוות מנחם</t>
+          <t>אביגיל</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4907,27 +4911,25 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>עין גדי</t>
+          <t>חוות דרומא</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dead Sea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4937,27 +4939,25 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>חצבה</t>
+          <t>סוסיא הקדומה</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4975,17 +4975,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>עין חצבה</t>
+          <t>אשתמוע</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5003,17 +5003,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>עידן</t>
+          <t>חוות מור ואברהם</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Aravah</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Arava</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5031,12 +5031,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>עשהאל</t>
+          <t>אזור תעשייה מיתרים</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5059,12 +5059,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>שמעה</t>
+          <t>חוות יויו</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5087,12 +5087,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>הר עמשא</t>
+          <t>חוות מקנה יהודה</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Judea</t>
+          <t>Yehuda</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5115,7 +5115,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>סוסיא</t>
+          <t>מעון</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5143,7 +5143,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>שני ליבנה</t>
+          <t>כרמל</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>בית יתיר</t>
+          <t>סוסיא</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>מעון</t>
+          <t>הר עמשא</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>כרמל</t>
+          <t>שמעה</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5283,17 +5283,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>סנסנה</t>
+          <t>שני ליבנה</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5303,27 +5303,25 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>נבטים</t>
+          <t>בית יתיר</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5333,27 +5331,25 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>אל סייד</t>
+          <t>עשהאל</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Center Negev</t>
+          <t>Judea</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Beer Sheva / Negev</t>
+          <t>West Bank</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5363,17 +5359,15 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>360</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>כרמים</t>
+          <t>תל שבע</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5403,7 +5397,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>באר שבע - מזרח</t>
+          <t>אל סייד</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5433,7 +5427,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>אשכולות</t>
+          <t>תארבין</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5463,7 +5457,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>רהט</t>
+          <t>גבעות בר</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5493,7 +5487,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>שובל</t>
+          <t>רהט</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5523,7 +5517,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>אתר דודאים</t>
+          <t>להב</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5553,7 +5547,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>להבים</t>
+          <t>כרמים</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5583,7 +5577,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>גבעות בר</t>
+          <t>עומר</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5613,7 +5607,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>דביר</t>
+          <t>אום בטין</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5643,7 +5637,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>כרמית</t>
+          <t>אזור תעשייה עידן הנגב</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5673,7 +5667,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>להב</t>
+          <t>שובל</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5703,7 +5697,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>באר שבע - דרום</t>
+          <t>באר שבע - צפון</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5733,7 +5727,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>תארבין</t>
+          <t>סנסנה</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5763,7 +5757,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>חורה</t>
+          <t>בית קמה</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5793,7 +5787,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>אום בטין</t>
+          <t>להבים</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5823,7 +5817,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>תל שבע</t>
+          <t>שגב שלום</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5853,7 +5847,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>מיתר</t>
+          <t>אתר דודאים</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5883,7 +5877,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>אזור תעשייה עידן הנגב</t>
+          <t>באר שבע - דרום</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5913,7 +5907,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>חצרים</t>
+          <t>כרמית</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5943,7 +5937,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>עומר</t>
+          <t>מיתר</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5973,7 +5967,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>שגב שלום</t>
+          <t>משמר הנגב</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6003,7 +5997,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>בית קמה</t>
+          <t>אשכולות</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6033,7 +6027,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>באר שבע - צפון</t>
+          <t>באר שבע - מערב</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6063,7 +6057,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>באר שבע - מערב</t>
+          <t>לקיה</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6093,7 +6087,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>משמר הנגב</t>
+          <t>דביר</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6123,7 +6117,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>לקיה</t>
+          <t>נבטים</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6153,17 +6147,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>אזור תעשייה נ.ע.מ</t>
+          <t>חצרים</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6183,17 +6177,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>בטחה</t>
+          <t>באר שבע - מזרח</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -6213,17 +6207,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>תאשור</t>
+          <t>חורה</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>West Negev</t>
+          <t>Center Negev</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Gaza Area</t>
+          <t>Beer Sheva / Negev</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6243,7 +6237,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>קלחים</t>
+          <t>ניר משה</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6273,7 +6267,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>אופקים</t>
+          <t>תדהר</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6303,7 +6297,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>גבולות</t>
+          <t>פדויים</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6333,7 +6327,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>דורות</t>
+          <t>אשל הנשיא</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6363,7 +6357,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>שבי דרום</t>
+          <t>ניר עקיבא</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6393,7 +6387,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>אשבול</t>
+          <t>קריית חינוך מרחבים</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6423,7 +6417,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ברור חיל</t>
+          <t>זרועה</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6453,7 +6447,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>זרועה</t>
+          <t>ברור חיל</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6483,7 +6477,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>צאלים</t>
+          <t>גבולות</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6513,7 +6507,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ניר משה</t>
+          <t>פטיש</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6543,7 +6537,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>קריית חינוך מרחבים</t>
+          <t>שדה צבי</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6573,7 +6567,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>רוחמה</t>
+          <t>שיבולים</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6603,7 +6597,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>תפרח</t>
+          <t>שבי דרום</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6633,7 +6627,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ברוש</t>
+          <t>בית הגדי</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6663,7 +6657,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>שרשרת</t>
+          <t>תפרח</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6693,7 +6687,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>אשל הנשיא</t>
+          <t>אורים</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6723,7 +6717,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>שדה צבי</t>
+          <t>תאשור</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6753,7 +6747,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>בית הגדי</t>
+          <t>דורות</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6783,7 +6777,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>אורים</t>
+          <t>מבועים</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6813,7 +6807,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>יושיביה</t>
+          <t>רנן</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6843,7 +6837,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>נתיבות</t>
+          <t>מסלול</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6873,7 +6867,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>שיבולים</t>
+          <t>אזור תעשייה נ.ע.מ</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6903,7 +6897,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ניר עקיבא</t>
+          <t>גילת</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6933,7 +6927,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>פטיש</t>
+          <t>רוחמה</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6963,7 +6957,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>גילת</t>
+          <t>שרשרת</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6993,7 +6987,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>רנן</t>
+          <t>בטחה</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7023,7 +7017,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>תדהר</t>
+          <t>יושיביה</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7053,7 +7047,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>מבועים</t>
+          <t>נתיבות</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7083,7 +7077,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>פדויים</t>
+          <t>אשבול</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7113,7 +7107,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>מסלול</t>
+          <t>קלחים</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7143,12 +7137,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ארז</t>
+          <t>ברוש</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Gaza Envelope</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -7167,18 +7161,18 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>מגן</t>
+          <t>צאלים</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Gaza Envelope</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7197,18 +7191,18 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>כרם שלום</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Gaza Envelope</t>
+          <t>West Negev</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -7227,13 +7221,13 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>נווה</t>
+          <t>עין השלושה</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7263,7 +7257,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ניר עוז</t>
+          <t>תקומה</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7293,7 +7287,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>אור הנר</t>
+          <t>דקל</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7323,7 +7317,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>מפלסים</t>
+          <t>ניר עם</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7353,7 +7347,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>יכיני</t>
+          <t>זיקים</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7383,7 +7377,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>כיסופים</t>
+          <t>ניר יצחק</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7413,7 +7407,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>שלומית</t>
+          <t>חניון רעים אנדרטת הנובה</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7443,7 +7437,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>יתד</t>
+          <t>חוף זיקים</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7473,7 +7467,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>תלמי אליהו</t>
+          <t>נווה</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7503,7 +7497,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>תלמי יוסף</t>
+          <t>שדה ניצן</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7533,7 +7527,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>אבשלום</t>
+          <t>עין הבשור</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7563,7 +7557,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>זיקים</t>
+          <t>יד מרדכי</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7593,7 +7587,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>נחל עוז</t>
+          <t>פרי גן</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7623,7 +7617,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>בני נצרים</t>
+          <t>חולית</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7653,7 +7647,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>פרי גן</t>
+          <t>כפר עזה</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7683,7 +7677,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>רעים</t>
+          <t>אור הנר</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7713,7 +7707,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ניר עם</t>
+          <t>סעד</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7743,7 +7737,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>גברעם</t>
+          <t>תלמי יוסף</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7773,7 +7767,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>שדה ניצן</t>
+          <t>אבשלום</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7803,7 +7797,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>יד מרדכי</t>
+          <t>נתיב העשרה</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7833,7 +7827,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>חניון רעים אנדרטת הנובה</t>
+          <t>גברעם</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7863,7 +7857,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>עלומים</t>
+          <t>בארי</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7893,7 +7887,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>חולית</t>
+          <t>ארז</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7923,7 +7917,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>מטווח ניר עם</t>
+          <t>נירים</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7983,7 +7977,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>כפר עזה</t>
+          <t>שדי אברהם</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8013,7 +8007,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>תקומה</t>
+          <t>בני נצרים</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8043,7 +8037,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>יבול</t>
+          <t>ניר עוז</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8073,7 +8067,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>נתיב העשרה</t>
+          <t>תלמי אליהו</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8103,7 +8097,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>שדי אברהם</t>
+          <t>כיסופים</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8133,7 +8127,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>שוקדה</t>
+          <t>נחל עוז</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8163,7 +8157,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>עין השלושה</t>
+          <t>רעים</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8193,7 +8187,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>סופה</t>
+          <t>יתד</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8223,7 +8217,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>סעד</t>
+          <t>מגן</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8253,7 +8247,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ניר יצחק</t>
+          <t>סופה</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8283,7 +8277,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>בארי</t>
+          <t>מפלסים</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8313,7 +8307,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>כרמיה</t>
+          <t>שוקדה</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8343,7 +8337,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>עין הבשור</t>
+          <t>שלומית</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8373,7 +8367,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>דקל</t>
+          <t>מטווח ניר עם</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8403,7 +8397,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>נירים</t>
+          <t>כרם שלום</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8433,7 +8427,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>חוף זיקים</t>
+          <t>כרמיה</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8463,17 +8457,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>יבול</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Gaza Envelope</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -8487,23 +8481,23 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>יכיני</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Gaza Envelope</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -8517,23 +8511,23 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>עלומים</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Gaza Envelope</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Gaza Area</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -8547,13 +8541,13 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8583,7 +8577,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8613,7 +8607,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8643,7 +8637,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8673,7 +8667,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8703,7 +8697,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8733,7 +8727,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8763,7 +8757,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8793,7 +8787,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8823,7 +8817,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8853,7 +8847,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8883,7 +8877,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8913,7 +8907,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8943,7 +8937,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8973,7 +8967,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9003,7 +8997,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9033,7 +9027,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9063,7 +9057,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9123,7 +9117,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9213,7 +9207,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9243,7 +9237,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9273,7 +9267,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9303,7 +9297,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9333,7 +9327,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9363,7 +9357,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9393,7 +9387,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9423,7 +9417,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9453,7 +9447,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9483,7 +9477,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9513,7 +9507,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9543,12 +9537,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -9573,12 +9567,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -9603,12 +9597,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -9633,7 +9627,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9663,7 +9657,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9693,7 +9687,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9723,7 +9717,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9753,7 +9747,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9783,7 +9777,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9813,7 +9807,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9843,7 +9837,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9873,7 +9867,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9903,7 +9897,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9933,7 +9927,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>חוסנייה</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9963,7 +9957,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9993,7 +9987,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>חוסנייה</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10023,7 +10017,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10053,7 +10047,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10083,7 +10077,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10113,7 +10107,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10143,7 +10137,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10173,7 +10167,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10203,7 +10197,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10233,7 +10227,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10263,7 +10257,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10293,7 +10287,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10323,7 +10317,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10353,7 +10347,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10383,7 +10377,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10413,7 +10407,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10443,7 +10437,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10473,7 +10467,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>עילבון</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10503,7 +10497,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10533,7 +10527,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10563,7 +10557,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10593,7 +10587,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10623,7 +10617,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>עילבון</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10653,7 +10647,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10683,7 +10677,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10713,7 +10707,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10743,7 +10737,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10773,7 +10767,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -10803,7 +10797,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10833,7 +10827,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10863,7 +10857,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10893,7 +10887,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -10923,7 +10917,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10953,7 +10947,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10983,12 +10977,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -11013,12 +11007,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -11043,12 +11037,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -11073,7 +11067,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>עין אל אסד</t>
+          <t>חמדת ימים</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11103,7 +11097,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -11133,7 +11127,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11163,7 +11157,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>בית ג'אן</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11193,7 +11187,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>אליפלט</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11223,7 +11217,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>בית ג'אן</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -11253,7 +11247,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>הר חלוץ</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11283,7 +11277,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>אליפלט</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11313,7 +11307,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>כסרא סמיע</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11343,7 +11337,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11373,7 +11367,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>אזור תעשייה צ.ח.ר</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -11403,7 +11397,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>כפר שמאי</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -11433,7 +11427,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>אפק</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11463,7 +11457,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11493,7 +11487,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11523,7 +11517,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11553,7 +11547,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11583,7 +11577,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11613,7 +11607,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11643,7 +11637,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>שפר</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11673,7 +11667,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11703,7 +11697,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>שפר</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11733,7 +11727,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>הר חלוץ</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11763,7 +11757,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11793,7 +11787,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>בענה</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11823,7 +11817,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11853,7 +11847,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11883,7 +11877,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>אזור תעשייה כרמיאל</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11913,7 +11907,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>אמירים</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11943,7 +11937,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11973,7 +11967,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -12003,7 +11997,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12033,7 +12027,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12063,7 +12057,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12093,7 +12087,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>אמירים</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12123,7 +12117,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>שזור</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12153,7 +12147,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -12183,7 +12177,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>צפת - נוף כנרת</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -12213,7 +12207,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>חמדת ימים</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -12243,7 +12237,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -12273,7 +12267,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>ראמה</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12303,7 +12297,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>סאג'ור</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12333,7 +12327,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>לבון</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12363,7 +12357,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>פרוד</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -12393,7 +12387,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>אזור תעשייה שער נעמן</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -12423,7 +12417,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12483,7 +12477,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -12513,7 +12507,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12543,7 +12537,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12573,7 +12567,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12603,7 +12597,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12633,7 +12627,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>חרשים</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12663,7 +12657,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>חרשים</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12693,7 +12687,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>אמנון</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -12723,7 +12717,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>עין אל אסד</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -12753,7 +12747,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ראמה</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -12783,7 +12777,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>נתיב השיירה</t>
+          <t>שזור</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -12813,7 +12807,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>בענה</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12843,7 +12837,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12873,7 +12867,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12903,7 +12897,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -12933,7 +12927,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -12963,7 +12957,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>צפת - נוף כנרת</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -12993,7 +12987,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>נחף</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -13023,7 +13017,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -13053,7 +13047,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>אמנון</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13083,7 +13077,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13113,7 +13107,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>כרמיאל</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13143,7 +13137,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13173,7 +13167,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>נתיב השיירה</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -13203,7 +13197,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>אזור תעשייה צ.ח.ר</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -13233,7 +13227,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>כרמיאל</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13263,7 +13257,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13293,7 +13287,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>אפק</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -13323,7 +13317,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>פרוד</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13353,7 +13347,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>כפר שמאי</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -13383,7 +13377,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -13443,7 +13437,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>נחף</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -13473,7 +13467,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>סאג'ור</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13503,7 +13497,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -13533,7 +13527,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -13563,7 +13557,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>כסרא סמיע</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -13593,7 +13587,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>לבון</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13623,7 +13617,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -13653,7 +13647,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>אזור תעשייה כרמיאל</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -13683,12 +13677,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -13713,12 +13707,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -13743,12 +13737,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -13773,12 +13767,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -13793,17 +13787,15 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F448" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -13833,7 +13825,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>כפר תקווה</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -13863,7 +13855,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>משהד</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -13893,7 +13885,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>שער העמקים</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -13923,7 +13915,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -13953,7 +13945,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -13983,7 +13975,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -14013,7 +14005,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>כפר ח'וואלד</t>
+          <t>בסמת טבעון</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -14043,7 +14035,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>אלונים</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -14073,7 +14065,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>אורנים</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -14103,7 +14095,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>ראס עלי</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14133,7 +14125,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>כפר ח'וואלד</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -14163,7 +14155,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -14193,7 +14185,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -14223,7 +14215,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -14253,7 +14245,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>כפר תקווה</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -14283,7 +14275,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -14313,7 +14305,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>סואעד חמירה</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -14343,7 +14335,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -14373,7 +14365,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -14403,7 +14395,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -14433,7 +14425,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -14463,7 +14455,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -14493,7 +14485,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>נופית</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14523,7 +14515,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -14553,7 +14545,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -14583,7 +14575,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -14613,7 +14605,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14643,7 +14635,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -14673,7 +14665,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -14703,7 +14695,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>בסמת טבעון</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -14733,7 +14725,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -14763,7 +14755,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -14793,7 +14785,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -14823,7 +14815,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>קריית טבעון - בית זייד</t>
+          <t>מגדל העמק</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -14853,7 +14845,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -14883,7 +14875,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>שער העמקים</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -14913,7 +14905,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>מגדל העמק</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -14943,7 +14935,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>נופית</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -14973,7 +14965,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -15003,7 +14995,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>אלונים</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -15033,7 +15025,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>אורנים</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -15063,7 +15055,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>קריית טבעון - בית זייד</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -15093,7 +15085,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -15123,7 +15115,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>משהד</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -15153,7 +15145,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15183,7 +15175,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -15213,7 +15205,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>ראס עלי</t>
+          <t>סואעד חמירה</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -15243,7 +15235,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -15273,7 +15265,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -15303,7 +15295,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -15333,7 +15325,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -15363,7 +15355,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -15393,7 +15385,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -15423,17 +15415,17 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -15453,17 +15445,17 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -15483,17 +15475,17 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -15513,17 +15505,17 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -15543,7 +15535,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -15573,7 +15565,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -15603,7 +15595,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -15633,7 +15625,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר יהושוע</t>
+          <t>נמל קיסריה</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -15663,7 +15655,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -15693,7 +15685,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -15723,7 +15715,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -15783,7 +15775,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -15813,7 +15805,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -15843,7 +15835,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -15873,7 +15865,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -15903,7 +15895,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -15933,7 +15925,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -15963,7 +15955,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -15993,7 +15985,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -16023,7 +16015,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -16053,7 +16045,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -16083,7 +16075,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -16143,7 +16135,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -16173,7 +16165,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -16203,7 +16195,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>נמל קיסריה</t>
+          <t>תחנת רכבת כפר יהושוע</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -16233,7 +16225,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -16263,7 +16255,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -16293,7 +16285,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -16323,7 +16315,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -16353,7 +16345,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -16383,7 +16375,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -16443,7 +16435,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -16473,7 +16465,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -16503,7 +16495,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -16533,7 +16525,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -16563,17 +16555,17 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>אלי עד</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -16593,17 +16585,17 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>חמת גדר</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -16623,17 +16615,17 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>אפיק</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -16653,17 +16645,17 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>יונתן</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -16683,7 +16675,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>כפר חרוב</t>
+          <t>אפיק</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -16713,7 +16705,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>חד נס</t>
+          <t>קצרין - אזור תעשייה</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -16743,7 +16735,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>אשדות יעקב</t>
+          <t>אבני איתן</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -16773,7 +16765,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>קשת</t>
+          <t>האון</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -16803,7 +16795,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>אלוני הבשן</t>
+          <t>שער הגולן</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -16833,7 +16825,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>נוב</t>
+          <t>תל קציר</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -16863,7 +16855,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>חספין</t>
+          <t>נוב</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -16893,7 +16885,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>אלמגור</t>
+          <t>עין גב</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -16923,7 +16915,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>נאות גולן</t>
+          <t>מבוא חמה</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -16953,7 +16945,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>רמת מגשימים</t>
+          <t>אלמגור</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -16983,7 +16975,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>מיצר</t>
+          <t>קדמת צבי</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -17013,7 +17005,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>קצרין - אזור תעשייה</t>
+          <t>אזור תעשייה בני יהודה</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -17043,7 +17035,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>מסדה</t>
+          <t>חד נס</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -17073,7 +17065,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>גשור</t>
+          <t>חמת גדר</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -17103,7 +17095,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>קדמת צבי</t>
+          <t>אלוני הבשן</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -17133,7 +17125,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>צמח</t>
+          <t>אלי עד</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -17163,7 +17155,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>מעלה גמלא</t>
+          <t>גשור</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -17193,7 +17185,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>בני יהודה וגבעת יואב</t>
+          <t>חספין</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -17223,7 +17215,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>רמות</t>
+          <t>כפר חרוב</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -17253,7 +17245,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>שער הגולן</t>
+          <t>כנף</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -17283,7 +17275,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>האון</t>
+          <t>אניעם</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -17313,7 +17305,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>עין גב</t>
+          <t>יונתן</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -17343,7 +17335,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>אבני איתן</t>
+          <t>קשת</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -17373,7 +17365,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>נטור</t>
+          <t>צמח</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17403,7 +17395,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>אניעם</t>
+          <t>בני יהודה וגבעת יואב</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -17433,7 +17425,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>תל קציר</t>
+          <t>רמת מגשימים</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17463,7 +17455,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>מבוא חמה</t>
+          <t>מעלה גמלא</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -17493,7 +17485,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>אזור תעשייה בני יהודה</t>
+          <t>אשדות יעקב</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -17523,7 +17515,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>כנף</t>
+          <t>נטור</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -17553,7 +17545,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>מעגן</t>
+          <t>רמות</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -17583,7 +17575,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>נאות גולן</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -17613,17 +17605,17 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>חיפה - מפרץ</t>
+          <t>מעגן</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -17643,17 +17635,17 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>אושה</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -17673,17 +17665,17 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>כפר המכבי</t>
+          <t>מסדה</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -17703,17 +17695,17 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>אזור תעשייה ניר עציון</t>
+          <t>מיצר</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -17733,7 +17725,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>כפר ביאליק</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -17763,7 +17755,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>רמת יוחנן</t>
+          <t>אזור תעשייה ניר עציון</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -17793,7 +17785,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>כפר גלים</t>
+          <t>חיפה - נווה שאנן ורמות כרמל</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -17853,7 +17845,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>טירת כרמל</t>
+          <t>כפר גלים</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -17883,7 +17875,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>איבטין</t>
+          <t>אזור תעשייה קריית ביאליק</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -17913,7 +17905,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>חיפה - נווה שאנן ורמות כרמל</t>
+          <t>קריית ביאליק</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -17943,7 +17935,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>חיפה - מערב</t>
+          <t>רמת יוחנן</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -17973,7 +17965,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>איבטין</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18003,7 +17995,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>החותרים</t>
+          <t>חיפה - מערב</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18033,7 +18025,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>כפר חסידים</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18063,7 +18055,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>קריית ים</t>
+          <t>קריית מוצקין</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18093,7 +18085,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>טירת כרמל</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18123,7 +18115,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>חיפה - קריית חיים ושמואל</t>
+          <t>קריית ים</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18153,7 +18145,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>החותרים</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18183,7 +18175,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>חיפה - בת גלים ק.אליעזר</t>
+          <t>חיפה - קריית חיים ושמואל</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18213,7 +18205,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>יגור</t>
+          <t>קריית אתא</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18243,7 +18235,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>כפר ביאליק</t>
+          <t>חיפה - בת גלים ק.אליעזר</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18273,7 +18265,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>קריית מוצקין</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18303,7 +18295,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>קריית אתא</t>
+          <t>כפר חסידים</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18333,12 +18325,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>נווה ים</t>
+          <t>אושה</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -18363,12 +18355,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>עופר</t>
+          <t>יגור</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -18393,12 +18385,12 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>בת שלמה</t>
+          <t>חיפה - מפרץ</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
@@ -18423,12 +18415,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>כפר המכבי</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -18453,7 +18445,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>פוריידיס</t>
+          <t>גבעת וולפסון</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18483,7 +18475,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>מאיר שפיה</t>
+          <t>בת שלמה</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -18513,7 +18505,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>עין איילה</t>
+          <t>מאיר שפיה</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -18543,7 +18535,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>צרופה</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18603,7 +18595,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>עתלית</t>
+          <t>עין חוד</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18633,7 +18625,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>מגדים</t>
+          <t>צרופה</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -18663,7 +18655,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>בית סוהר קישון</t>
+          <t>פוריידיס</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -18693,7 +18685,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>עין חוד</t>
+          <t>מגדים</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -18723,7 +18715,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>עין הוד</t>
+          <t>עין איילה</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -18753,7 +18745,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>עספיא</t>
+          <t>דלית אל כרמל</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -18783,7 +18775,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>דלית אל כרמל</t>
+          <t>נווה ים</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -18813,7 +18805,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>בית צבי</t>
+          <t>עספיא</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -18843,7 +18835,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>גבעת וולפסון</t>
+          <t>בית צבי</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -18873,7 +18865,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>בית אורן</t>
+          <t>גבע כרמל</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -18903,7 +18895,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>גבע כרמל</t>
+          <t>עתלית</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -18933,17 +18925,17 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>מרום גולן</t>
+          <t>בית סוהר קישון</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -18953,25 +18945,27 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F620" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>רמת טראמפ</t>
+          <t>עין הוד</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -18981,25 +18975,27 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>אודם</t>
+          <t>בית אורן</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -19009,25 +19005,27 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F622" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>מג'דל שמס</t>
+          <t>עופר</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -19037,15 +19035,17 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F623" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>נמרוד</t>
+          <t>מסעדה</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19073,7 +19073,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>אורטל</t>
+          <t>מרום גולן</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19101,7 +19101,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>עין זיוון</t>
+          <t>קלע אלון</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19129,7 +19129,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>אל רום</t>
+          <t>אודם</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19185,7 +19185,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>קלע אלון</t>
+          <t>מג'דל שמס</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19213,7 +19213,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>עין קנייא</t>
+          <t>נמרוד</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19241,7 +19241,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>בוקעתא</t>
+          <t>עין קנייא</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -19269,7 +19269,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>מסעדה</t>
+          <t>עין זיוון</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19297,17 +19297,17 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>רמת טראמפ</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -19325,17 +19325,17 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>בוקעתא</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -19353,17 +19353,17 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>מעלה עירון</t>
+          <t>אורטל</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -19381,17 +19381,17 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>אל רום</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -19409,7 +19409,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>מעלה עירון</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19437,7 +19437,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>קציר</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -19465,7 +19465,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19493,7 +19493,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>מדרך עוז</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19521,7 +19521,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19549,7 +19549,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -19577,7 +19577,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -19605,7 +19605,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>ברטעה</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19633,7 +19633,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19661,7 +19661,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19689,7 +19689,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -19717,7 +19717,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19745,7 +19745,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>רגבים</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19773,7 +19773,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19801,7 +19801,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19829,7 +19829,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -19857,7 +19857,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -19885,7 +19885,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -19913,7 +19913,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -19941,7 +19941,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>אום אל פחם</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -19969,7 +19969,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>מצר</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -19997,7 +19997,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>גלעד</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -20025,7 +20025,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>מועאוויה</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -20053,7 +20053,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -20081,7 +20081,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>קציר</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -20109,7 +20109,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -20137,7 +20137,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -20165,30 +20165,142 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
+          <t>עין אל סהלה</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>עין העמק</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>מצפה אילן</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>עין השופט</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
           <t>באקה אל גרבייה</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
+      <c r="B668" t="inlineStr">
         <is>
           <t>Wadi Ara</t>
         </is>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C668" t="inlineStr">
         <is>
           <t>Haifa Area</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr">
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
         <is>
           <t>pre_only</t>
         </is>
       </c>
-      <c r="F664" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F886"/>
+  <dimension ref="A1:F895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>עין יעקב</t>
+          <t>ברעם</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>אביבים</t>
+          <t>מנות</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,7 +511,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>אלקוש</t>
+          <t>שאר ישוב</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>בן עמי</t>
+          <t>צבעון</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>סאסא</t>
+          <t>ריחאנייה</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>כפר ורדים</t>
+          <t>יחיעם</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>חניתה</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>דפנה</t>
+          <t>מעלות תרשיחא</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ריחאנייה</t>
+          <t>בית העלמין החדש נהריה</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>יערה</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -751,7 +751,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>בית הלל</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>חוף אכזיב</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>פקיעין החדשה</t>
+          <t>להבות הבשן</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>נהריה</t>
+          <t>אבירים</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>מעונה</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>שניר</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>מעיליא</t>
+          <t>שומרה</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>פסוטה</t>
+          <t>עברון</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>שניר</t>
+          <t>כפר בלום</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>געתון</t>
+          <t>אילון</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>סער</t>
+          <t>לימן</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>שדה נחמיה</t>
+          <t>עין יעקב</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1111,7 +1111,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>גונן</t>
+          <t>חוסן</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>אדמית</t>
+          <t>כפר ורדים</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>כברי</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>עלמה</t>
+          <t>פקיעין</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>מרכז אזורי מבואות חרמון</t>
+          <t>זרעית</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>דישון</t>
+          <t>שמיר</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1291,7 +1291,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>בית ספר שדה מירון</t>
+          <t>כפר סאלד</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>כרם בן זמרה</t>
+          <t>קיבוץ דן</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>מתת</t>
+          <t>בן עמי</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>עמיר</t>
+          <t>שלומי</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ערב אל עראמשה</t>
+          <t>מכמנים - כמאנה מערבית</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>אילון</t>
+          <t>שתולה</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>נווה זיו</t>
+          <t>שדה נחמיה</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>מכמנים - כמאנה מערבית</t>
+          <t>תל חי</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>אזור תעשייה רמת דלתון</t>
+          <t>הילה</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>נאות מרדכי</t>
+          <t>אדמית</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1591,7 +1591,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>יחיעם</t>
+          <t>דלתון</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>הגושרים</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1651,7 +1651,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>מלכיה</t>
+          <t>בית ספר שדה מירון</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1681,7 +1681,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>אבן מנחם</t>
+          <t>גשר הזיו</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>שומרה</t>
+          <t>אביבים</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>שתולה</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>לימן</t>
+          <t>ע'ג'ר</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>מנרה</t>
+          <t>נטועה</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>שאר ישוב</t>
+          <t>ג'ש - גוש חלב</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1861,7 +1861,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>בית העלמין החדש נהריה</t>
+          <t>לב החולה</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>חוסן</t>
+          <t>ערב אל עראמשה</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>מנות</t>
+          <t>צוריאל</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>גורן</t>
+          <t>בצת</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>תל חי</t>
+          <t>סאסא</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>מצובה</t>
+          <t>יערה</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>כפר גלעדי</t>
+          <t>דפנה</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ע'ג'ר</t>
+          <t>מנרה</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2101,7 +2101,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>מרגליות</t>
+          <t>געתון</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2131,7 +2131,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>יפתח</t>
+          <t>עמיר</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>נווה זיו</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2191,7 +2191,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>עברון</t>
+          <t>יפתח</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>פקיעין</t>
+          <t>מטולה</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>מעלות תרשיחא</t>
+          <t>מצובה</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>חורפיש</t>
+          <t>מתת</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2311,7 +2311,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>כפר בלום</t>
+          <t>כפר גלעדי</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ברעם</t>
+          <t>עלמה</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>מעונה</t>
+          <t>אלקוש</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2401,7 +2401,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>בית הלל</t>
+          <t>נאות מרדכי</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>גורנות הגליל</t>
+          <t>רמות נפתלי</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>מטולה</t>
+          <t>אבן מנחם</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>צוריאל</t>
+          <t>אזור תעשייה רמת דלתון</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>רמות נפתלי</t>
+          <t>דישון</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2551,7 +2551,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>שלומי</t>
+          <t>חוף אכזיב</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>כברי</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>להבות הבשן</t>
+          <t>חורפיש</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2641,7 +2641,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>גשר הזיו</t>
+          <t>פקיעין החדשה</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>קיבוץ דן</t>
+          <t>עבדון</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>הגושרים</t>
+          <t>גורן</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2731,7 +2731,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2761,7 +2761,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>זרעית</t>
+          <t>מרגליות</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>עבדון</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>מרכז אזורי מבואות חרמון</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2851,7 +2851,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>דלתון</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>שמיר</t>
+          <t>נהריה</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2911,7 +2911,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>צבעון</t>
+          <t>פסוטה</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>הילה</t>
+          <t>כרם בן זמרה</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3001,7 +3001,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>אבירים</t>
+          <t>חניתה</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3031,7 +3031,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>נטועה</t>
+          <t>גורנות הגליל</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>לב החולה</t>
+          <t>מעיליא</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>כפר סאלד</t>
+          <t>סער</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ג'ש - גוש חלב</t>
+          <t>מלכיה</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>להבות הבשן</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3263,7 +3263,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>להבות הבשן</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>גונן</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>אביבים</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>אביבים</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3489,7 +3489,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>צבעון</t>
+          <t>ג'ש - גוש חלב</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ג'ש - גוש חלב</t>
+          <t>צבעון</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3545,17 +3545,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>דלתון</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3565,27 +3565,25 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>בית ירח</t>
+          <t>אזור תעשייה רמת דלתון</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lower Galilee</t>
+          <t>Confrontation Line</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Galilee</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3595,17 +3593,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3635,7 +3631,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3665,7 +3661,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>שרונה</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3695,7 +3691,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3725,7 +3721,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3755,7 +3751,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3785,7 +3781,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3815,7 +3811,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3845,7 +3841,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3875,7 +3871,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3905,7 +3901,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3935,7 +3931,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3965,7 +3961,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3995,7 +3991,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4025,7 +4021,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4055,7 +4051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4085,7 +4081,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4115,7 +4111,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>גבעת אבני</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4145,7 +4141,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4175,7 +4171,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4205,7 +4201,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>שרונה</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4235,7 +4231,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4265,7 +4261,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4295,7 +4291,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4325,7 +4321,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4355,7 +4351,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4385,7 +4381,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4415,7 +4411,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4445,7 +4441,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4475,7 +4471,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4505,7 +4501,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4535,7 +4531,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4565,7 +4561,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>גבעת אבני</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4595,7 +4591,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4625,7 +4621,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>בית ירח</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4649,13 +4645,13 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>בית ירח</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4679,13 +4675,13 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4715,7 +4711,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4745,7 +4741,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>שרונה</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4775,7 +4771,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4805,7 +4801,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4835,7 +4831,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4865,7 +4861,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4895,7 +4891,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4925,7 +4921,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4955,7 +4951,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4985,7 +4981,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5015,7 +5011,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5045,7 +5041,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5075,7 +5071,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5105,7 +5101,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5135,7 +5131,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5165,7 +5161,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5195,7 +5191,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>גבעת אבני</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5225,7 +5221,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5255,7 +5251,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5285,7 +5281,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>שרונה</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5315,7 +5311,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5345,7 +5341,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5375,7 +5371,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5405,7 +5401,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5435,7 +5431,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5465,7 +5461,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5495,7 +5491,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5525,7 +5521,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5555,7 +5551,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5585,7 +5581,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5615,7 +5611,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5645,7 +5641,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>גבעת אבני</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5675,7 +5671,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5705,12 +5701,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>בית ירח</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5729,18 +5725,18 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Center Galilee</t>
+          <t>Lower Galilee</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5759,13 +5755,13 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5795,7 +5791,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5825,7 +5821,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5855,7 +5851,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5885,7 +5881,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5915,7 +5911,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5945,7 +5941,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5975,7 +5971,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6005,7 +6001,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6035,7 +6031,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6065,7 +6061,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>עילבון</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6095,7 +6091,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6125,7 +6121,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6155,7 +6151,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6185,7 +6181,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6215,7 +6211,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6245,7 +6241,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6275,7 +6271,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6335,7 +6331,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6365,7 +6361,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6395,7 +6391,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6425,7 +6421,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6455,7 +6451,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6485,7 +6481,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6515,7 +6511,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6545,7 +6541,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6575,7 +6571,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6605,7 +6601,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6635,7 +6631,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6665,7 +6661,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6695,7 +6691,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6725,7 +6721,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6755,7 +6751,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6785,7 +6781,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6815,7 +6811,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6845,7 +6841,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6875,7 +6871,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6905,7 +6901,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6935,7 +6931,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6965,7 +6961,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6995,7 +6991,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7025,7 +7021,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7055,7 +7051,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7085,7 +7081,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>עילבון</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7115,7 +7111,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7145,7 +7141,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7169,13 +7165,13 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7199,13 +7195,13 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7235,7 +7231,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7265,7 +7261,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7295,7 +7291,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7325,7 +7321,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7355,7 +7351,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7385,7 +7381,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7415,7 +7411,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7445,7 +7441,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7475,7 +7471,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7505,7 +7501,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>עילבון</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7535,7 +7531,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7565,7 +7561,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7595,7 +7591,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7625,7 +7621,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7655,7 +7651,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7685,7 +7681,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7715,7 +7711,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7775,7 +7771,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7805,7 +7801,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7835,7 +7831,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7865,7 +7861,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7895,7 +7891,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7925,7 +7921,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7955,7 +7951,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7985,7 +7981,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8015,7 +8011,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8045,7 +8041,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8075,7 +8071,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8105,7 +8101,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8135,7 +8131,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8165,7 +8161,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8195,7 +8191,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8225,7 +8221,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8255,7 +8251,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8285,7 +8281,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8315,7 +8311,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8345,7 +8341,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8375,7 +8371,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8405,7 +8401,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8435,7 +8431,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8465,7 +8461,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8495,7 +8491,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8525,7 +8521,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>עילבון</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8555,7 +8551,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8585,12 +8581,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8609,18 +8605,18 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Upper Galilee</t>
+          <t>Center Galilee</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8639,13 +8635,13 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>חמדת ימים</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8675,7 +8671,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8705,7 +8701,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>חרשים</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8735,7 +8731,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>כפר שמאי</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8765,7 +8761,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>צפת - נוף כנרת</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8795,7 +8791,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ביריה</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8825,7 +8821,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8855,7 +8851,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>אליפלט</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8885,7 +8881,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>כרמיאל</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8915,7 +8911,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>נתיב השיירה</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8945,7 +8941,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>סאג'ור</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8975,7 +8971,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>כרמיאל</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -9005,7 +9001,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9035,7 +9031,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ראמה</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9065,7 +9061,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9095,7 +9091,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>לבון</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9125,7 +9121,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>אמירים</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9155,7 +9151,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9185,7 +9181,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9215,7 +9211,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>פרוד</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9245,7 +9241,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9275,7 +9271,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9305,7 +9301,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>שזור</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9335,7 +9331,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9365,7 +9361,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9395,7 +9391,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9425,7 +9421,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>עין אל אסד</t>
+          <t>אליפלט</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9455,7 +9451,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9485,7 +9481,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9515,7 +9511,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -9545,7 +9541,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9575,7 +9571,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>אמנון</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9605,7 +9601,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9635,7 +9631,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>אזור תעשייה כרמיאל</t>
+          <t>בית ג'אן</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9665,7 +9661,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>נחף</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9695,7 +9691,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9725,7 +9721,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9755,7 +9751,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9785,7 +9781,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9815,7 +9811,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>אזור תעשייה צ.ח.ר</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9845,7 +9841,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>אפק</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9875,7 +9871,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9905,7 +9901,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9935,7 +9931,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9965,7 +9961,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9995,7 +9991,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10025,7 +10021,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10055,7 +10051,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10085,7 +10081,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>אזור תעשייה כרמיאל</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10115,7 +10111,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10145,7 +10141,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>אמנון</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10175,7 +10171,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>שזור</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10205,7 +10201,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10235,7 +10231,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>נחף</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10265,7 +10261,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10295,7 +10291,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>פרוד</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10325,7 +10321,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10355,7 +10351,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>לבון</t>
+          <t>כפר שמאי</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10385,7 +10381,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10415,7 +10411,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>עין אל אסד</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10445,7 +10441,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>דיר אל-אסד</t>
+          <t>שפר</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10475,7 +10471,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>בענה</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10505,7 +10501,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>סאג'ור</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10535,7 +10531,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10565,7 +10561,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>אזור תעשייה צ.ח.ר</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10595,7 +10591,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10625,7 +10621,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>בענה</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10655,7 +10651,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10685,7 +10681,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>שפר</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10715,7 +10711,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>הר חלוץ</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10745,7 +10741,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10775,7 +10771,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>חמדת ימים</t>
+          <t>אפק</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10805,7 +10801,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>אזור תעשייה שער נעמן</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -10835,7 +10831,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10865,7 +10861,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10895,7 +10891,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>אמירים</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10925,7 +10921,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>חרשים</t>
+          <t>כסרא סמיע</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -10955,7 +10951,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>דיר אל-אסד</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10985,7 +10981,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>בית ג'אן</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11015,7 +11011,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11045,7 +11041,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11075,7 +11071,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>הר חלוץ</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11105,7 +11101,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>נתיב השיירה</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11135,7 +11131,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>כסרא סמיע</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -11165,7 +11161,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>ראמה</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11195,7 +11191,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11225,7 +11221,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11255,7 +11251,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>צפת - נוף כנרת</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -11285,7 +11281,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11305,15 +11301,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11337,13 +11335,13 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11363,17 +11361,15 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F366" t="n">
-        <v>360</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>חמדת ימים</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11403,7 +11399,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -11433,7 +11429,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>חרשים</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -11463,7 +11459,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>כפר שמאי</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11493,7 +11489,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>צפת - נוף כנרת</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11523,7 +11519,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ביריה</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11553,7 +11549,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11583,7 +11579,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>אליפלט</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11613,7 +11609,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>כרמיאל</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11643,7 +11639,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>נתיב השיירה</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11673,7 +11669,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>סאג'ור</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11703,7 +11699,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>כרמיאל</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11733,7 +11729,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11763,7 +11759,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ראמה</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11793,7 +11789,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11823,7 +11819,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>לבון</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11853,7 +11849,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>אמירים</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11883,7 +11879,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11913,7 +11909,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11943,7 +11939,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>פרוד</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11973,7 +11969,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -12003,7 +11999,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -12033,7 +12029,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>שזור</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12063,7 +12059,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12093,7 +12089,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12123,7 +12119,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12153,7 +12149,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>עין אל אסד</t>
+          <t>אליפלט</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12183,7 +12179,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -12213,7 +12209,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -12243,7 +12239,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -12273,7 +12269,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -12303,7 +12299,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>אמנון</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12333,7 +12329,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12363,7 +12359,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>אזור תעשייה כרמיאל</t>
+          <t>בית ג'אן</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12393,7 +12389,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>נחף</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -12423,7 +12419,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -12453,7 +12449,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12483,7 +12479,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -12513,7 +12509,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -12543,7 +12539,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>אזור תעשייה צ.ח.ר</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12573,7 +12569,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>אפק</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12603,7 +12599,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12633,7 +12629,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12663,7 +12659,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12693,7 +12689,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12723,7 +12719,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -12753,7 +12749,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -12783,7 +12779,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -12813,7 +12809,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>אזור תעשייה כרמיאל</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -12843,7 +12839,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12873,7 +12869,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>אמנון</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12903,7 +12899,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>שזור</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12933,7 +12929,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -12963,7 +12959,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>נחף</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -12993,7 +12989,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -13023,7 +13019,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>פרוד</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -13053,7 +13049,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -13083,7 +13079,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>לבון</t>
+          <t>כפר שמאי</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13113,7 +13109,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13143,7 +13139,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>עין אל אסד</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13173,7 +13169,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>דיר אל-אסד</t>
+          <t>שפר</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13203,7 +13199,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>בענה</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -13233,7 +13229,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>סאג'ור</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -13263,7 +13259,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -13293,7 +13289,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>אזור תעשייה צ.ח.ר</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13323,7 +13319,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -13353,7 +13349,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>בענה</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13383,7 +13379,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -13413,7 +13409,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>שפר</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -13443,7 +13439,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>הר חלוץ</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -13473,7 +13469,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -13503,7 +13499,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>חמדת ימים</t>
+          <t>אפק</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13533,7 +13529,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>אזור תעשייה שער נעמן</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -13563,7 +13559,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -13593,7 +13589,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -13623,7 +13619,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>אמירים</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13653,7 +13649,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>חרשים</t>
+          <t>כסרא סמיע</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -13683,7 +13679,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>דיר אל-אסד</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -13713,7 +13709,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>בית ג'אן</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -13743,7 +13739,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -13773,7 +13769,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -13803,7 +13799,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>הר חלוץ</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -13833,7 +13829,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>נתיב השיירה</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -13863,7 +13859,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>כסרא סמיע</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -13893,7 +13889,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>ראמה</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -13923,7 +13919,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -13953,7 +13949,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -13983,7 +13979,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>צפת - נוף כנרת</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -14013,7 +14009,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -14033,15 +14029,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -14061,15 +14059,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>missile_only</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -14097,7 +14097,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -14125,7 +14125,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14153,12 +14153,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -14173,22 +14173,20 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F460" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -14203,22 +14201,20 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F461" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -14233,22 +14229,20 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F462" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -14263,22 +14257,20 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F463" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -14293,22 +14285,20 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F464" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>HaAmakim</t>
+          <t>Upper Galilee</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -14323,17 +14313,15 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F465" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>משהד</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -14363,7 +14351,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -14393,7 +14381,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -14453,7 +14441,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -14483,7 +14471,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -14513,7 +14501,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>קריית טבעון - בית זייד</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14543,7 +14531,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -14573,7 +14561,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -14603,7 +14591,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -14633,7 +14621,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>שער העמקים</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14663,7 +14651,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>כפר תקווה</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -14693,7 +14681,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>אלונים</t>
+          <t>ראס עלי</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -14723,7 +14711,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>נופית</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -14753,7 +14741,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -14783,7 +14771,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>כפר תקווה</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -14813,7 +14801,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>כפר ח'וואלד</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -14843,7 +14831,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>אורנים</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -14873,7 +14861,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -14903,7 +14891,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -14933,7 +14921,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>בסמת טבעון</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -14963,7 +14951,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>קריית טבעון - בית זייד</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -14993,7 +14981,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -15023,7 +15011,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -15053,7 +15041,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>נופית</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -15083,7 +15071,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -15113,7 +15101,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -15143,7 +15131,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -15173,7 +15161,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15203,7 +15191,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>אורנים</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -15233,7 +15221,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>כפר ח'וואלד</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -15263,7 +15251,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -15293,7 +15281,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -15323,7 +15311,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>שער העמקים</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -15353,7 +15341,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -15383,7 +15371,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -15413,7 +15401,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -15443,7 +15431,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -15473,7 +15461,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -15503,7 +15491,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -15533,7 +15521,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>אלונים</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -15563,7 +15551,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -15593,7 +15581,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -15623,7 +15611,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -15653,7 +15641,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -15683,7 +15671,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -15713,7 +15701,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -15743,7 +15731,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -15773,7 +15761,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -15803,7 +15791,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -15863,7 +15851,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>ראס עלי</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -15893,7 +15881,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>מרכז חבר</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -15917,13 +15905,13 @@
         </is>
       </c>
       <c r="F518" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>יזרעאל</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -15947,13 +15935,13 @@
         </is>
       </c>
       <c r="F519" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -15977,13 +15965,13 @@
         </is>
       </c>
       <c r="F520" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>בסמת טבעון</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -16007,7 +15995,7 @@
         </is>
       </c>
       <c r="F521" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="522">
@@ -16037,13 +16025,13 @@
         </is>
       </c>
       <c r="F522" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -16067,13 +16055,13 @@
         </is>
       </c>
       <c r="F523" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -16103,7 +16091,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -16133,7 +16121,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>מרחביה מושב</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -16163,7 +16151,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -16193,7 +16181,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>עפולה</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -16223,7 +16211,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>סולם</t>
+          <t>רמת צבי</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -16253,7 +16241,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>כפר ח'וואלד</t>
+          <t>אחוזת ברק</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -16283,7 +16271,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>מגן שאול</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -16313,7 +16301,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>גן נר</t>
+          <t>נורית</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -16343,7 +16331,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבואות הגלבוע</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -16373,7 +16361,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>אורנים</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -16403,7 +16391,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>סנדלה</t>
+          <t>ישובי יעל</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -16433,7 +16421,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -16463,7 +16451,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -16493,7 +16481,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -16523,7 +16511,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -16553,7 +16541,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>קריית טבעון - בית זייד</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -16583,7 +16571,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>נורית</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -16613,7 +16601,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -16643,7 +16631,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>היוגב</t>
+          <t>מגן שאול</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -16673,7 +16661,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>דברת</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -16703,7 +16691,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -16733,7 +16721,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>מגדל העמק</t>
+          <t>דחי</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -16763,7 +16751,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>רם און</t>
+          <t>כפר יחזקאל</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -16793,7 +16781,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -16823,7 +16811,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>כפר יחזקאל</t>
+          <t>נין</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -16853,7 +16841,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>אזור תעשייה מבואות הגלבוע</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -16883,7 +16871,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>מרחביה קיבוץ</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -16913,7 +16901,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>כפר מצר</t>
+          <t>כפר ברוך</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -16943,7 +16931,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>אלונים</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -16973,7 +16961,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>נופית</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -17003,7 +16991,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>סואעד חמירה</t>
+          <t>קבוצת גבע</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -17033,7 +17021,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -17063,7 +17051,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>עין דור</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -17093,7 +17081,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -17123,7 +17111,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>כפר מצר</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -17153,7 +17141,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>דחי</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -17183,7 +17171,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -17213,7 +17201,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>מרחביה מושב</t>
+          <t>דברת</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -17243,7 +17231,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>מוקיבלה</t>
+          <t>גזית</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -17273,7 +17261,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>משהד</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -17303,7 +17291,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>עין דור</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -17333,7 +17321,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>מגדל העמק</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -17363,7 +17351,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>אחוזת ברק</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -17393,7 +17381,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר ברוך</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17423,7 +17411,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>ראס עלי</t>
+          <t>סולם</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -17453,7 +17441,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17483,7 +17471,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>כפר קיש</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -17513,7 +17501,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -17543,7 +17531,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>מתחם סקי גלבוע</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -17573,7 +17561,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -17603,7 +17591,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>כפר תקווה</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -17633,7 +17621,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>מוקיבלה</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -17663,7 +17651,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>אורנים</t>
+          <t>טמרה בגלבוע</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -17693,7 +17681,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>גזית</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -17723,7 +17711,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>כפר ברוך</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -17753,7 +17741,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>ישובי אומן</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -17783,7 +17771,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>בסמת טבעון</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -17813,7 +17801,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>טמרה בגלבוע</t>
+          <t>היוגב</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -17843,7 +17831,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>נאעורה</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -17873,7 +17861,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>מרחביה קיבוץ</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -17903,7 +17891,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>עפולה</t>
+          <t>מרכז חבר</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -17933,7 +17921,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>גן נר</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -17963,7 +17951,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>גדעונה</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -17993,7 +17981,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>קבוצת גבע</t>
+          <t>רם און</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18023,7 +18011,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>שער העמקים</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18053,7 +18041,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>רמת צבי</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18083,7 +18071,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>נאעורה</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18113,7 +18101,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>כפר קיש</t>
+          <t>ראס עלי</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18143,7 +18131,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>סנדלה</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18173,7 +18161,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18203,7 +18191,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>גדעונה</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18233,7 +18221,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>בסמת טבעון</t>
+          <t>כפר תקווה</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18263,7 +18251,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>כפר ח'וואלד</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18293,7 +18281,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>אזור תעשייה אלון התבור</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -18323,7 +18311,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18353,7 +18341,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>אזור תעשייה אלון התבור</t>
+          <t>קריית טבעון - בית זייד</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18383,7 +18371,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18413,7 +18401,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>שער העמקים</t>
+          <t>נופית</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -18443,7 +18431,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>נין</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -18473,7 +18461,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>תחנת רכבת כפר ברוך</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18503,7 +18491,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -18533,7 +18521,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>ישובי יעל</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -18563,7 +18551,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18593,7 +18581,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>ישובי אומן</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -18623,7 +18611,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>מתחם סקי גלבוע</t>
+          <t>אלונים</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18653,17 +18641,17 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר יהושוע</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -18677,23 +18665,23 @@
         </is>
       </c>
       <c r="F610" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>יזרעאל</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -18707,23 +18695,23 @@
         </is>
       </c>
       <c r="F611" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -18737,23 +18725,23 @@
         </is>
       </c>
       <c r="F612" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>סואעד חמירה</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -18767,23 +18755,23 @@
         </is>
       </c>
       <c r="F613" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>גן השומרון</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -18797,23 +18785,23 @@
         </is>
       </c>
       <c r="F614" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Menashe</t>
+          <t>HaAmakim</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Galilee</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -18827,13 +18815,13 @@
         </is>
       </c>
       <c r="F615" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -18863,7 +18851,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>נמל קיסריה</t>
+          <t>תחנת רכבת כפר יהושוע</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -18893,7 +18881,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -18923,7 +18911,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -18953,7 +18941,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -18983,7 +18971,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19013,7 +19001,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19043,7 +19031,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -19073,7 +19061,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19103,7 +19091,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19133,7 +19121,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19163,7 +19151,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19193,7 +19181,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19223,7 +19211,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19253,7 +19241,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19283,7 +19271,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -19313,7 +19301,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>גן השומרון</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19343,7 +19331,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>עין עירון</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19373,7 +19361,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -19403,7 +19391,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>חדרה - נווה חיים</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19433,7 +19421,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19463,7 +19451,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19493,7 +19481,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -19523,7 +19511,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>חדרה - נווה חיים</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19553,7 +19541,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19583,7 +19571,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>עין עירון</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19613,7 +19601,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -19643,7 +19631,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -19673,7 +19661,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19703,7 +19691,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19733,7 +19721,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19763,7 +19751,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>נמל קיסריה</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -19793,7 +19781,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר יהושוע</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19817,13 +19805,13 @@
         </is>
       </c>
       <c r="F648" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19847,13 +19835,13 @@
         </is>
       </c>
       <c r="F649" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19877,13 +19865,13 @@
         </is>
       </c>
       <c r="F650" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19907,13 +19895,13 @@
         </is>
       </c>
       <c r="F651" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>גן השומרון</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -19937,13 +19925,13 @@
         </is>
       </c>
       <c r="F652" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -19967,13 +19955,13 @@
         </is>
       </c>
       <c r="F653" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -20003,7 +19991,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>נמל קיסריה</t>
+          <t>תחנת רכבת כפר יהושוע</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -20033,7 +20021,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -20063,7 +20051,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -20093,7 +20081,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -20123,7 +20111,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -20153,7 +20141,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -20183,7 +20171,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -20213,7 +20201,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -20243,7 +20231,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -20273,7 +20261,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -20303,7 +20291,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -20333,7 +20321,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -20363,7 +20351,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -20393,7 +20381,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -20423,7 +20411,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -20453,7 +20441,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>גן השומרון</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -20483,7 +20471,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>עין עירון</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -20513,7 +20501,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -20543,7 +20531,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>חדרה - נווה חיים</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -20573,7 +20561,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -20603,7 +20591,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -20633,7 +20621,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -20663,7 +20651,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>חדרה - נווה חיים</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -20693,7 +20681,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -20723,7 +20711,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>עין עירון</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -20753,7 +20741,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -20783,7 +20771,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -20813,7 +20801,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -20843,7 +20831,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -20873,7 +20861,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -20903,7 +20891,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>נמל קיסריה</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -20933,17 +20921,17 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>מבוא חמה</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
@@ -20957,23 +20945,23 @@
         </is>
       </c>
       <c r="F686" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>אניעם</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
@@ -20987,23 +20975,23 @@
         </is>
       </c>
       <c r="F687" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>תל קציר</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
@@ -21017,23 +21005,23 @@
         </is>
       </c>
       <c r="F688" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>קצרין</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
@@ -21047,23 +21035,23 @@
         </is>
       </c>
       <c r="F689" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>מעלה גמלא</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -21077,23 +21065,23 @@
         </is>
       </c>
       <c r="F690" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>חספין</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Southern Golan</t>
+          <t>Menashe</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -21107,13 +21095,13 @@
         </is>
       </c>
       <c r="F691" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>אשדות יעקב</t>
+          <t>קשת</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -21143,7 +21131,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>מסדה</t>
+          <t>אניעם</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -21173,7 +21161,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>קדמת צבי</t>
+          <t>צמח</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -21203,7 +21191,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>רמות</t>
+          <t>שער הגולן</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -21263,7 +21251,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>רמת מגשימים</t>
+          <t>יונתן</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -21293,7 +21281,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>גשור</t>
+          <t>מסדה</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -21323,7 +21311,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>חד נס</t>
+          <t>עין גב</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -21353,7 +21341,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>קצרין - אזור תעשייה</t>
+          <t>נטור</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -21383,7 +21371,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>אלמגור</t>
+          <t>מעלה גמלא</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -21413,7 +21401,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>אלוני הבשן</t>
+          <t>אפיק</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -21443,7 +21431,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>קשת</t>
+          <t>אשדות יעקב</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -21473,7 +21461,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>נוב</t>
+          <t>חספין</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -21503,7 +21491,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>שער הגולן</t>
+          <t>גשור</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -21533,7 +21521,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>האון</t>
+          <t>רמות</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -21563,7 +21551,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>בני יהודה וגבעת יואב</t>
+          <t>האון</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -21593,7 +21581,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>אזור תעשייה בני יהודה</t>
+          <t>נאות גולן</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -21623,7 +21611,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>כפר חרוב</t>
+          <t>מעגן</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -21653,7 +21641,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>חמת גדר</t>
+          <t>תל קציר</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -21683,7 +21671,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>נטור</t>
+          <t>נוב</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -21713,7 +21701,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>כנף</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -21743,7 +21731,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>עין גב</t>
+          <t>קצרין - אזור תעשייה</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -21803,7 +21791,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>צמח</t>
+          <t>בני יהודה וגבעת יואב</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -21833,7 +21821,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>יונתן</t>
+          <t>רמת מגשימים</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -21863,7 +21851,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>מעגן</t>
+          <t>אלוני הבשן</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -21893,7 +21881,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>אפיק</t>
+          <t>אלמגור</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -21923,7 +21911,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>נאות גולן</t>
+          <t>אזור תעשייה בני יהודה</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -21983,7 +21971,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>צמח</t>
+          <t>כפר חרוב</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -22003,25 +21991,27 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F721" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F721" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>חיפה - בת גלים ק.אליעזר</t>
+          <t>חד נס</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -22041,17 +22031,17 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>חיפה - מפרץ</t>
+          <t>קדמת צבי</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -22071,17 +22061,17 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>כפר גלים</t>
+          <t>כנף</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -22101,17 +22091,17 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>חיפה - קריית חיים ושמואל</t>
+          <t>חמת גדר</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -22131,17 +22121,17 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>אושה</t>
+          <t>מבוא חמה</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -22161,17 +22151,17 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>כפר חסידים</t>
+          <t>צמח</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -22181,27 +22171,25 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F727" t="n">
-        <v>240</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>קצרין</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -22211,27 +22199,25 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F728" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>קדמת צבי</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -22241,27 +22227,25 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F729" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>יגור</t>
+          <t>קצרין - אזור תעשייה</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>HaMifratz (The Bay)</t>
+          <t>Southern Golan</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -22271,17 +22255,15 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F730" t="n">
-        <v>240</v>
-      </c>
+          <t>missile_only</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr"/>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>קריית אתא</t>
+          <t>איבטין</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -22311,7 +22293,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>חיפה - נווה שאנן ורמות כרמל</t>
+          <t>כפר גלים</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -22341,7 +22323,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>קריית ים</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -22371,7 +22353,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>החותרים</t>
+          <t>אזור תעשייה קריית ביאליק</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -22401,7 +22383,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>קריית מוצקין</t>
+          <t>קריית ביאליק</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -22431,7 +22413,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>טירת כרמל</t>
+          <t>קריית מוצקין</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -22461,7 +22443,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>חיפה - קריית חיים ושמואל</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -22491,7 +22473,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>חיפה - מערב</t>
+          <t>חיפה - בת גלים ק.אליעזר</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -22521,7 +22503,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>טירת כרמל</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -22551,7 +22533,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>כפר ביאליק</t>
+          <t>אזור תעשייה ניר עציון</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -22611,7 +22593,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>אזור תעשייה ניר עציון</t>
+          <t>יגור</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -22641,7 +22623,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>בית עלמין תל רגב</t>
+          <t>קריית אתא</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -22671,7 +22653,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>איבטין</t>
+          <t>כפר ביאליק</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -22701,7 +22683,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>רמת יוחנן</t>
+          <t>חיפה - מפרץ</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -22731,7 +22713,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>חיפה - בת גלים ק.אליעזר</t>
+          <t>חיפה - מערב</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -22755,13 +22737,13 @@
         </is>
       </c>
       <c r="F746" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>חיפה - מפרץ</t>
+          <t>בית עלמין תל רגב</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -22785,13 +22767,13 @@
         </is>
       </c>
       <c r="F747" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>כפר גלים</t>
+          <t>החותרים</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -22815,13 +22797,13 @@
         </is>
       </c>
       <c r="F748" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>חיפה - קריית חיים ושמואל</t>
+          <t>אושה</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -22845,13 +22827,13 @@
         </is>
       </c>
       <c r="F749" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>אושה</t>
+          <t>חיפה - נווה שאנן ורמות כרמל</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -22875,13 +22857,13 @@
         </is>
       </c>
       <c r="F750" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>כפר חסידים</t>
+          <t>קריית ים</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -22905,13 +22887,13 @@
         </is>
       </c>
       <c r="F751" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>כפר חסידים</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -22935,13 +22917,13 @@
         </is>
       </c>
       <c r="F752" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>רמת יוחנן</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -22965,13 +22947,13 @@
         </is>
       </c>
       <c r="F753" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>יגור</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -22995,13 +22977,13 @@
         </is>
       </c>
       <c r="F754" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>קריית אתא</t>
+          <t>איבטין</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -23031,7 +23013,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>חיפה - נווה שאנן ורמות כרמל</t>
+          <t>כפר גלים</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -23061,7 +23043,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>קריית ים</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -23091,7 +23073,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>החותרים</t>
+          <t>אזור תעשייה קריית ביאליק</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -23121,7 +23103,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>קריית מוצקין</t>
+          <t>קריית ביאליק</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -23151,7 +23133,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>טירת כרמל</t>
+          <t>קריית מוצקין</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -23181,7 +23163,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>חיפה - קריית חיים ושמואל</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -23211,7 +23193,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>חיפה - מערב</t>
+          <t>חיפה - בת גלים ק.אליעזר</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -23241,7 +23223,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>טירת כרמל</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -23271,7 +23253,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>כפר ביאליק</t>
+          <t>אזור תעשייה ניר עציון</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -23331,7 +23313,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>אזור תעשייה ניר עציון</t>
+          <t>יגור</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -23361,7 +23343,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>בית עלמין תל רגב</t>
+          <t>קריית אתא</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -23391,7 +23373,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>איבטין</t>
+          <t>כפר ביאליק</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -23421,7 +23403,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>רמת יוחנן</t>
+          <t>חיפה - מפרץ</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -23451,12 +23433,12 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>בת שלמה</t>
+          <t>חיפה - מערב</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -23475,18 +23457,18 @@
         </is>
       </c>
       <c r="F770" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>בית עלמין תל רגב</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -23505,18 +23487,18 @@
         </is>
       </c>
       <c r="F771" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>עופר</t>
+          <t>החותרים</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -23535,18 +23517,18 @@
         </is>
       </c>
       <c r="F772" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>גבע כרמל</t>
+          <t>אושה</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -23565,18 +23547,18 @@
         </is>
       </c>
       <c r="F773" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>הבונים</t>
+          <t>חיפה - נווה שאנן ורמות כרמל</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -23595,18 +23577,18 @@
         </is>
       </c>
       <c r="F774" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>עין חוד</t>
+          <t>קריית ים</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -23625,18 +23607,18 @@
         </is>
       </c>
       <c r="F775" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>גבעת וולפסון</t>
+          <t>כפר חסידים</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -23655,18 +23637,18 @@
         </is>
       </c>
       <c r="F776" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>מאיר שפיה</t>
+          <t>רמת יוחנן</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -23685,18 +23667,18 @@
         </is>
       </c>
       <c r="F777" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>בית אורן</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>HaCarmel</t>
+          <t>HaMifratz (The Bay)</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -23715,13 +23697,13 @@
         </is>
       </c>
       <c r="F778" t="n">
-        <v>240</v>
+        <v>360</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>מגדים</t>
+          <t>דלית אל כרמל</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -23751,7 +23733,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>פוריידיס</t>
+          <t>עספיא</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -23781,7 +23763,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>עספיא</t>
+          <t>פוריידיס</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -23811,7 +23793,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>עתלית</t>
+          <t>צרופה</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -23841,7 +23823,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>עין הוד</t>
+          <t>בת שלמה</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -23871,7 +23853,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>בית צבי</t>
+          <t>גבעת וולפסון</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -23901,7 +23883,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>צרופה</t>
+          <t>עין הוד</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -23931,7 +23913,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>דלית אל כרמל</t>
+          <t>עתלית</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -23961,7 +23943,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>בית סוהר קישון</t>
+          <t>בית צבי</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -23991,7 +23973,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>נווה ים</t>
+          <t>בית סוהר קישון</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -24021,7 +24003,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>עין איילה</t>
+          <t>מגדים</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -24051,7 +24033,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>בת שלמה</t>
+          <t>בית אורן</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -24075,13 +24057,13 @@
         </is>
       </c>
       <c r="F790" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>גבע כרמל</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -24105,13 +24087,13 @@
         </is>
       </c>
       <c r="F791" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>עופר</t>
+          <t>מאיר שפיה</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -24135,13 +24117,13 @@
         </is>
       </c>
       <c r="F792" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>גבע כרמל</t>
+          <t>נווה ים</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -24165,13 +24147,13 @@
         </is>
       </c>
       <c r="F793" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>הבונים</t>
+          <t>עופר</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -24195,7 +24177,7 @@
         </is>
       </c>
       <c r="F794" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="795">
@@ -24225,13 +24207,13 @@
         </is>
       </c>
       <c r="F795" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>גבעת וולפסון</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -24255,13 +24237,13 @@
         </is>
       </c>
       <c r="F796" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>מאיר שפיה</t>
+          <t>הבונים</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -24285,13 +24267,13 @@
         </is>
       </c>
       <c r="F797" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>בית אורן</t>
+          <t>עין איילה</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -24315,13 +24297,13 @@
         </is>
       </c>
       <c r="F798" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>מגדים</t>
+          <t>דלית אל כרמל</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -24351,7 +24333,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>פוריידיס</t>
+          <t>עספיא</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -24381,7 +24363,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>עספיא</t>
+          <t>פוריידיס</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -24411,7 +24393,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>עתלית</t>
+          <t>צרופה</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -24441,7 +24423,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>עין הוד</t>
+          <t>בת שלמה</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -24471,7 +24453,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>בית צבי</t>
+          <t>גבעת וולפסון</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -24501,7 +24483,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>צרופה</t>
+          <t>עין הוד</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -24531,7 +24513,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>דלית אל כרמל</t>
+          <t>עתלית</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -24561,7 +24543,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>בית סוהר קישון</t>
+          <t>בית צבי</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -24591,7 +24573,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>נווה ים</t>
+          <t>בית סוהר קישון</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -24621,7 +24603,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>עין איילה</t>
+          <t>מגדים</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -24651,17 +24633,17 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>בוקעתא</t>
+          <t>בית אורן</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
@@ -24671,25 +24653,27 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F810" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F810" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>עין זיוון</t>
+          <t>גבע כרמל</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
@@ -24699,25 +24683,27 @@
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F811" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F811" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>עין קנייא</t>
+          <t>מאיר שפיה</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
@@ -24727,25 +24713,27 @@
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F812" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F812" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>מסעדה</t>
+          <t>נווה ים</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -24755,25 +24743,27 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F813" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F813" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>מרום גולן</t>
+          <t>עופר</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -24783,25 +24773,27 @@
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F814" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F814" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>נמרוד</t>
+          <t>עין חוד</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -24811,25 +24803,27 @@
       </c>
       <c r="E815" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F815" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F815" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>קלע אלון</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -24839,25 +24833,27 @@
       </c>
       <c r="E816" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F816" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F816" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>שעל</t>
+          <t>הבונים</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
@@ -24867,25 +24863,27 @@
       </c>
       <c r="E817" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F817" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F817" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>רמת טראמפ</t>
+          <t>עין איילה</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Northern Golan</t>
+          <t>HaCarmel</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Golan</t>
+          <t>Haifa Area</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -24895,10 +24893,12 @@
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>pre_only</t>
-        </is>
-      </c>
-      <c r="F818" t="inlineStr"/>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F818" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -24931,7 +24931,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>מג'דל שמס</t>
+          <t>עין קנייא</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -24959,7 +24959,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>אודם</t>
+          <t>אורטל</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -24987,7 +24987,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>אורטל</t>
+          <t>קלע אלון</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -25015,17 +25015,17 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>מג'דל שמס</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D823" t="inlineStr">
@@ -25043,17 +25043,17 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>בוקעתא</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -25071,17 +25071,17 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>מרום גולן</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D825" t="inlineStr">
@@ -25099,17 +25099,17 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>מסעדה</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D826" t="inlineStr">
@@ -25127,17 +25127,17 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>קציר</t>
+          <t>שעל</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
@@ -25155,17 +25155,17 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>נמרוד</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -25183,17 +25183,17 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>עין זיוון</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D829" t="inlineStr">
@@ -25211,17 +25211,17 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>אודם</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D830" t="inlineStr">
@@ -25239,17 +25239,17 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>רמת טראמפ</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Wadi Ara</t>
+          <t>Northern Golan</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>Haifa Area</t>
+          <t>Golan</t>
         </is>
       </c>
       <c r="D831" t="inlineStr">
@@ -25267,7 +25267,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -25295,7 +25295,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -25323,7 +25323,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -25351,7 +25351,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -25379,7 +25379,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>מעלה עירון</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -25407,7 +25407,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -25435,7 +25435,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>באקה אל גרבייה</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -25463,7 +25463,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -25491,7 +25491,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -25519,7 +25519,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -25547,7 +25547,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>באקה אל גרבייה</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -25575,7 +25575,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -25603,7 +25603,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -25631,7 +25631,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>קציר</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -25659,7 +25659,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -25687,7 +25687,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -25715,7 +25715,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>עין השופט</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -25743,7 +25743,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -25771,7 +25771,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -25799,7 +25799,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -25827,7 +25827,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>עין אל סהלה</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -25855,7 +25855,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -25883,7 +25883,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>עין העמק</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -25911,7 +25911,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>מצר</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -25931,17 +25931,15 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F855" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>מדרך עוז</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -25961,17 +25959,15 @@
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F856" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr"/>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>אום אל פחם</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -25991,17 +25987,15 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F857" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>ברטעה</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -26021,17 +26015,15 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F858" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>קציר</t>
+          <t>מצפה אילן</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -26051,17 +26043,15 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F859" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>מעלה עירון</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -26081,17 +26071,15 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F860" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>מועאוויה</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -26111,17 +26099,15 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F861" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>רגבים</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -26141,17 +26127,15 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F862" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>גלעד</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -26171,17 +26155,15 @@
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>paired_missile</t>
-        </is>
-      </c>
-      <c r="F863" t="n">
-        <v>300</v>
-      </c>
+          <t>pre_only</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -26211,7 +26193,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -26241,7 +26223,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -26271,7 +26253,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -26301,7 +26283,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>מעלה עירון</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -26331,7 +26313,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -26361,7 +26343,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>באקה אל גרבייה</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -26391,7 +26373,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -26421,7 +26403,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -26451,7 +26433,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -26481,7 +26463,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>באקה אל גרבייה</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -26511,7 +26493,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -26541,7 +26523,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -26571,7 +26553,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>קציר</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -26601,7 +26583,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -26631,7 +26613,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -26661,7 +26643,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>עין השופט</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -26691,7 +26673,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -26721,7 +26703,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -26751,7 +26733,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -26781,7 +26763,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>עין אל סהלה</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -26811,7 +26793,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -26841,7 +26823,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>עין העמק</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -26865,6 +26847,276 @@
         </is>
       </c>
       <c r="F886" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>מצר</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F887" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>מדרך עוז</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F888" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>אום אל פחם</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F889" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>ברטעה</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F890" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>מצפה אילן</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F891" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>מעלה עירון</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F892" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>מועאוויה</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F893" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>רגבים</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F894" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>גלעד</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Wadi Ara</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Haifa Area</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>paired_missile</t>
+        </is>
+      </c>
+      <c r="F895" t="n">
         <v>300</v>
       </c>
     </row>

--- a/mismatches.xlsx
+++ b/mismatches.xlsx
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>להבות הבשן</t>
+          <t>איזור תעשייה מילואות צפון</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>גונן</t>
+          <t>להבות הבשן</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>איזור תעשייה מילואות צפון</t>
+          <t>בצת</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>בצת</t>
+          <t>ראש הנקרה</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ראש הנקרה</t>
+          <t>חוף בצת</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>חוף בצת</t>
+          <t>גונן</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>אביבים</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>אביבים</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>צבעון</t>
+          <t>יראון</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>יראון</t>
+          <t>צבעון</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>קריית שמונה</t>
+          <t>יפתח</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>מנרה</t>
+          <t>קריית שמונה</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1069,7 +1069,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>יפתח</t>
+          <t>מנרה</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1097,7 +1097,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>כפר יובל</t>
+          <t>מעיין ברוך</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>משגב עם</t>
+          <t>יפתח</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>יפתח</t>
+          <t>כפר יובל</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1181,7 +1181,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>מעיין ברוך</t>
+          <t>משגב עם</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ג'ש - גוש חלב</t>
+          <t>אזור תעשייה רמת דלתון</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>אזור תעשייה רמת דלתון</t>
+          <t>כרם בן זמרה</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>דלתון</t>
+          <t>ג'ש - גוש חלב</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>כרם בן זמרה</t>
+          <t>דלתון</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>מרכז אזורי מבואות חרמון</t>
+          <t>רמות נפתלי</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>רמות נפתלי</t>
+          <t>יפתח</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1377,7 +1377,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>יפתח</t>
+          <t>מרכז אזורי מבואות חרמון</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1461,7 +1461,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>לבון</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>אליפלט</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>בית העלמין החדש עכו</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>מרכז אזורי רמת כורזים</t>
+          <t>ראש פינה</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1581,7 +1581,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>כפר מסריק</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1641,7 +1641,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>גדות</t>
+          <t>אחיהוד</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>מזרעה</t>
+          <t>ראמה</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>כישור</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>מירון</t>
+          <t>כורזים ורד הגליל</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>אזור תעשייה כרמיאל</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ג'דידה מכר</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ראש פינה</t>
+          <t>בית העלמין החדש עכו</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>כחל</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1881,7 +1881,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>שפר</t>
+          <t>נחף</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>עכו - אזור תעשייה</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>קדרים</t>
+          <t>איילת השחר</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>כסרא סמיע</t>
+          <t>דיר אל-אסד</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2001,7 +2001,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>עמקה</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2031,7 +2031,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>כרמיאל</t>
+          <t>בית ג'אן</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2061,7 +2061,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>חרשים</t>
+          <t>עכו</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2091,7 +2091,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>עמקה</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>כפר יאסיף</t>
+          <t>בוסתן הגליל</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>עמיעד</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>אמירים</t>
+          <t>כרכום</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2211,7 +2211,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>שבי ציון</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>לוחמי הגטאות</t>
+          <t>מירון</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>בוסתן הגליל</t>
+          <t>לבון</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>איילת השחר</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2331,7 +2331,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>רגבה</t>
+          <t>לוחמי הגטאות</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>בית ג'אן</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>שמרת</t>
+          <t>עמוקה</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>שייח' דנון</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>הר חלוץ</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>דיר אל-אסד</t>
+          <t>חולתה</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2511,7 +2511,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>אפק</t>
+          <t>פרוד</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2541,7 +2541,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>אזור תעשייה שער נעמן</t>
+          <t>כרמיאל</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>עין המפרץ</t>
+          <t>עין אל אסד</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>מזרעה</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2631,7 +2631,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>פרוד</t>
+          <t>אזור תעשייה שער נעמן</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2661,7 +2661,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>אמנון</t>
+          <t>קדרים</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>כפר הנשיא</t>
+          <t>כפר יאסיף</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>יסעור</t>
+          <t>גדות</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>שדה אליעזר</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2781,7 +2781,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>שייח' דנון</t>
+          <t>עכו - רמות ים</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2811,7 +2811,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>אבו סנאן</t>
+          <t>אליפלט</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2841,7 +2841,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>מנחת מחניים</t>
+          <t>ג'וליס</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2871,7 +2871,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>שזור</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2901,7 +2901,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>טל - אל</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2931,7 +2931,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>כליל</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2961,7 +2961,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ג'וליס</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>נחף</t>
+          <t>ג'דידה מכר</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>עמוקה</t>
+          <t>צפת - נוף כנרת</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3051,7 +3051,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>כמון - כמאנה מזרחית</t>
+          <t>שמרת</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3081,7 +3081,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>כחל</t>
+          <t>אזור תעשייה כרמיאל</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3111,7 +3111,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>כפר שמאי</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3141,7 +3141,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>כורזים ורד הגליל</t>
+          <t>טובא זנגריה</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>מחניים</t>
+          <t>אבו סנאן</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3201,7 +3201,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>בית העמק</t>
+          <t>כמון - כמאנה מזרחית</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3231,7 +3231,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>עכו</t>
+          <t>אשרת</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>עכו - רמות ים</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>יסוד המעלה</t>
+          <t>אמנון</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>כרכום</t>
+          <t>מרכז אזורי רמת כורזים</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3351,7 +3351,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>משמר הירדן</t>
+          <t>אמירים</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3381,7 +3381,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>כפר שמאי</t>
+          <t>חרשים</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3411,7 +3411,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>שדה אליעזר</t>
+          <t>מחניים</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3441,7 +3441,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>אחיהוד</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>טל - אל</t>
+          <t>שפר</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3501,7 +3501,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>עמיעד</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3531,7 +3531,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>חמדת ימים</t>
+          <t>בענה</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>אזור תעשייה צ.ח.ר</t>
+          <t>כליל</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>אשרת</t>
+          <t>יסוד המעלה</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ירכא</t>
+          <t>יסעור</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3651,7 +3651,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>שזור</t>
+          <t>אזור תעשייה צ.ח.ר</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3681,7 +3681,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>צפת - נוף כנרת</t>
+          <t>הר חלוץ</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3711,7 +3711,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>כישור</t>
+          <t>רגבה</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>עין אל אסד</t>
+          <t>כפר הנשיא</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3771,7 +3771,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>אפק</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3801,7 +3801,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>נס עמים</t>
+          <t>כפר מסריק</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3831,7 +3831,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>חולתה</t>
+          <t>כסרא סמיע</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>בענה</t>
+          <t>בית העמק</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3891,7 +3891,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>טובא זנגריה</t>
+          <t>סאג'ור</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>סאג'ור</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3951,7 +3951,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>שבי ציון</t>
+          <t>חמדת ימים</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3981,7 +3981,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>עכו - אזור תעשייה</t>
+          <t>ירכא</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4011,7 +4011,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ראמה</t>
+          <t>חצור הגלילית</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4041,7 +4041,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ביריה</t>
+          <t>מנחת מחניים</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>חצור הגלילית</t>
+          <t>נס עמים</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4101,7 +4101,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>עין המפרץ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>משמר הירדן</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4189,7 +4189,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>מרכז אזורי מרום גליל</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>בר יוחאי</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4245,7 +4245,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>מרכז אזורי מרום גליל</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4273,7 +4273,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>בר יוחאי</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ביריה</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>ביריה</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4441,7 +4441,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>אור הגנוז</t>
+          <t>ספסופה - כפר חושן</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>צפת - עיר</t>
+          <t>צפת - עכברה</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4497,7 +4497,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>קדיתא</t>
+          <t>צפת - עיר</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4525,7 +4525,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>צפת - עכברה</t>
+          <t>אור הגנוז</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ספסופה - כפר חושן</t>
+          <t>קדיתא</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>תובל</t>
+          <t>פלך</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4609,7 +4609,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>מגדל תפן</t>
+          <t>ינוח ג'ת</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4665,7 +4665,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>גיתה</t>
+          <t>מג'דל כרום</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4693,7 +4693,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>דיר אל-אסד</t>
+          <t>תובל</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4749,7 +4749,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>לפידות</t>
+          <t>מגדל תפן</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ינוח ג'ת</t>
+          <t>דיר אל-אסד</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>צורית גילון</t>
+          <t>גיתה</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4833,7 +4833,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>פלך</t>
+          <t>לפידות</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>מג'דל כרום</t>
+          <t>צורית גילון</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4889,7 +4889,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>איבטין</t>
+          <t>יגור</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4919,7 +4919,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>נשר</t>
+          <t>קריית מוצקין</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4949,7 +4949,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>חיפה - בת גלים ק.אליעזר</t>
+          <t>אזור תעשייה קריית ביאליק</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4979,7 +4979,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>כפר חסידים</t>
+          <t>כפר גלים</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5039,7 +5039,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>רמת יוחנן</t>
+          <t>חיפה - מפרץ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5069,7 +5069,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>כפר גלים</t>
+          <t>חיפה - מערב</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>טירת כרמל</t>
+          <t>כפר חסידים</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>בית עלמין תל רגב</t>
+          <t>חיפה - קריית חיים ושמואל</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>החותרים</t>
+          <t>טירת כרמל</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5189,7 +5189,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>כפר ביאליק</t>
+          <t>החותרים</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>חיפה - קריית חיים ושמואל</t>
+          <t>איבטין</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>אזור תעשייה קריית ביאליק</t>
+          <t>רמת יוחנן</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5279,7 +5279,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>יגור</t>
+          <t>כפר המכבי</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>קריית אתא</t>
+          <t>רכסים</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>חיפה - נווה שאנן ורמות כרמל</t>
+          <t>קריית אתא</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5369,7 +5369,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>כפר המכבי</t>
+          <t>קריית ים</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5399,7 +5399,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>חיפה - מפרץ</t>
+          <t>אושה</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5429,7 +5429,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>רכסים</t>
+          <t>חיפה - נווה שאנן ורמות כרמל</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5459,7 +5459,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>אושה</t>
+          <t>קריית ביאליק</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5489,7 +5489,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>קריית ים</t>
+          <t>בית עלמין תל רגב</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>חיפה - מערב</t>
+          <t>נשר</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5549,7 +5549,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>קריית מוצקין</t>
+          <t>חיפה - בת גלים ק.אליעזר</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5579,7 +5579,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>קריית ביאליק</t>
+          <t>כפר ביאליק</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>עתלית</t>
+          <t>עספיא</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>צרופה</t>
+          <t>בית אורן</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5699,7 +5699,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>בית סוהר קישון</t>
+          <t>עופר</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>נווה ים</t>
+          <t>גבע כרמל</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5759,7 +5759,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>בית אורן</t>
+          <t>בית צבי</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5789,7 +5789,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>עין איילה</t>
+          <t>עתלית</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5819,7 +5819,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>עופר</t>
+          <t>מאיר שפיה</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5849,7 +5849,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>גבע כרמל</t>
+          <t>עין כרמל</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5879,7 +5879,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>פוריידיס</t>
+          <t>בית סוהר קישון</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5909,7 +5909,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>עין כרמל</t>
+          <t>גבעת וולפסון</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5939,7 +5939,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>עספיא</t>
+          <t>עין איילה</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5969,7 +5969,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>בית צבי</t>
+          <t>מגדים</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5999,7 +5999,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>גבעת וולפסון</t>
+          <t>עין הוד</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6029,7 +6029,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>הבונים</t>
+          <t>עין חוד</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6059,7 +6059,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>עין חוד</t>
+          <t>דלית אל כרמל</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6089,7 +6089,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>דלית אל כרמל</t>
+          <t>הבונים</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6119,7 +6119,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>מגדים</t>
+          <t>נווה ים</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>מאיר שפיה</t>
+          <t>פוריידיס</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>עין הוד</t>
+          <t>צרופה</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6209,7 +6209,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>בסמת טבעון</t>
+          <t>תמרת</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6239,7 +6239,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>משהד</t>
+          <t>נוף הגליל</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6269,7 +6269,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>אורנים</t>
+          <t>זרזיר</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6299,7 +6299,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>נצרת</t>
+          <t>אזור תעשייה מבואות הגלבוע</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6329,7 +6329,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ראס עלי</t>
+          <t>בית שערים</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>כפר ברוך</t>
+          <t>אלונים</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6389,7 +6389,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>מרחביה מושב</t>
+          <t>נורית</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6419,7 +6419,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>כדורי</t>
+          <t>הושעיה</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6449,7 +6449,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ציפורי</t>
+          <t>קריית טבעון - בית זייד</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6479,7 +6479,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>גבעת אלה</t>
+          <t>דחי</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6509,7 +6509,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>גדעונה</t>
+          <t>יפעת</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6539,7 +6539,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>שדה יעקב</t>
+          <t>כפר החורש</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>בית שערים</t>
+          <t>נאעורה</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6599,7 +6599,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>רם און</t>
+          <t>שמשית</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6659,7 +6659,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ישובי יעל</t>
+          <t>תל עדשים</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6689,7 +6689,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>אכסאל</t>
+          <t>שריד</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>שיבלי אום אלג'נם</t>
+          <t>אילניה</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6749,7 +6749,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>גבת</t>
+          <t>עילוט</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6779,7 +6779,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>גניגר</t>
+          <t>מזרע</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6809,7 +6809,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>חג'אג'רה</t>
+          <t>מתחם סקי גלבוע</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6839,7 +6839,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>קבוצת גבע</t>
+          <t>שער העמקים</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>רמת דוד</t>
+          <t>עפולה</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6929,7 +6929,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>נוף הגליל</t>
+          <t>נצרת</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6959,7 +6959,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>כעביה טבאש</t>
+          <t>אחוזת ברק</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6989,7 +6989,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ישובי אומן</t>
+          <t>ישובי יעל</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>בית לחם הגלילית</t>
+          <t>כפר תבור</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7049,7 +7049,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>מגדל העמק</t>
+          <t>גן נר</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7079,7 +7079,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>כפר ח'וואלד</t>
+          <t>רם און</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7109,7 +7109,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>עפולה</t>
+          <t>דבוריה</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7139,7 +7139,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>סולם</t>
+          <t>תחנת רכבת כפר ברוך</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7169,7 +7169,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>כפר גדעון</t>
+          <t>מרחביה מושב</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>גזית</t>
+          <t>גבעת אלה</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7229,7 +7229,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>זרזיר</t>
+          <t>אזור תעשייה אלון התבור</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7259,7 +7259,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>מגן שאול</t>
+          <t>דברת</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7289,7 +7289,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>אזור תעשייה אלון התבור</t>
+          <t>משהד</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7319,7 +7319,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>היוגב</t>
+          <t>בלפוריה</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>נופית</t>
+          <t>מרחביה קיבוץ</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7379,7 +7379,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>כפר החורש</t>
+          <t>שדה יעקב</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7439,7 +7439,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>קריית טבעון - בית זייד</t>
+          <t>בית לחם הגלילית</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7469,7 +7469,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>מוקיבלה</t>
+          <t>בסמת טבעון</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7499,7 +7499,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>אלונים</t>
+          <t>בית קשת</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7529,7 +7529,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>כפר תבור</t>
+          <t>כפר גדעון</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7559,7 +7559,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>נין</t>
+          <t>אלוני אבא</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>דחי</t>
+          <t>כפר תקווה</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7619,7 +7619,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>אילניה</t>
+          <t>סואעד חמירה</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7649,7 +7649,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>מנשית זבדה</t>
+          <t>כפר ברוך</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>אחוזת ברק</t>
+          <t>ראס עלי</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7709,7 +7709,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>כפר קיש</t>
+          <t>רמת צבי</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7739,7 +7739,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>עדי</t>
+          <t>אורנים</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7769,7 +7769,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>כפר יחזקאל</t>
+          <t>אכסאל</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7799,7 +7799,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>בית קשת</t>
+          <t>מגדל העמק</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7829,7 +7829,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>נורית</t>
+          <t>סולם</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>שמשית</t>
+          <t>כפר יהושע</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>עילוט</t>
+          <t>נין</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7919,7 +7919,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>נאעורה</t>
+          <t>כפר כנא</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7949,7 +7949,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>מזרע</t>
+          <t>נהלל</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7979,7 +7979,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>סואעד חמירה</t>
+          <t>רמת דוד</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8009,7 +8009,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>רמת צבי</t>
+          <t>גדעונה</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8039,7 +8039,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>כפר יהושע</t>
+          <t>כפר ח'וואלד</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8069,7 +8069,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>כפר כנא</t>
+          <t>היוגב</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -8099,7 +8099,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>נהלל</t>
+          <t>יפיע</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8129,7 +8129,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>תמרת</t>
+          <t>כפר יחזקאל</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>מתחם סקי גלבוע</t>
+          <t>כפר מצר</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>עין מאהל</t>
+          <t>מנשית זבדה</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8219,7 +8219,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>שריד</t>
+          <t>אזור תעשייה ציפורית</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8249,7 +8249,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>טמרה בגלבוע</t>
+          <t>נופית</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>אלוני אבא</t>
+          <t>כעביה טבאש</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8309,7 +8309,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>שער העמקים</t>
+          <t>מגן שאול</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>כפר תקווה</t>
+          <t>גזית</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>דבוריה</t>
+          <t>מוקיבלה</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8399,7 +8399,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>הושעיה</t>
+          <t>כדורי</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8429,7 +8429,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>רמת ישי</t>
+          <t>גניגר</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8459,7 +8459,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר ברוך</t>
+          <t>עדי</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8489,7 +8489,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבואות הגלבוע</t>
+          <t>אלון הגליל</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8519,7 +8519,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>מרכז חבר</t>
+          <t>הרדוף</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8549,7 +8549,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>יפיע</t>
+          <t>כפר קיש</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8579,7 +8579,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>הסוללים</t>
+          <t>שדמות דבורה</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ריינה</t>
+          <t>חג'אג'רה</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8639,7 +8639,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>שדמות דבורה</t>
+          <t>ריינה</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>גן נר</t>
+          <t>ישובי אומן</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -8699,7 +8699,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>מרחביה קיבוץ</t>
+          <t>שיבלי אום אלג'נם</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8729,7 +8729,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>דברת</t>
+          <t>טמרה בגלבוע</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>אלון הגליל</t>
+          <t>רמת ישי</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8789,7 +8789,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>בלפוריה</t>
+          <t>ציפורי</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8819,7 +8819,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>אזור תעשייה ציפורית</t>
+          <t>מרכז חבר</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8849,7 +8849,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>תל עדשים</t>
+          <t>הסוללים</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>כפר מצר</t>
+          <t>קבוצת גבע</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8909,7 +8909,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>יפעת</t>
+          <t>גבת</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8939,7 +8939,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>הרדוף</t>
+          <t>עין מאהל</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8969,7 +8969,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>כלנית</t>
+          <t>חנתון</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8999,7 +8999,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>שורשים</t>
+          <t>רקפת</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9029,7 +9029,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>יובלים</t>
+          <t>מע'אר</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>מנוף</t>
+          <t>לוטם וחמדון</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>שפרעם</t>
+          <t>יודפת</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>מורן</t>
+          <t>מנוף</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9149,7 +9149,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>לוטם וחמדון</t>
+          <t>סלמה</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9179,7 +9179,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>בועיינה-נוג'ידאת</t>
+          <t>בית רימון</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9209,7 +9209,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>כפר מנדא</t>
+          <t>מרכז אזורי משגב</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9239,7 +9239,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>אשחר</t>
+          <t>דיר חנא</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9269,7 +9269,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>מרכז אזורי משגב</t>
+          <t>אשחר</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -9299,7 +9299,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>דמיידה</t>
+          <t>רומת אל הייב</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -9329,7 +9329,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ראס אל-עין</t>
+          <t>אעבלין</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -9359,7 +9359,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>קורנית</t>
+          <t>שורשים</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9389,7 +9389,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>יעד</t>
+          <t>מצפה נטופה</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>סלמה</t>
+          <t>חוסנייה</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -9479,7 +9479,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>בית סוהר צלמון</t>
+          <t>שכניה</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -9509,7 +9509,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>כאוכב אבו אלהיג'א</t>
+          <t>כפר חנניה</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -9539,7 +9539,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>שעב</t>
+          <t>ערב אל נעים</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -9569,7 +9569,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>סכנין</t>
+          <t>כפר מנדא</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>מצפה נטופה</t>
+          <t>שפרעם</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -9629,7 +9629,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>אשבל</t>
+          <t>הררית יחד</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -9659,7 +9659,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>עראבה</t>
+          <t>בועיינה-נוג'ידאת</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ביר אלמכסור</t>
+          <t>קורנית</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>טמרה</t>
+          <t>עראבה</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -9749,7 +9749,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>בית רימון</t>
+          <t>חזון</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -9779,7 +9779,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ערב אל נעים</t>
+          <t>שעב</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -9809,7 +9809,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>מע'אר</t>
+          <t>דמיידה</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9839,7 +9839,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>חזון</t>
+          <t>ביר אלמכסור</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9869,7 +9869,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>דיר חנא</t>
+          <t>אבטליון</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -9899,7 +9899,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>רומת אל הייב</t>
+          <t>יעד</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -9929,7 +9929,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>רקפת</t>
+          <t>בית סוהר צלמון</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9959,7 +9959,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>עצמון - שגב</t>
+          <t>אשבל</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9989,7 +9989,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>טפחות</t>
+          <t>כאוכב אבו אלהיג'א</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10019,7 +10019,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>שכניה</t>
+          <t>מעלה צביה</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -10049,7 +10049,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>אבטליון</t>
+          <t>טמרה</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10079,7 +10079,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>מורשת</t>
+          <t>מורן</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -10109,7 +10109,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>חוסנייה</t>
+          <t>כלנית</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>חנתון</t>
+          <t>טורעאן</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10169,7 +10169,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>טורעאן</t>
+          <t>כאבול</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10199,7 +10199,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>יודפת</t>
+          <t>מסד</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>כאבול</t>
+          <t>יובלים</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -10259,7 +10259,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>מעלה צביה</t>
+          <t>מורשת</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -10289,7 +10289,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>אעבלין</t>
+          <t>עצמון - שגב</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -10319,7 +10319,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>כפר חנניה</t>
+          <t>טפחות</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>הררית יחד</t>
+          <t>ראס אל-עין</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -10379,7 +10379,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>מסד</t>
+          <t>סכנין</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>מצפה</t>
+          <t>כינרת קבוצה</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10439,7 +10439,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>אפיקים</t>
+          <t>שדה אילן</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -10469,7 +10469,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>אזור תעשייה בר-לב</t>
+          <t>כפר כמא</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -10499,7 +10499,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>מגדל</t>
+          <t>יבנאל</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -10529,7 +10529,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>כפר זיתים</t>
+          <t>אפיקים</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>יבנאל</t>
+          <t>הודיות</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -10589,7 +10589,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>אזור תעשייה תרדיון</t>
+          <t>פוריה עילית</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>כפר נהר הירדן</t>
+          <t>דגניה א</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -10649,7 +10649,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>אתר ההנצחה גולני</t>
+          <t>כפר זיתים</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -10679,7 +10679,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>פוריה נווה עובד</t>
+          <t>אלומות</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10709,7 +10709,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>טבריה</t>
+          <t>מצפה</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -10739,7 +10739,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>בית ירח</t>
+          <t>ואדי אל חמאם</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>אלומות</t>
+          <t>אזור תעשייה קדמת גליל</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -10799,7 +10799,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>שרונה</t>
+          <t>כפר חיטים</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -10829,7 +10829,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>רביד</t>
+          <t>טבריה</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -10859,7 +10859,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>בית זרע</t>
+          <t>מגדל</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -10889,7 +10889,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>כפר כמא</t>
+          <t>כינרת מושבה</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -10919,7 +10919,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>פוריה כפר עבודה</t>
+          <t>שרונה</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10949,7 +10949,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>אזור תעשייה קדמת גליל</t>
+          <t>חוקוק</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>הודיות</t>
+          <t>פוריה נווה עובד</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>לבנים</t>
+          <t>ארבל</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -11039,7 +11039,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>כינרת קבוצה</t>
+          <t>גינוסר</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -11069,7 +11069,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>כינרת מושבה</t>
+          <t>בית זרע</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11099,7 +11099,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ארבל</t>
+          <t>בית ירח</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11129,7 +11129,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ואדי אל חמאם</t>
+          <t>הזורעים</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11159,7 +11159,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>דגניה א</t>
+          <t>לבנים</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -11189,7 +11189,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>חוקוק</t>
+          <t>אזור תעשייה בר-לב</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -11219,7 +11219,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>שדה אילן</t>
+          <t>פוריה כפר עבודה</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -11249,7 +11249,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>גבעת אבני</t>
+          <t>לביא</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -11279,7 +11279,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>דגניה ב</t>
+          <t>אתר ההנצחה גולני</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -11309,7 +11309,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>לביא</t>
+          <t>רביד</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -11339,7 +11339,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>פוריה עילית</t>
+          <t>גבעת אבני</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -11369,7 +11369,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>הזורעים</t>
+          <t>אזור תעשייה תרדיון</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>כפר חיטים</t>
+          <t>נבי שועייב</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -11429,7 +11429,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>גינוסר</t>
+          <t>כפר נהר הירדן</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -11459,7 +11459,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>נבי שועייב</t>
+          <t>דגניה ב</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -11489,7 +11489,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>בית חנניה</t>
+          <t>אביאל</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -11519,7 +11519,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>גבעת עדה</t>
+          <t>גן השומרון</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -11549,7 +11549,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>כפר פינס</t>
+          <t>מעגן מיכאל</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -11579,7 +11579,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>להבות חביבה</t>
+          <t>כפר פינס</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -11609,7 +11609,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>מעיין צבי</t>
+          <t>חדרה - מרכז</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -11639,7 +11639,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>שער מנשה</t>
+          <t>בי"ס כרמים בנימינה</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -11669,7 +11669,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>קיסריה</t>
+          <t>גן שמואל</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -11699,7 +11699,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>גן השומרון</t>
+          <t>אלוני יצחק</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -11729,7 +11729,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>אזור תעשייה מבוא כרמל</t>
+          <t>ברקאי</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -11759,7 +11759,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>עין עירון</t>
+          <t>אזור תעשייה יקנעם עילית</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -11789,7 +11789,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>עמיקם</t>
+          <t>חדרה - מזרח</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -11819,7 +11819,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>עין שמר</t>
+          <t>תחנת רכבת כפר יהושוע</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -11849,7 +11849,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>מעגן מיכאל</t>
+          <t>שער מנשה</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -11879,7 +11879,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>אזור תעשייה יקנעם עילית</t>
+          <t>אזור תעשייה מבוא כרמל</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -11909,7 +11909,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>אביאל</t>
+          <t>בית חנניה</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>חדרה - נווה חיים</t>
+          <t>שדות ים</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11969,7 +11969,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>בי"ס כרמים בנימינה</t>
+          <t>עמיקם</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -11999,7 +11999,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>שדה יצחק</t>
+          <t>פרדס חנה כרכור</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>משמרות</t>
+          <t>כפר גליקסון</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12059,7 +12059,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ברקאי</t>
+          <t>עין עירון</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12089,7 +12089,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>חדרה - מרכז</t>
+          <t>מתחם שביל התפוזים</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -12119,7 +12119,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>אור עקיבא</t>
+          <t>תלמי אלעזר</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -12149,7 +12149,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>אלוני יצחק</t>
+          <t>מעיין צבי</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -12209,7 +12209,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>חדרה - מזרח</t>
+          <t>חדרה - מערב</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -12239,7 +12239,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>בנימינה</t>
+          <t>גבעת עדה</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -12269,7 +12269,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>ג'סר א-זרקא</t>
+          <t>אור עקיבא</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -12299,7 +12299,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>שדות ים</t>
+          <t>קיסריה</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -12329,7 +12329,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>פרדס חנה כרכור</t>
+          <t>משמרות</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -12359,7 +12359,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>תלמי אלעזר</t>
+          <t>מאור</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -12389,7 +12389,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>גן שמואל</t>
+          <t>שדה יצחק</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -12419,7 +12419,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>מאור</t>
+          <t>זכרון יעקב</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -12449,7 +12449,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>אזור תעשייה קיסריה</t>
+          <t>ג'סר א-זרקא</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -12479,7 +12479,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>מתחם שביל התפוזים</t>
+          <t>בנימינה</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -12509,7 +12509,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>חדרה - מערב</t>
+          <t>עין שמר</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -12539,7 +12539,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>תחנת רכבת כפר יהושוע</t>
+          <t>אזור תעשייה קיסריה</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -12569,7 +12569,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>זכרון יעקב</t>
+          <t>חדרה - נווה חיים</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -12599,7 +12599,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>כפר גליקסון</t>
+          <t>להבות חביבה</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -12741,7 +12741,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>גבעת עוז</t>
+          <t>אל עריאן</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -12771,7 +12771,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>אל עריאן</t>
+          <t>באקה אל גרבייה</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -12801,7 +12801,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>מצר</t>
+          <t>רמות מנשה</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -12831,7 +12831,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ג'ת</t>
+          <t>חריש</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -12861,7 +12861,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>מדרך עוז</t>
+          <t>דליה</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -12891,7 +12891,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>מייסר</t>
+          <t>רמת השופט</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -12921,7 +12921,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>משמר העמק</t>
+          <t>מצר</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -12951,7 +12951,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>מצפה אילן</t>
+          <t>אליקים</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -12981,7 +12981,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>עין העמק</t>
+          <t>מצפה אילן</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13011,7 +13011,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>כפר קרע</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -13041,7 +13041,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>כפר קרע</t>
+          <t>מגל</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -13071,7 +13071,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ברטעה</t>
+          <t>עין השופט</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -13101,7 +13101,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>באקה אל גרבייה</t>
+          <t>אום אל פחם</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -13131,7 +13131,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>חריש</t>
+          <t>יקנעם עילית</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -13191,7 +13191,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>רמות מנשה</t>
+          <t>אום אל קוטוף</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -13221,7 +13221,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>מגל</t>
+          <t>ברטעה</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -13251,7 +13251,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ערערה</t>
+          <t>ג'ת</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -13281,7 +13281,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>עין אל סהלה</t>
+          <t>גלעד</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -13311,7 +13311,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>רמת השופט</t>
+          <t>מדרך עוז</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -13341,7 +13341,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>אום אל קוטוף</t>
+          <t>מועאוויה</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>קציר</t>
+          <t>קיבוץ מגידו</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -13401,7 +13401,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>אליקים</t>
+          <t>מי עמי</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -13431,7 +13431,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>יקנעם המושבה והזורע</t>
+          <t>ערערה</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -13461,7 +13461,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>גלעד</t>
+          <t>יקנעם המושבה והזורע</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -13491,7 +13491,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>מי עמי</t>
+          <t>רגבים</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -13521,7 +13521,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>רגבים</t>
+          <t>קציר</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -13551,7 +13551,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>יקנעם עילית</t>
+          <t>עין אל סהלה</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -13581,7 +13581,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>קיבוץ מגידו</t>
+          <t>גבעת עוז</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -13611,7 +13611,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>עין השופט</t>
+          <t>משמר העמק</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -13641,7 +13641,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>אום אל פחם</t>
+          <t>עין העמק</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -13671,7 +13671,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>מועאוויה</t>
+          <t>מייסר</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -13701,7 +13701,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ביר הדאג'</t>
+          <t>ירוחם</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -13731,7 +13731,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>תל ערד</t>
+          <t>רביבים</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -13761,7 +13761,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>כסייפה</t>
+          <t>ערערה בנגב</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -13791,7 +13791,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>באר מילכה</t>
+          <t>מצפה רמון</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -13821,7 +13821,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>כפר הנוקדים</t>
+          <t>עזוז</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -13851,7 +13851,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ואדי אל נעם דרום</t>
+          <t>באר מילכה</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -13881,7 +13881,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>רביבים</t>
+          <t>מרעית</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -13941,7 +13941,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>עזוז</t>
+          <t>אשלים</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -13971,7 +13971,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>אל פורעה</t>
+          <t>טללים</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -14001,7 +14001,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>קדש ברנע</t>
+          <t>שאנטי במדבר</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>אשלים</t>
+          <t>מרחב עם</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -14061,7 +14061,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>אזור תעשייה רותם</t>
+          <t>ביר הדאג'</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -14091,7 +14091,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>אבו תלול</t>
+          <t>אזור תעשייה רותם</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -14121,7 +14121,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>סעווה</t>
+          <t>כמהין</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -14151,7 +14151,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>רתמים</t>
+          <t>דימונה</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -14181,7 +14181,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>קסר א-סר</t>
+          <t>ערד</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -14211,7 +14211,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>משאבי שדה</t>
+          <t>כפר הנוקדים</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -14241,7 +14241,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ניצנה</t>
+          <t>אל פורעה</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -14271,7 +14271,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>ירוחם</t>
+          <t>סעווה</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -14301,7 +14301,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>דימונה</t>
+          <t>ואדי אל נעם דרום</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -14331,7 +14331,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>טללים</t>
+          <t>אבו תלול</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -14361,7 +14361,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>מדרשת בן גוריון</t>
+          <t>אבו קרינאת</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -14421,7 +14421,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>מצפה רמון</t>
+          <t>משאבי שדה</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -14451,7 +14451,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>אבו קרינאת</t>
+          <t>מדרשת בן גוריון</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -14481,7 +14481,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>מרחב עם</t>
+          <t>ניצנה</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -14511,7 +14511,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>מרעית</t>
+          <t>תל ערד</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -14541,7 +14541,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ערערה בנגב</t>
+          <t>קדש ברנע</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -14571,7 +14571,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>כמהין</t>
+          <t>רתמים</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -14601,7 +14601,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>שאנטי במדבר</t>
+          <t>כסייפה</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -14631,7 +14631,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>ערד</t>
+          <t>קסר א-סר</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -14661,7 +14661,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>כרמית</t>
+          <t>לקיה</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -14691,7 +14691,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>עומר</t>
+          <t>נבטים</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -14721,7 +14721,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>באר שבע - דרום</t>
+          <t>אום בטין</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -14751,7 +14751,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>גבעות בר</t>
+          <t>תארבין</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -14781,7 +14781,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>תארבין</t>
+          <t>באר שבע - דרום</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -14811,7 +14811,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>תל שבע</t>
+          <t>שגב שלום</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -14841,7 +14841,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>להבים</t>
+          <t>אזור תעשייה עידן הנגב</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -14871,7 +14871,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>באר שבע - מערב</t>
+          <t>רהט</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -14901,7 +14901,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>אשכולות</t>
+          <t>להב</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -14931,7 +14931,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>חצרים</t>
+          <t>מיתר</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -14961,7 +14961,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>חורה</t>
+          <t>באר שבע - צפון</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -14991,7 +14991,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>לקיה</t>
+          <t>סנסנה</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -15021,7 +15021,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>משמר הנגב</t>
+          <t>שובל</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -15051,7 +15051,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>באר שבע - מזרח</t>
+          <t>עומר</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -15081,7 +15081,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>כרמים</t>
+          <t>בית קמה</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -15111,7 +15111,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>שגב שלום</t>
+          <t>כרמים</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -15141,7 +15141,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>שובל</t>
+          <t>חצרים</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -15171,7 +15171,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>רהט</t>
+          <t>אשכולות</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -15201,7 +15201,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>אל סייד</t>
+          <t>באר שבע - מזרח</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -15231,7 +15231,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>אום בטין</t>
+          <t>כרמית</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -15261,7 +15261,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>מיתר</t>
+          <t>באר שבע - מערב</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -15291,7 +15291,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>סנסנה</t>
+          <t>אל סייד</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -15321,7 +15321,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>אזור תעשייה עידן הנגב</t>
+          <t>להבים</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -15351,7 +15351,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>להב</t>
+          <t>משמר הנגב</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -15381,7 +15381,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>אתר דודאים</t>
+          <t>חורה</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -15441,7 +15441,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>נבטים</t>
+          <t>תל שבע</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -15471,7 +15471,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>בית קמה</t>
+          <t>גבעות בר</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -15501,7 +15501,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>באר שבע - צפון</t>
+          <t>אתר דודאים</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -15531,7 +15531,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>קלחים</t>
+          <t>ברוש</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -15559,7 +15559,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>נתיבות</t>
+          <t>פדויים</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -15587,7 +15587,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>גילת</t>
+          <t>קריית חינוך מרחבים</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -15615,7 +15615,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>זרועה</t>
+          <t>שרשרת</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -15643,7 +15643,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>מסלול</t>
+          <t>רנן</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -15671,7 +15671,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>רנן</t>
+          <t>שבי דרום</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -15699,7 +15699,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>בטחה</t>
+          <t>צאלים</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -15727,7 +15727,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>אופקים</t>
+          <t>זרועה</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -15755,7 +15755,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>תפרח</t>
+          <t>דורות</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -15783,7 +15783,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>אזור תעשייה נ.ע.מ</t>
+          <t>רוחמה</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -15811,7 +15811,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>תאשור</t>
+          <t>פטיש</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -15839,7 +15839,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ברור חיל</t>
+          <t>ניר עקיבא</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -15867,7 +15867,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>שבי דרום</t>
+          <t>תדהר</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -15895,7 +15895,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>פטיש</t>
+          <t>יושיביה</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -15923,7 +15923,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>אשל הנשיא</t>
+          <t>תאשור</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -15951,7 +15951,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>שיבולים</t>
+          <t>תפרח</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -15979,7 +15979,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>מבועים</t>
+          <t>אזור תעשייה נ.ע.מ</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -16007,7 +16007,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>צאלים</t>
+          <t>שדה צבי</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -16035,7 +16035,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>פדויים</t>
+          <t>מבועים</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -16063,7 +16063,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>גבולות</t>
+          <t>גילת</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -16091,7 +16091,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>בית הגדי</t>
+          <t>ניר משה</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -16119,7 +16119,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>תדהר</t>
+          <t>קלחים</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -16147,7 +16147,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>ברוש</t>
+          <t>שיבולים</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -16175,7 +16175,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>אורים</t>
+          <t>בית הגדי</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -16203,7 +16203,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>ניר עקיבא</t>
+          <t>מסלול</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -16231,7 +16231,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>יושיביה</t>
+          <t>אופקים</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -16259,7 +16259,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>שרשרת</t>
+          <t>אשבול</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -16287,7 +16287,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>קריית חינוך מרחבים</t>
+          <t>ברור חיל</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -16315,7 +16315,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>שדה צבי</t>
+          <t>אשל הנשיא</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -16343,7 +16343,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>ניר משה</t>
+          <t>אורים</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -16371,7 +16371,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>אשבול</t>
+          <t>נתיבות</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -16399,7 +16399,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>רוחמה</t>
+          <t>בטחה</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -16427,7 +16427,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>דורות</t>
+          <t>גבולות</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -16485,7 +16485,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>מצדה</t>
+          <t>עין בוקק</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -16515,7 +16515,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>עין בוקק</t>
+          <t>עין תמר</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -16545,7 +16545,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>עין גדי</t>
+          <t>מצדה</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -16575,7 +16575,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>מרחצאות עין גדי</t>
+          <t>עין גדי</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>מלונות ים המלח מרכז</t>
+          <t>נאות הכיכר</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -16635,7 +16635,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>חוות מנחם</t>
+          <t>מצפה מדרג</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -16665,7 +16665,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>נווה זוהר</t>
+          <t>חוות מנחם</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -16695,7 +16695,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>נאות הכיכר</t>
+          <t>נווה זוהר</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -16725,7 +16725,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>מצפה מדרג</t>
+          <t>מרחצאות עין גדי</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -16785,7 +16785,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>עין תמר</t>
+          <t>מלונות ים המלח מרכז</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -16815,7 +16815,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>עין חצבה</t>
+          <t>עידן</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -16843,7 +16843,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>עידן</t>
+          <t>עין חצבה</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -16899,7 +16899,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>מצפה יאיר</t>
+          <t>אזור תעשייה מיתרים</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -16927,7 +16927,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>אשתמוע</t>
+          <t>מצפה יאיר</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -16983,7 +16983,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>חוות יויו</t>
+          <t>חוות מקנה יהודה</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -17039,7 +17039,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>אביגיל</t>
+          <t>אשתמוע</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>חוות מקנה יהודה</t>
+          <t>אביגיל</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -17123,7 +17123,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>אזור תעשייה מיתרים</t>
+          <t>סוסיא הקדומה</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -17151,7 +17151,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>סוסיא הקדומה</t>
+          <t>חוות יויו</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -17207,7 +17207,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>הר עמשא</t>
+          <t>טנא עומרים</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -17237,7 +17237,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>מעון</t>
+          <t>בית יתיר</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -17267,7 +17267,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>עשהאל</t>
+          <t>כרמל</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -17297,7 +17297,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>שני ליבנה</t>
+          <t>הר עמשא</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -17327,7 +17327,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>שמעה</t>
+          <t>שני ליבנה</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -17357,7 +17357,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>בית יתיר</t>
+          <t>סוסיא</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -17387,7 +17387,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>כרמל</t>
+          <t>מעון</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -17417,7 +17417,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>סוסיא</t>
+          <t>עשהאל</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -17447,7 +17447,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>טנא עומרים</t>
+          <t>שמעה</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
